--- a/job_results.xlsx
+++ b/job_results.xlsx
@@ -1,27 +1,869 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shiv\Projects\AIML\JobAutoPipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F25DC773A252ABDACC1048A0E95E5B445BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B521D5-ADC1-4237-A19C-2A8D5D7D300B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Job Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="166">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>raw_data</t>
+  </si>
+  <si>
+    <t>09b24e237daa8c76</t>
+  </si>
+  <si>
+    <t>AI Tools &amp; Automation Intern (Developer)</t>
+  </si>
+  <si>
+    <t>Job Role: AI Developer Intern (LLM + MCP + AI Trends)
+Role Overview:
+We are hiring an AI Developer Intern who can both:
+Build AI systems (LLMs, MCP servers, APIs)
+Continuously track and evaluate new AI tools &amp; releases
+This is a builder + researcher hybrid role, but execution &gt; research.
+Key Responsibilities:
+AI Development (Primary Focus)
+Build applications using: OpenAI, Anthropic, Google DeepMind
+Implement: Tool/function calling, Context handling, Prompt pipelines
+MCP Server &amp; AI Systems
+Build and maintain MCP (Model Context Protocol) servers
+Create tools that LLMs can use: APIs, Internal systems
+Design: Multi-step workflows, Structured outputs
+AI Tools &amp; Trends Tracking (Important)
+Stay updated with: New AI tools launches, Model updates, Dev frameworks
+Sources to track: Twitter (AI builders), Product Hunt, GitHub trending
+Filter: What is useful vs hype
+Rapid Prototyping
+Build quick POCs using new tools
+Example: Try new model integrate test report
+Convert useful tools into: Internal features, Product improvements
+Weekly Intelligence Reports
+Share: 5–10 new tools, 2 tools worth implementing, 1 working demo/POC
+Required Skills:
+Must-Have: Python or JavaScript (strong basics), API understanding, Basic LLM knowledge: Tokens, Context Prompting, Critical (Filter Here), Can build, not just explore, Understands: MCP / tool calling, How LLM apps actually work, Cursor, Antigravity
+Good to Have: RAG / vector DB, FastAPI / Node backend, GitHub projects
+Ideal Candidate:
+Builds side projects
+Actively explores new AI tools
+Thinks: “How can I use this in real product?”
+Not a YouTube learner, a doer</t>
+  </si>
+  <si>
+    <t>https://in.indeed.com/viewjob?jk=09b24e237daa8c76</t>
+  </si>
+  <si>
+    <t>Indeed</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>{'jobKey': '09b24e237daa8c76', 'scrapingInfo': {'page': 1, 'index': 0, 'inputUrl': 'https://in.indeed.com/jobs?q=ai+developer&amp;l=Mumbai%2C+Maharashtra&amp;fromage=3&amp;radius=25&amp;sc=0kf%3Aattr%28CF3CP%29%3B&amp;from=searchOnDesktopSerp&amp;vjk=081ff9624c1074d7'}, 'title': 'AI Tools &amp; Automation Intern (Developer)', 'jobType': ['Full-time'], 'descriptionHtml': '&lt;div&gt;&lt;h3 class="jobSectionHeader"&gt;&lt;b&gt;Job Role: AI Developer Intern (LLM + MCP + AI Trends)&lt;/b&gt;&lt;/h3&gt;&lt;p&gt;&lt;b&gt;\nRole Overview:&lt;/b&gt;&lt;br&gt;\nWe are hiring an AI Developer Intern who can both:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;\nBuild AI systems (LLMs, MCP servers, APIs)&lt;/li&gt;&lt;li&gt;\nContinuously track and evaluate new AI tools &amp;amp; releases&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;\nThis is a builder + researcher hybrid role, but execution &amp;gt; research.&lt;/p&gt;&lt;p&gt;&lt;b&gt;\nKey Responsibilities:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;b&gt;\nAI Development (Primary Focus)&lt;/b&gt;&lt;ul&gt;&lt;li&gt;\nBuild applications using: OpenAI, Anthropic, Google DeepMind&lt;/li&gt;&lt;li&gt;\nImplement: Tool/function calling, Context handling, Prompt pipelines&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;b&gt;\nMCP Server &amp;amp; AI Systems&lt;/b&gt;&lt;ul&gt;&lt;li&gt;\nBuild and maintain MCP (Model Context Protocol) servers&lt;/li&gt;&lt;li&gt;\nCreate tools that LLMs can use: APIs, Internal systems&lt;/li&gt;&lt;li&gt;\nDesign: Multi-step workflows, Structured outputs&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;b&gt;\nAI Tools &amp;amp; Trends Tracking (Important)&lt;/b&gt;&lt;ul&gt;&lt;li&gt;\nStay updated with: New AI tools launches, Model updates, Dev frameworks&lt;/li&gt;&lt;li&gt;\nSources to track: Twitter (AI builders), Product Hunt, GitHub trending&lt;/li&gt;&lt;li&gt;\nFilter: What is useful vs hype&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;b&gt;\nRapid Prototyping&lt;/b&gt;&lt;ul&gt;&lt;li&gt;\nBuild quick POCs using new tools&lt;/li&gt;\nExample: Try new model integrate test&lt;li&gt; report&lt;/li&gt;&lt;li&gt;\nConvert useful tools into: Internal features, Product improvements&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;b&gt;\nWeekly Intelligence Reports&lt;/b&gt;&lt;ul&gt;&lt;li&gt;\nShare: 5&amp;ndash;10 new tools, 2 tools worth implementing, 1 working demo/POC&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;&lt;br&gt;\nRequired Skills:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;\nMust-Have: Python or JavaScript (strong basics), API understanding, Basic LLM knowledge: Tokens, Context Prompting, Critical (Filter Here), Can build, not just explore, Understands: MCP / tool calling, How LLM apps actually work, Cursor, Antigravity&lt;/li&gt;&lt;li&gt;\nGood to Have: RAG / vector DB, FastAPI / Node backend, GitHub projects&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;\nIdeal Candidate:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;\nBuilds side projects&lt;/li&gt;&lt;li&gt;\nActively explores new AI tools&lt;/li&gt;&lt;li&gt;\nThinks: &amp;ldquo;How can I use this in real product?&amp;rdquo;&lt;/li&gt;&lt;li&gt;\nNot a YouTube learner, a doer&lt;/li&gt;&lt;/ul&gt;&lt;/div&gt;&lt;p&gt;&lt;/p&gt;', 'descriptionText': 'Job Role: AI Developer Intern (LLM + MCP + AI Trends)\n\nRole Overview:\nWe are hiring an AI Developer Intern who can both:\n\nBuild AI systems (LLMs, MCP servers, APIs)\nContinuously track and evaluate new AI tools &amp; releases\n\nThis is a builder + researcher hybrid role, but execution &gt; research.\n\nKey Responsibilities:\n\nAI Development (Primary Focus)\nBuild applications using: OpenAI, Anthropic, Google DeepMind\nImplement: Tool/function calling, Context handling, Prompt pipelines\nMCP Server &amp; AI Systems\nBuild and maintain MCP (Model Context Protocol) servers\nCreate tools that LLMs can use: APIs, Internal systems\nDesign: Multi-step workflows, Structured outputs\nAI Tools &amp; Trends Tracking (Important)\nStay updated with: New AI tools launches, Model updates, Dev frameworks\nSources to track: Twitter (AI builders), Product Hunt, GitHub trending\nFilter: What is useful vs hype\nRapid Prototyping\nBuild quick POCs using new tools\nExample: Try new model integrate test report\nConvert useful tools into: Internal features, Product improvements\nWeekly Intelligence Reports\nShare: 5–10 new tools, 2 tools worth implementing, 1 working demo/POC\n\nRequired Skills:\n\nMust-Have: Python or JavaScript (strong basics), API understanding, Basic LLM knowledge: Tokens, Context Prompting, Critical (Filter Here), Can build, not just explore, Understands: MCP / tool calling, How LLM apps actually work, Cursor, Antigravity\nGood to Have: RAG / vector DB, FastAPI / Node backend, GitHub projects\n\nIdeal Candidate:\n\nBuilds side projects\nActively explores new AI tools\nThinks: “How can I use this in real product?”\nNot a YouTube learner, a doer', 'companyName': 'Hudson Manpower', 'companyUrl': 'https://in.indeed.com/cmp/Hudson-Manpower', 'location': {'city': None, 'postalCode': None, 'country': 'India', 'countryCode': 'IN', 'formattedAddressLong': 'Mumbai, Maharashtra', 'formattedAddressShort': 'Mumbai, Maharashtra', 'latitude': 19.148296, 'longitude': 72.88497, 'streetAddress': None, 'fullAddress': 'Mumbai, Maharashtra'}, 'salary': {'salaryCurrency': 'INR', 'salaryMax': 15000, 'salaryMin': 5000, 'salarySource': 'EXTRACTION', 'salaryText': '₹5,000 - ₹15,000 a month', 'salaryType': 'monthly'}, 'rating': {'rating': 0, 'count': 0}, 'benefits': [], 'occupation': ['Software Development Occupations', 'Data &amp; Database Occupations', 'Technology Occupations', 'Software Development &amp; Architecture Occupations', 'Data Scientists &amp; Statisticians'], 'attributes': ['Node.js', 'Law', 'MCP', 'Full-time', 'Git', "Master's degree", "Bachelor's degree", 'JavaScript', 'Hybrid work', 'GitHub', 'APIs', 'AI', 'Python'], 'contacts': [], 'shifts': [], 'socialInsurance': [], 'workingSystem': [], 'shiftAndSchedule': [], 'postedToday': False, 'hiringDemand': {'isHighVolumeHiring': False, 'isUrgentHire': False}, 'datePublished': '2026-04-07', 'expired': False, 'source': 'Hudson Manpower', 'age': '3 days ago', 'isRemote': False, 'locale': 'in', 'language': 'en', 'jobUrl': 'https://in.indeed.com/viewjob?jk=09b24e237daa8c76', 'emails': [], 'companyAddresses': [], 'companyLinks': {'facebook': None, 'instagram': None, 'twitter': None, 'customLinks': [], 'corporateWebsite': None}, 'companyCeo': {'name': None, 'photoUrl': None, 'startDate': None}, 'numOfCandidates': None, 'requirements': []}</t>
+  </si>
+  <si>
+    <t>6e6973fba943569f</t>
+  </si>
+  <si>
+    <t>Python Developer (Backend &amp; AI) – Contract</t>
+  </si>
+  <si>
+    <t>*Job Description:*
+*Job Type:* Contract (6 months, extendable)
+We are looking for a Python Developer with experience in backend development and basic exposure to AI-based applications.
+*Responsibilities:*
+* Develop backend applications using Python
+* Work with data using Pandas and NumPy
+* Build and maintain APIs (Flask or FastAPI)
+* Support AI-related development work
+* Deploy applications on AWS
+* Work with team members on project tasks
+*Requirements:*
+* 5+ years of Python development experience
+* Knowledge of APIs (Flask or FastAPI)
+* Basic experience with AWS
+* Understanding of databases (PostgreSQL, MongoDB, etc.)
+* Familiarity with Git
+*Good to Have:*
+* Exposure to AI tools (LangChain or similar)
+* Experience with PySpark
+Pay: ₹90,000.00 - ₹110,000.00 per month
+Work Location: In person</t>
+  </si>
+  <si>
+    <t>https://in.indeed.com/viewjob?jk=6e6973fba943569f</t>
+  </si>
+  <si>
+    <t>{'jobKey': '6e6973fba943569f', 'scrapingInfo': {'page': 1, 'index': 1, 'inputUrl': 'https://in.indeed.com/jobs?q=ai+developer&amp;l=Mumbai%2C+Maharashtra&amp;fromage=3&amp;radius=25&amp;sc=0kf%3Aattr%28CF3CP%29%3B&amp;from=searchOnDesktopSerp&amp;vjk=081ff9624c1074d7'}, 'title': 'Python Developer (Backend &amp; AI) – Contract', 'jobType': ['Full-time'], 'descriptionHtml': '&lt;p&gt;&lt;b&gt;Job Description:&lt;/b&gt;&lt;/p&gt;&lt;p&gt;&lt;b&gt;Job Type:&lt;/b&gt; Contract (6 months, extendable)&lt;/p&gt;&lt;p&gt;We are looking for a Python Developer with experience in backend development and basic exposure to AI-based applications.&lt;/p&gt;&lt;p&gt;&lt;b&gt;Responsibilities:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Develop backend applications using Python&lt;/li&gt;&lt;li&gt;Work with data using Pandas and NumPy&lt;/li&gt;&lt;li&gt;Build and maintain APIs (Flask or FastAPI)&lt;/li&gt;&lt;li&gt;Support AI-related development work&lt;/li&gt;&lt;li&gt;Deploy applications on AWS&lt;/li&gt;&lt;li&gt;Work with team members on project tasks&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;Requirements:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;5+ years of Python development experience&lt;/li&gt;&lt;li&gt;Knowledge of APIs (Flask or FastAPI)&lt;/li&gt;&lt;li&gt;Basic experience with AWS&lt;/li&gt;&lt;li&gt;Understanding of databases (PostgreSQL, MongoDB, etc.)&lt;/li&gt;&lt;li&gt;Familiarity with Git&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;Good to Have:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Exposure to AI tools (LangChain or similar)&lt;/li&gt;&lt;li&gt;Experience with PySpark&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Pay: ₹90,000.00 - ₹110,000.00 per month&lt;/p&gt;&lt;p&gt;Work Location: In person&lt;/p&gt;', 'descriptionText': '*Job Description:*\n\n*Job Type:* Contract (6 months, extendable)\n\nWe are looking for a Python Developer with experience in backend development and basic exposure to AI-based applications.\n\n*Responsibilities:*\n\n* Develop backend applications using Python\n* Work with data using Pandas and NumPy\n* Build and maintain APIs (Flask or FastAPI)\n* Support AI-related development work\n* Deploy applications on AWS\n* Work with team members on project tasks\n\n*Requirements:*\n\n* 5+ years of Python development experience\n* Knowledge of APIs (Flask or FastAPI)\n* Basic experience with AWS\n* Understanding of databases (PostgreSQL, MongoDB, etc.)\n* Familiarity with Git\n\n*Good to Have:*\n\n* Exposure to AI tools (LangChain or similar)\n* Experience with PySpark\n\nPay: ₹90,000.00 - ₹110,000.00 per month\n\nWork Location: In person', 'companyName': 'Dsouza Electricals', 'companyUrl': 'https://in.indeed.com/cmp/Dsouza-Electricals', 'location': {'city': None, 'postalCode': None, 'country': 'India', 'countryCode': 'IN', 'formattedAddressLong': 'Andheri East, Mumbai, Maharashtra', 'formattedAddressShort': 'Andheri East, Mumbai, Maharashtra', 'latitude': 19.114424, 'longitude': 72.86794, 'streetAddress': None, 'fullAddress': 'Andheri East, Mumbai, Maharashtra'}, 'salary': {'salaryCurrency': 'INR', 'salaryMax': 110000, 'salaryMin': 90000, 'salarySource': 'EXTRACTION', 'salaryText': '₹90,000 - ₹1,10,000 a month', 'salaryType': 'monthly'}, 'rating': {'rating': 0, 'count': 0}, 'benefits': [], 'occupation': ['Software Development Occupations', 'Back End Developers', 'Technology Occupations', 'Software Development &amp; Architecture Occupations'], 'attributes': ['NumPy', 'Full-time', 'Git', 'MongoDB', 'Databases', 'Pandas', 'AWS', 'PostgreSQL', 'Back-end development', 'APIs', 'In-person', 'Flask', 'AI', 'Python'], 'contacts': [], 'shifts': [], 'socialInsurance': [], 'workingSystem': [], 'shiftAndSchedule': [], 'postedToday': False, 'hiringDemand': {'isHighVolumeHiring': False, 'isUrgentHire': False}, 'datePublished': '2026-04-07', 'expired': False, 'source': 'Indeed', 'age': '3 days ago', 'isRemote': False, 'locale': 'in', 'language': 'en', 'jobUrl': 'https://in.indeed.com/viewjob?jk=6e6973fba943569f', 'emails': [], 'companyAddresses': [], 'companyLinks': {'facebook': None, 'instagram': None, 'twitter': None, 'customLinks': [], 'corporateWebsite': None}, 'companyCeo': {'name': None, 'photoUrl': None, 'startDate': None}, 'numOfCandidates': None, 'requirements': []}</t>
+  </si>
+  <si>
+    <t>8703bdf94a292bd4</t>
+  </si>
+  <si>
+    <t>AI Prompt Specialist</t>
+  </si>
+  <si>
+    <t>*Position:* AI Prompt Specialist
+*Location:* Andheri West, Mumbai
+*Job Type:* Full-Time
+*Working Hours:* Monday – Saturday | 10:00 AM – 7:00 PM
+*About the Company*
+Diamond Atelier operates in the US market with a strong presence in the jewelry industry and is expanding under its brand _Diamond Forest_ into western wear with a nature-inspired aesthetic.
+*Role Overview*
+Translate abstract ideas into high-quality visual references and AI-generated product shoot concepts. The role focuses on building frames, moods, lighting, and compositions to help the team visualize campaigns and shoots before execution.
+*Key Responsibilities*
+* Create AI-generated visual references and concept frames
+* Generate AI-based product shoot concepts and visuals for products
+* Develop mood boards and pre-visualizations for shoots
+* Generate multiple variations (lighting, styling, composition)
+* Align outputs with luxury aesthetics and brand direction
+* Support visual planning for campaigns, shoots, and sets
+*Requirements*
+* Strong understanding of visual aesthetics, lighting, and composition
+* Experience with tools like Midjourney, DALL·E, Stable Diffusion, Runway, Firefly, etc.
+* Ability to write and refine advanced prompts
+* Strong ability to convert abstract ideas into visuals
+* Strong taste level, especially in luxury aesthetics
+*Preferred*
+* Experience in fashion / jewelry / luxury
+* Understanding of real shoot setups
+* Storyboarding or sequence visualization skills
+*Note*
+AI will be used for ideation, visualization, and product shoot concepts only. Final execution will be done through real shoots.
+Job Types: Full-time, Permanent
+Pay: From ₹30,000.00 per month
+Work Location: In person</t>
+  </si>
+  <si>
+    <t>https://in.indeed.com/viewjob?jk=8703bdf94a292bd4</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>{'jobKey': '8703bdf94a292bd4', 'scrapingInfo': {'page': 1, 'index': 2, 'inputUrl': 'https://in.indeed.com/jobs?q=ai+developer&amp;l=Mumbai%2C+Maharashtra&amp;fromage=3&amp;radius=25&amp;sc=0kf%3Aattr%28CF3CP%29%3B&amp;from=searchOnDesktopSerp&amp;vjk=081ff9624c1074d7'}, 'title': 'AI Prompt Specialist', 'jobType': ['Permanent', 'Full-time'], 'descriptionHtml': '&lt;p&gt;&lt;b&gt;Position:&lt;/b&gt; AI Prompt Specialist&lt;br/&gt;&lt;b&gt;Location:&lt;/b&gt; Andheri West, Mumbai&lt;br/&gt;&lt;b&gt;Job Type:&lt;/b&gt; Full-Time&lt;br/&gt;&lt;b&gt;Working Hours:&lt;/b&gt; Monday &amp;ndash; Saturday | 10:00 AM &amp;ndash; 7:00 PM&lt;/p&gt;&lt;p&gt;&lt;b&gt;About the Company&lt;/b&gt;&lt;/p&gt;&lt;p&gt;Diamond Atelier operates in the US market with a strong presence in the jewelry industry and is expanding under its brand &lt;i&gt;Diamond Forest&lt;/i&gt; into western wear with a nature-inspired aesthetic.&lt;/p&gt;&lt;p&gt;&lt;b&gt;Role Overview&lt;/b&gt;&lt;/p&gt;&lt;p&gt;Translate abstract ideas into high-quality visual references and AI-generated product shoot concepts. The role focuses on building frames, moods, lighting, and compositions to help the team visualize campaigns and shoots before execution.&lt;/p&gt;&lt;p&gt;&lt;b&gt;Key Responsibilities&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Create AI-generated visual references and concept frames&lt;/li&gt;&lt;li&gt;Generate AI-based product shoot concepts and visuals for products&lt;/li&gt;&lt;li&gt;Develop mood boards and pre-visualizations for shoots&lt;/li&gt;&lt;li&gt;Generate multiple variations (lighting, styling, composition)&lt;/li&gt;&lt;li&gt;Align outputs with luxury aesthetics and brand direction&lt;/li&gt;&lt;li&gt;Support visual planning for campaigns, shoots, and sets&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;Requirements&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Strong understanding of visual aesthetics, lighting, and composition&lt;/li&gt;&lt;li&gt;Experience with tools like Midjourney, DALL&amp;middot;E, Stable Diffusion, Runway, Firefly, etc.&lt;/li&gt;&lt;li&gt;Ability to write and refine advanced prompts&lt;/li&gt;&lt;li&gt;Strong ability to convert abstract ideas into visuals&lt;/li&gt;&lt;li&gt;Strong taste level, especially in luxury aesthetics&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;Preferred&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Experience in fashion / jewelry / luxury&lt;/li&gt;&lt;li&gt;Understanding of real shoot setups&lt;/li&gt;&lt;li&gt;Storyboarding or sequence visualization skills&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;Note&lt;/b&gt;&lt;/p&gt;&lt;p&gt;AI will be used for ideation, visualization, and product shoot concepts only. Final execution will be done through real shoots.&lt;/p&gt;&lt;p&gt;Job Types: Full-time, Permanent&lt;/p&gt;&lt;p&gt;Pay: From ₹30,000.00 per month&lt;/p&gt;&lt;p&gt;Work Location: In person&lt;/p&gt;', 'descriptionText': '*Position:* AI Prompt Specialist\n*Location:* Andheri West, Mumbai\n*Job Type:* Full-Time\n*Working Hours:* Monday – Saturday | 10:00 AM – 7:00 PM\n\n*About the Company*\n\nDiamond Atelier operates in the US market with a strong presence in the jewelry industry and is expanding under its brand _Diamond Forest_ into western wear with a nature-inspired aesthetic.\n\n*Role Overview*\n\nTranslate abstract ideas into high-quality visual references and AI-generated product shoot concepts. The role focuses on building frames, moods, lighting, and compositions to help the team visualize campaigns and shoots before execution.\n\n*Key Responsibilities*\n\n* Create AI-generated visual references and concept frames\n* Generate AI-based product shoot concepts and visuals for products\n* Develop mood boards and pre-visualizations for shoots\n* Generate multiple variations (lighting, styling, composition)\n* Align outputs with luxury aesthetics and brand direction\n* Support visual planning for campaigns, shoots, and sets\n\n*Requirements*\n\n* Strong understanding of visual aesthetics, lighting, and composition\n* Experience with tools like Midjourney, DALL·E, Stable Diffusion, Runway, Firefly, etc.\n* Ability to write and refine advanced prompts\n* Strong ability to convert abstract ideas into visuals\n* Strong taste level, especially in luxury aesthetics\n\n*Preferred*\n\n* Experience in fashion / jewelry / luxury\n* Understanding of real shoot setups\n* Storyboarding or sequence visualization skills\n\n*Note*\n\nAI will be used for ideation, visualization, and product shoot concepts only. Final execution will be done through real shoots.\n\nJob Types: Full-time, Permanent\n\nPay: From ₹30,000.00 per month\n\nWork Location: In person', 'companyName': 'DIAMOND ATELIER', 'companyUrl': 'https://in.indeed.com/cmp/Diamond-Atelier-4', 'location': {'city': None, 'postalCode': None, 'country': 'India', 'countryCode': 'IN', 'formattedAddressLong': 'Mumbai, Maharashtra', 'formattedAddressShort': 'Mumbai, Maharashtra', 'latitude': 19.148296, 'longitude': 72.88497, 'streetAddress': None, 'fullAddress': 'Mumbai, Maharashtra'}, 'salary': {'salaryCurrency': 'INR', 'salarySource': 'EXTRACTION', 'salaryText': 'From ₹30,000 a month', 'salaryType': 'monthly'}, 'rating': {'rating': 0, 'count': 0}, 'benefits': [], 'occupation': ['Science &amp; Research Occupations'], 'attributes': ['Permanent', 'Full-time', 'In-person', 'AI'], 'contacts': [], 'shifts': [], 'socialInsurance': [], 'workingSystem': [], 'shiftAndSchedule': [], 'postedToday': True, 'hiringDemand': {'isHighVolumeHiring': False, 'isUrgentHire': False}, 'datePublished': '2026-04-10', 'expired': False, 'source': 'Indeed', 'age': 'an hour ago', 'isRemote': False, 'locale': 'in', 'language': 'en', 'jobUrl': 'https://in.indeed.com/viewjob?jk=8703bdf94a292bd4', 'emails': [], 'companyAddresses': [], 'companyDescription': 'Diamond Atelier is a leading company,  in a Diamond Industry lead its business in a Lab Grown Diamond ( CVD/HPHT)  by providing customized products to the Clients by knowing their needs. Diamond Atelier’s Vision is to reach the clients overall the World.', 'companyLinks': {'facebook': None, 'instagram': None, 'twitter': None, 'customLinks': [], 'corporateWebsite': None}, 'companyCeo': {'name': None, 'photoUrl': None, 'startDate': None}, 'numOfCandidates': None, 'requirements': []}</t>
+  </si>
+  <si>
+    <t>34e776f0ccb1e85a</t>
+  </si>
+  <si>
+    <t>Front End Developer</t>
+  </si>
+  <si>
+    <t>*Job Summary:*
+We are looking for a skilled Frontend Developer (Min exp 2-5 years) to build responsive and user-friendly web applications for banking and financial platforms such as CBS, UPI, and payment systems. The candidate should have strong expertise in modern front-end technologies and a focus on performance, usability, and security.
+*Key Responsibilities:*
+* Develop and maintain *responsive web applications* using modern frontend frameworks
+* Build intuitive UI/UX for *banking and payment platforms*
+* Integrate frontend with *REST APIs and backend services*
+* Ensure cross-browser compatibility and mobile responsiveness
+* Optimize applications for maximum speed and scalability
+* Implement *secure coding practices* as per industry standards
+* Collaborate with backend developers, QA, and design teams
+* Troubleshoot and fix UI issues and bugs
+* Participate in code reviews and follow best practices
+* *Required Skills:*
+* Strong knowledge of *HTML5, CSS3, JavaScript (ES6+)*
+* Hands-on experience with *Angular / React / Vue.js* (Angular preferred)
+* Experience with *TypeScript* (for Angular)
+* Understanding of *REST API integration*
+* Knowledge of *responsive design frameworks (Bootstrap, Tailwind)*
+* Familiarity with *Git version control*
+* Basic understanding of *web security practices*
+*Preferred Skills:*
+* Experience in *banking/fintech domain (CBS, UPI, Payment systems)*
+* Knowledge of *UI/UX design principles*
+* Experience with *state management (NgRx, Redux, etc.)*
+* Familiarity with *CI/CD pipelines*
+* Understanding of *performance optimization techniques*
+*Educational Qualification:* Bachelor’s degree in computer science, IT, or related field
+*Soft Skills:*
+* Strong problem-solving ability
+* Good communication and teamwork
+* Attention to detail and design sense
+*Why Join Us:*
+* Work on *cutting-edge fintech and banking platforms*
+* Opportunity to contribute to *UPI and digital payment systems*
+* Collaborative and growth-focused work environment
+Pay: ₹600,000.00 - ₹1,000,000.00 per year
+Benefits:
+* Paid sick time
+* Paid time off
+* Provident Fund
+Work Location: In person</t>
+  </si>
+  <si>
+    <t>https://in.indeed.com/viewjob?jk=34e776f0ccb1e85a</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>{'jobKey': '34e776f0ccb1e85a', 'scrapingInfo': {'page': 1, 'index': 0, 'inputUrl': 'https://in.indeed.com/jobs?q=front+end+developer&amp;l=Mumbai%2C+Maharashtra&amp;fromage=3&amp;radius=25&amp;sc=0kf%3Aattr%285QWDV%7C7EQCZ%7CCF3CP%252COR%29attr%286M28R%7C84K74%7CFGY89%7CJB2WC%7CNGEEK%7CX62BT%7CY7U37%252COR%29%3B&amp;from=searchOnDesktopSerp&amp;vjk=eba79aef448b8e17'}, 'title': 'Front End Developer', 'jobType': ['Full-time'], 'descriptionHtml': '&lt;p&gt;&lt;b&gt;Job Summary:&lt;/b&gt;&lt;/p&gt;&lt;p&gt;We are looking for a skilled Frontend Developer (Min exp 2-5 years) to build responsive and user-friendly web applications for banking and financial platforms such as CBS, UPI, and payment systems. The candidate should have strong expertise in modern front-end technologies and a focus on performance, usability, and security.&lt;/p&gt;&lt;p&gt;&lt;b&gt;Key Responsibilities:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Develop and maintain &lt;b&gt;responsive web applications&lt;/b&gt; using modern frontend frameworks&lt;/li&gt;&lt;li&gt;Build intuitive UI/UX for &lt;b&gt;banking and payment platforms&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Integrate frontend with &lt;b&gt;REST APIs and backend services&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Ensure cross-browser compatibility and mobile responsiveness&lt;/li&gt;&lt;li&gt;Optimize applications for maximum speed and scalability&lt;/li&gt;&lt;li&gt;Implement &lt;b&gt;secure coding practices&lt;/b&gt; as per industry standards&lt;/li&gt;&lt;li&gt;Collaborate with backend developers, QA, and design teams&lt;/li&gt;&lt;li&gt;Troubleshoot and fix UI issues and bugs&lt;/li&gt;&lt;li&gt;Participate in code reviews and follow best practices&lt;/li&gt;&lt;li&gt;&lt;b&gt;Required Skills:&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Strong knowledge of &lt;b&gt;HTML5, CSS3, JavaScript (ES6+)&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Hands-on experience with &lt;b&gt;Angular / React / Vue.js&lt;/b&gt; (Angular preferred)&lt;/li&gt;&lt;li&gt;Experience with &lt;b&gt;TypeScript&lt;/b&gt; (for Angular)&lt;/li&gt;&lt;li&gt;Understanding of &lt;b&gt;REST API integration&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Knowledge of &lt;b&gt;responsive design frameworks (Bootstrap, Tailwind)&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Familiarity with &lt;b&gt;Git version control&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Basic understanding of &lt;b&gt;web security practices&lt;/b&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;Preferred Skills:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Experience in &lt;b&gt;banking/fintech domain (CBS, UPI, Payment systems)&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Knowledge of &lt;b&gt;UI/UX design principles&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Experience with &lt;b&gt;state management (NgRx, Redux, etc.)&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Familiarity with &lt;b&gt;CI/CD pipelines&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Understanding of &lt;b&gt;performance optimization techniques&lt;/b&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;Educational Qualification:&lt;/b&gt; Bachelor&amp;rsquo;s degree in computer science, IT, or related field&lt;/p&gt;&lt;p&gt;&lt;b&gt;Soft Skills:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Strong problem-solving ability&lt;/li&gt;&lt;li&gt;Good communication and teamwork&lt;/li&gt;&lt;li&gt;Attention to detail and design sense&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;Why Join Us:&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Work on &lt;b&gt;cutting-edge fintech and banking platforms&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Opportunity to contribute to &lt;b&gt;UPI and digital payment systems&lt;/b&gt;&lt;/li&gt;&lt;li&gt;Collaborative and growth-focused work environment&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Pay: ₹600,000.00 - ₹1,000,000.00 per year&lt;/p&gt;&lt;p&gt;Benefits:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Paid sick time&lt;/li&gt;&lt;li&gt;Paid time off&lt;/li&gt;&lt;li&gt;Provident Fund&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Work Location: In person&lt;/p&gt;', 'descriptionText': '*Job Summary:*\n\nWe are looking for a skilled Frontend Developer (Min exp 2-5 years) to build responsive and user-friendly web applications for banking and financial platforms such as CBS, UPI, and payment systems. The candidate should have strong expertise in modern front-end technologies and a focus on performance, usability, and security.\n\n*Key Responsibilities:*\n\n* Develop and maintain *responsive web applications* using modern frontend frameworks\n* Build intuitive UI/UX for *banking and payment platforms*\n* Integrate frontend with *REST APIs and backend services*\n* Ensure cross-browser compatibility and mobile responsiveness\n* Optimize applications for maximum speed and scalability\n* Implement *secure coding practices* as per industry standards\n* Collaborate with backend developers, QA, and design teams\n* Troubleshoot and fix UI issues and bugs\n* Participate in code reviews and follow best practices\n* *Required Skills:*\n* Strong knowledge of *HTML5, CSS3, JavaScript (ES6+)*\n* Hands-on experience with *Angular / React / Vue.js* (Angular preferred)\n* Experience with *TypeScript* (for Angular)\n* Understanding of *REST API integration*\n* Knowledge of *responsive design frameworks (Bootstrap, Tailwind)*\n* Familiarity with *Git version control*\n* Basic understanding of *web security practices*\n\n*Preferred Skills:*\n\n* Experience in *banking/fintech domain (CBS, UPI, Payment systems)*\n* Knowledge of *UI/UX design principles*\n* Experience with *state management (NgRx, Redux, etc.)*\n* Familiarity with *CI/CD pipelines*\n* Understanding of *performance optimization techniques*\n\n*Educational Qualification:* Bachelor’s degree in computer science, IT, or related field\n\n*Soft Skills:*\n\n* Strong problem-solving ability\n* Good communication and teamwork\n* Attention to detail and design sense\n\n*Why Join Us:*\n\n* Work on *cutting-edge fintech and banking platforms*\n* Opportunity to contribute to *UPI and digital payment systems*\n* Collaborative and growth-focused work environment\n\nPay: ₹600,000.00 - ₹1,000,000.00 per year\n\nBenefits:\n* Paid sick time\n* Paid time off\n* Provident Fund\n\nWork Location: In person', 'companyName': 'IDSSPL Technologies Pvt. Ltd.', 'companyUrl': 'https://in.indeed.com/cmp/Idsspl-Technologies-Pvt.-Ltd.', 'location': {'city': None, 'postalCode': None, 'country': 'India', 'countryCode': 'IN', 'formattedAddressLong': 'Mumbai, Maharashtra', 'formattedAddressShort': 'Mumbai, Maharashtra', 'latitude': 19.148296, 'longitude': 72.88497, 'streetAddress': None, 'fullAddress': 'Mumbai, Maharashtra'}, 'salary': {'salaryCurrency': 'INR', 'salaryMax': 1000000, 'salaryMin': 600000, 'salarySource': 'EXTRACTION', 'salaryText': '₹6,00,000 - ₹10,00,000 a year', 'salaryType': 'yearly'}, 'rating': {'rating': 0, 'count': 0}, 'benefits': ['Provident Fund', 'Paid time off', 'Paid sick time'], 'occupation': ['Software Development Occupations', 'Technology Occupations', 'Software Development &amp; Architecture Occupations', 'Front End Developers'], 'attributes': ['BCS', 'CI/CD', 'Provident Fund', 'Computer Science', 'CSS', 'Bootstrap', 'React', 'Full-time', 'Git', 'Responsive web design', 'UI design', "Bachelor's degree", 'Paid time off', 'JavaScript', 'Continuous integration', 'REST', 'Redux', 'Angular', 'UX', 'APIs', 'UI', 'In-person', 'Vue.js', 'TypeScript', 'Communication skills', 'Banking', 'HTML', 'Paid sick time'], 'contacts': [], 'shifts': [], 'socialInsurance': [], 'workingSystem': [], 'shiftAndSchedule': [], 'postedToday': False, 'hiringDemand': {'isHighVolumeHiring': False, 'isUrgentHire': False}, 'datePublished': '2026-04-08', 'expired': False, 'source': 'Indeed', 'age': '2 days ago', 'isRemote': False, 'locale': 'in', 'language': 'en', 'jobUrl': 'https://in.indeed.com/viewjob?jk=34e776f0ccb1e85a', 'emails': [], 'companyAddresses': [], 'companyLinks': {'facebook': None, 'instagram': None, 'twitter': None, 'customLinks': [], 'corporateWebsite': None}, 'companyCeo': {'name': None, 'photoUrl': None, 'startDate': None}, 'numOfCandidates': None, 'requirements': []}</t>
+  </si>
+  <si>
+    <t>cd457ee0a9646a25</t>
+  </si>
+  <si>
+    <t>Front End Team Leader</t>
+  </si>
+  <si>
+    <t>About the Role
+Passion3DWorld is seeking an experienced and dynamic Frontend Lead to head our newly launched Legal Tech vertical. In this senior individual contributor role, you will lead a team of 4 talented frontend engineers, driving the development of cutting-edge legal technology solutions. This is an exciting opportunity to shape the technical direction of a new product line while mentoring and growing a high-performing team.
+Passion3DWorld provides world-class enterprise-specific solutions at the intersection of Robotics, AI/ML, and 3D Printing. Our Legal Tech vertical is a new and rapidly growing arm focused on building intelligent legal products.
+What You'll Do
+- Lead and mentor a team of 4 frontend engineers, conducting code reviews and fostering a culture of technical excellence
+- Architect and build scalable, high-performance web applications using ReactJS, NextJS, NodeJS, and modern frontend frameworks
+- Collaborate closely with product managers, designers, and backend engineers to deliver end-to-end legal technology solutions
+- Define and enforce frontend best practices, coding standards, and technical roadmaps
+- Drive the adoption of modern tools including Tailwind CSS, HTML5, and responsive design principles
+- Work closely with stakeholders to translate business requirements into technical specifications and deliverables
+Qualifications
+- 3+ years of professional frontend development experience, with hands-on expertise in ReactJS and NextJS
+- Proven experience with NodeJS for backend integration and API consumption
+- Strong proficiency in modern CSS frameworks (Tailwind preferred), HTML5, and responsive design
+- Demonstrated experience leading or mentoring a team of engineers
+- Excellent communication skills and the ability to work cross-functionally with product and design teams
+- Strong problem-solving abilities and a passion for building high-quality legal technology products
+Nice to Have
+- Experience building legal tech, fintech, or other regulated-domain applications
+- Familiarity with TypeScript and state management libraries (Redux, Zustand)
+- Experience with CI/CD pipelines and automated testing
+Compensation
+- CTC: 12-15 LPA (based on experience and skills)
+- Full-time, permanent position with flexible working arrangements
+Job Type: Full-time
+Pay: ₹1,200,000.00 - ₹1,500,000.00 per year
+Ability to commute/relocate:
+* Mumbai, Maharashtra: Reliably commute or planning to relocate before starting work (Preferred)
+Education:
+* Bachelor's (Preferred)
+Experience:
+* Front-end development: 3 years (Preferred)
+Language:
+* English (Preferred)
+Work Location: In person</t>
+  </si>
+  <si>
+    <t>https://in.indeed.com/viewjob?jk=cd457ee0a9646a25</t>
+  </si>
+  <si>
+    <t>{'jobKey': 'cd457ee0a9646a25', 'scrapingInfo': {'page': 1, 'index': 1, 'inputUrl': 'https://in.indeed.com/jobs?q=front+end+developer&amp;l=Mumbai%2C+Maharashtra&amp;fromage=3&amp;radius=25&amp;sc=0kf%3Aattr%285QWDV%7C7EQCZ%7CCF3CP%252COR%29attr%286M28R%7C84K74%7CFGY89%7CJB2WC%7CNGEEK%7CX62BT%7CY7U37%252COR%29%3B&amp;from=searchOnDesktopSerp&amp;vjk=eba79aef448b8e17'}, 'title': 'Front End Team Leader', 'jobType': ['Full-time'], 'descriptionHtml': "&lt;p&gt;About the Role&lt;/p&gt;&lt;p&gt;Passion3DWorld is seeking an experienced and dynamic Frontend Lead to head our newly launched Legal Tech vertical. In this senior individual contributor role, you will lead a team of 4 talented frontend engineers, driving the development of cutting-edge legal technology solutions. This is an exciting opportunity to shape the technical direction of a new product line while mentoring and growing a high-performing team.&lt;/p&gt;&lt;p&gt;Passion3DWorld provides world-class enterprise-specific solutions at the intersection of Robotics, AI/ML, and 3D Printing. Our Legal Tech vertical is a new and rapidly growing arm focused on building intelligent legal products.&lt;/p&gt;&lt;p&gt;What You'll Do&lt;/p&gt;&lt;p&gt;- Lead and mentor a team of 4 frontend engineers, conducting code reviews and fostering a culture of technical excellence&lt;/p&gt;&lt;p&gt;- Architect and build scalable, high-performance web applications using ReactJS, NextJS, NodeJS, and modern frontend frameworks&lt;/p&gt;&lt;p&gt;- Collaborate closely with product managers, designers, and backend engineers to deliver end-to-end legal technology solutions&lt;/p&gt;&lt;p&gt;- Define and enforce frontend best practices, coding standards, and technical roadmaps&lt;/p&gt;&lt;p&gt;- Drive the adoption of modern tools including Tailwind CSS, HTML5, and responsive design principles&lt;/p&gt;&lt;p&gt;- Work closely with stakeholders to translate business requirements into technical specifications and deliverables&lt;/p&gt;&lt;p&gt;Qualifications&lt;/p&gt;&lt;p&gt;- 3+ years of professional frontend development experience, with hands-on expertise in ReactJS and NextJS&lt;/p&gt;&lt;p&gt;- Proven experience with NodeJS for backend integration and API consumption&lt;/p&gt;&lt;p&gt;- Strong proficiency in modern CSS frameworks (Tailwind preferred), HTML5, and responsive design&lt;/p&gt;&lt;p&gt;- Demonstrated experience leading or mentoring a team of engineers&lt;/p&gt;&lt;p&gt;- Excellent communication skills and the ability to work cross-functionally with product and design teams&lt;/p&gt;&lt;p&gt;- Strong problem-solving abilities and a passion for building high-quality legal technology products&lt;/p&gt;&lt;p&gt;Nice to Have&lt;/p&gt;&lt;p&gt;- Experience building legal tech, fintech, or other regulated-domain applications&lt;/p&gt;&lt;p&gt;- Familiarity with TypeScript and state management libraries (Redux, Zustand)&lt;/p&gt;&lt;p&gt;- Experience with CI/CD pipelines and automated testing&lt;/p&gt;&lt;p&gt;Compensation&lt;/p&gt;&lt;p&gt;- CTC: 12-15 LPA (based on experience and skills)&lt;/p&gt;&lt;p&gt;- Full-time, permanent position with flexible working arrangements&lt;/p&gt;&lt;p&gt;Job Type: Full-time&lt;/p&gt;&lt;p&gt;Pay: ₹1,200,000.00 - ₹1,500,000.00 per year&lt;/p&gt;&lt;p&gt;Ability to commute/relocate:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Mumbai, Maharashtra: Reliably commute or planning to relocate before starting work (Preferred)&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Education:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Bachelor's (Preferred)&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Experience:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Front-end development: 3 years (Preferred)&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Language:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;English (Preferred)&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Work Location: In person&lt;/p&gt;", 'descriptionText': "About the Role\n\nPassion3DWorld is seeking an experienced and dynamic Frontend Lead to head our newly launched Legal Tech vertical. In this senior individual contributor role, you will lead a team of 4 talented frontend engineers, driving the development of cutting-edge legal technology solutions. This is an exciting opportunity to shape the technical direction of a new product line while mentoring and growing a high-performing team.\n\nPassion3DWorld provides world-class enterprise-specific solutions at the intersection of Robotics, AI/ML, and 3D Printing. Our Legal Tech vertical is a new and rapidly growing arm focused on building intelligent legal products.\n\nWhat You'll Do\n\n- Lead and mentor a team of 4 frontend engineers, conducting code reviews and fostering a culture of technical excellence\n\n- Architect and build scalable, high-performance web applications using ReactJS, NextJS, NodeJS, and modern frontend frameworks\n\n- Collaborate closely with product managers, designers, and backend engineers to deliver end-to-end legal technology solutions\n\n- Define and enforce frontend best practices, coding standards, and technical roadmaps\n\n- Drive the adoption of modern tools including Tailwind CSS, HTML5, and responsive design principles\n\n- Work closely with stakeholders to translate business requirements into technical specifications and deliverables\n\nQualifications\n\n- 3+ years of professional frontend development experience, with hands-on expertise in ReactJS and NextJS\n\n- Proven experience with NodeJS for backend integration and API consumption\n\n- Strong proficiency in modern CSS frameworks (Tailwind preferred), HTML5, and responsive design\n\n- Demonstrated experience leading or mentoring a team of engineers\n\n- Excellent communication skills and the ability to work cross-functionally with product and design teams\n\n- Strong problem-solving abilities and a passion for building high-quality legal technology products\n\nNice to Have\n\n- Experience building legal tech, fintech, or other regulated-domain applications\n\n- Familiarity with TypeScript and state management libraries (Redux, Zustand)\n\n- Experience with CI/CD pipelines and automated testing\n\nCompensation\n\n- CTC: 12-15 LPA (based on experience and skills)\n\n- Full-time, permanent position with flexible working arrangements\n\nJob Type: Full-time\n\nPay: ₹1,200,000.00 - ₹1,500,000.00 per year\n\n\n\nAbility to commute/relocate:\n* Mumbai, Maharashtra: Reliably commute or planning to relocate before starting work (Preferred)\n\nEducation:\n* Bachelor's (Preferred)\n\nExperience:\n* Front-end development: 3 years (Preferred)\n\nLanguage:\n* English (Preferred)\n\nWork Location: In person", 'companyName': 'TechPeek Magnus Solutions Pvt. Ltd.', 'companyUrl': 'https://in.indeed.com/cmp/Techpeek-Magnus-Solutions-Pvt.-Ltd.', 'location': {'city': None, 'postalCode': None, 'country': 'India', 'countryCode': 'IN', 'formattedAddressLong': 'Mumbai, Maharashtra', 'formattedAddressShort': 'Mumbai, Maharashtra', 'latitude': 19.148296, 'longitude': 72.88497, 'streetAddress': 'Andheri Kurla Road', 'fullAddress': 'Mumbai, Maharashtra'}, 'salary': {'salaryCurrency': 'INR', 'salaryMax': 1500000, 'salaryMin': 1200000, 'salarySource': 'EXTRACTION', 'salaryText': '₹12,00,000 - ₹15,00,000 a year', 'salaryType': 'yearly'}, 'rating': {'rating': 0, 'count': 0}, 'benefits': [], 'occupation': ['Software Development Occupations', 'Technology Occupations', 'Software Development &amp; Architecture Occupations', 'Front End Developers'], 'attributes': ['CI/CD', 'Node.js', 'CSS', 'React', 'Test automation', 'Full-time', 'English', 'Responsive web design', "Bachelor's degree", 'Continuous integration', 'Mentoring', 'Redux', 'APIs', 'Front-end development', 'In-person', 'TypeScript', 'Communication skills', 'HTML'], 'contacts': [], 'shifts': [], 'socialInsurance': [], 'workingSystem': [], 'shiftAndSchedule': [], 'postedToday': False, 'hiringDemand': {'isHighVolumeHiring': False, 'isUrgentHire': False}, 'datePublished': '2026-04-08', 'expired': False, 'source': 'Indeed', 'age': '2 days ago', 'isRemote': False, 'locale': 'in', 'language': 'en', 'jobUrl': 'https://in.indeed.com/viewjob?jk=cd457ee0a9646a25', 'emails': [], 'companyAddresses': [], 'companyLinks': {'facebook': None, 'instagram': None, 'twitter': None, 'customLinks': [], 'corporateWebsite': None}, 'companyCeo': {'name': None, 'photoUrl': None, 'startDate': None}, 'numOfCandidates': None, 'requirements': [{'label': 'HTML', 'requirementSeverity': 'REQUIRED'}, {'label': 'CSS', 'requirementSeverity': 'REQUIRED'}, {'label': 'React', 'requirementSeverity': 'REQUIRED'}, {'label': 'TypeScript', 'requirementSeverity': 'REQUIRED'}, {'label': 'Node.js', 'requirementSeverity': 'PREFERRED'}]}</t>
+  </si>
+  <si>
+    <t>ea90ae9827e1f8c7</t>
+  </si>
+  <si>
+    <t>Full Stack Developer</t>
+  </si>
+  <si>
+    <t>*About Us:*
+Exhibit Technologies, a leading media organisation with over 19+ years of experience in print and digital media, specialises in driving conversations in technology, automobiles, and lifestyle. Our diverse portfolio includes two renowned publications: Exhibit, a premium magazine focused on technology and lifestyle, and BBC Top Gear, a celebrated automotive magazine. We craft compelling content, organise engaging events, and develop innovative digital experiences that seamlessly integrate technology, lifestyle, and entertainment to captivate and inspire audiences.
+*About the Role:*
+We are looking for a Full Stack Developer to join our digital team. You’ll play a key role in building and improving our websites and online platforms. If you enjoy creating smooth, fast, and visually engaging digital experiences, this role is for you.
+*Key Responsibilities*
+* Develop and maintain web applications using Laravel and React.
+* Create and manage REST APIs and database structures.
+* Integrate social media APIs (Instagram, YouTube) for campaigns and analytics.
+* Build and manage interactive dashboards and data-driven modules.
+* Ensure all websites are responsive, fast, and user-friendly across devices.
+* Collaborate with the design and content teams for digital campaigns and feature rollouts.
+* Handle code versioning and testing to ensure smooth performance.
+*Must-Have Skills*
+* 2-3 years of experience as a Full Stack Developer.
+* Strong knowledge of Laravel and React/Vue with TypeScript.
+* Experience working with APIs, MySQL/PostgreSQL, and Git.
+* Understanding of responsive design and modern CSS frameworks (Tailwind).
+* Strong problem-solving and debugging skills.
+*Good to Have*
+* Experience with Graph API integrations.
+* Knowledge of data visualization tools (Recharts, Chart.js).
+* Familiarity with testing tools like Pest, PHPUnit, or Jest.
+Job Types: Full-time, Permanent
+Pay: ₹40,000.00 - ₹50,000.00 per month
+Experience:
+* Laravel: 2 years (Required)
+Location:
+* Andheri West, Mumbai, Maharashtra (Required)
+Work Location: In person</t>
+  </si>
+  <si>
+    <t>https://in.indeed.com/viewjob?jk=ea90ae9827e1f8c7</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>{'jobKey': 'ea90ae9827e1f8c7', 'scrapingInfo': {'page': 1, 'index': 2, 'inputUrl': 'https://in.indeed.com/jobs?q=front+end+developer&amp;l=Mumbai%2C+Maharashtra&amp;fromage=3&amp;radius=25&amp;sc=0kf%3Aattr%285QWDV%7C7EQCZ%7CCF3CP%252COR%29attr%286M28R%7C84K74%7CFGY89%7CJB2WC%7CNGEEK%7CX62BT%7CY7U37%252COR%29%3B&amp;from=searchOnDesktopSerp&amp;vjk=eba79aef448b8e17'}, 'title': 'Full Stack Developer', 'jobType': ['Permanent', 'Full-time'], 'descriptionHtml': '&lt;p&gt;&lt;b&gt;About Us:&lt;/b&gt;&lt;br/&gt;Exhibit Technologies, a leading media organisation with over 19+ years of experience in print and digital media, specialises in driving conversations in technology, automobiles, and lifestyle. Our diverse portfolio includes two renowned publications: Exhibit, a premium magazine focused on technology and lifestyle, and BBC Top Gear, a celebrated automotive magazine. We craft compelling content, organise engaging events, and develop innovative digital experiences that seamlessly integrate technology, lifestyle, and entertainment to captivate and inspire audiences.&lt;/p&gt;&lt;p&gt;&lt;b&gt;About the Role:&lt;/b&gt;&lt;br/&gt;We are looking for a Full Stack Developer to join our digital team. You&amp;rsquo;ll play a key role in building and improving our websites and online platforms. If you enjoy creating smooth, fast, and visually engaging digital experiences, this role is for you.&lt;/p&gt;&lt;p&gt;&lt;b&gt;Key Responsibilities&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Develop and maintain web applications using Laravel and React.&lt;/li&gt;&lt;li&gt;Create and manage REST APIs and database structures.&lt;/li&gt;&lt;li&gt;Integrate social media APIs (Instagram, YouTube) for campaigns and analytics.&lt;/li&gt;&lt;li&gt;Build and manage interactive dashboards and data-driven modules.&lt;/li&gt;&lt;li&gt;Ensure all websites are responsive, fast, and user-friendly across devices.&lt;/li&gt;&lt;li&gt;Collaborate with the design and content teams for digital campaigns and feature rollouts.&lt;/li&gt;&lt;li&gt;Handle code versioning and testing to ensure smooth performance.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;Must-Have Skills&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;2-3 years of experience as a Full Stack Developer.&lt;/li&gt;&lt;li&gt;Strong knowledge of Laravel and React/Vue with TypeScript.&lt;/li&gt;&lt;li&gt;Experience working with APIs, MySQL/PostgreSQL, and Git.&lt;/li&gt;&lt;li&gt;Understanding of responsive design and modern CSS frameworks (Tailwind).&lt;/li&gt;&lt;li&gt;Strong problem-solving and debugging skills.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;b&gt;Good to Have&lt;/b&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Experience with Graph API integrations.&lt;/li&gt;&lt;li&gt;Knowledge of data visualization tools (Recharts, Chart.js).&lt;/li&gt;&lt;li&gt;Familiarity with testing tools like Pest, PHPUnit, or Jest.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Job Types: Full-time, Permanent&lt;/p&gt;&lt;p&gt;Pay: ₹40,000.00 - ₹50,000.00 per month&lt;/p&gt;&lt;p&gt;Experience:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Laravel: 2 years (Required)&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Location:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Andheri West, Mumbai, Maharashtra (Required)&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Work Location: In person&lt;/p&gt;', 'companyLogoUrl': 'https://d2q79iu7y748jz.cloudfront.net/s/_squarelogo/256x256/c1a0e1fde4392563a01303e16089a63c', 'descriptionText': '*About Us:*\nExhibit Technologies, a leading media organisation with over 19+ years of experience in print and digital media, specialises in driving conversations in technology, automobiles, and lifestyle. Our diverse portfolio includes two renowned publications: Exhibit, a premium magazine focused on technology and lifestyle, and BBC Top Gear, a celebrated automotive magazine. We craft compelling content, organise engaging events, and develop innovative digital experiences that seamlessly integrate technology, lifestyle, and entertainment to captivate and inspire audiences.\n\n*About the Role:*\nWe are looking for a Full Stack Developer to join our digital team. You’ll play a key role in building and improving our websites and online platforms. If you enjoy creating smooth, fast, and visually engaging digital experiences, this role is for you.\n\n*Key Responsibilities*\n\n* Develop and maintain web applications using Laravel and React.\n* Create and manage REST APIs and database structures.\n* Integrate social media APIs (Instagram, YouTube) for campaigns and analytics.\n* Build and manage interactive dashboards and data-driven modules.\n* Ensure all websites are responsive, fast, and user-friendly across devices.\n* Collaborate with the design and content teams for digital campaigns and feature rollouts.\n* Handle code versioning and testing to ensure smooth performance.\n\n*Must-Have Skills*\n\n* 2-3 years of experience as a Full Stack Developer.\n* Strong knowledge of Laravel and React/Vue with TypeScript.\n* Experience working with APIs, MySQL/PostgreSQL, and Git.\n* Understanding of responsive design and modern CSS frameworks (Tailwind).\n* Strong problem-solving and debugging skills.\n\n*Good to Have*\n\n* Experience with Graph API integrations.\n* Knowledge of data visualization tools (Recharts, Chart.js).\n* Familiarity with testing tools like Pest, PHPUnit, or Jest.\n\nJob Types: Full-time, Permanent\n\nPay: ₹40,000.00 - ₹50,000.00 per month\n\n\n\nExperience:\n* Laravel: 2 years (Required)\n\nLocation:\n* Andheri West, Mumbai, Maharashtra (Required)\n\nWork Location: In person', 'companyName': 'Exhibit Technologies Pvt ltd', 'companyUrl': 'https://in.indeed.com/cmp/Exhibit-Technologies-Pvt-Ltd', 'location': {'city': None, 'postalCode': None, 'country': 'India', 'countryCode': 'IN', 'formattedAddressLong': 'Andheri West, Mumbai, Maharashtra', 'formattedAddressShort': 'Andheri West, Mumbai, Maharashtra', 'latitude': 19.13866, 'longitude': 72.79039, 'streetAddress': None, 'fullAddress': 'Andheri West, Mumbai, Maharashtra'}, 'salary': {'salaryCurrency': 'INR', 'salaryMax': 50000, 'salaryMin': 40000, 'salarySource': 'EXTRACTION', 'salaryText': '₹40,000 - ₹50,000 a month', 'salaryType': 'monthly'}, 'rating': {'rating': 2.7, 'count': 3}, 'benefits': [], 'occupation': ['Software Development Occupations', 'Technology Occupations', 'Software Development &amp; Architecture Occupations'], 'attributes': ['Permanent', 'CSS', 'React', 'Full-stack development', 'Laravel', 'Full-time', 'Git', 'Responsive web design', 'JavaScript', 'PostgreSQL', 'REST', 'APIs', 'In-person', 'Data visualization', 'TypeScript', 'Debugging', 'MySQL'], 'contacts': [], 'shifts': [], 'socialInsurance': [], 'workingSystem': [], 'shiftAndSchedule': [], 'postedToday': False, 'hiringDemand': {'isHighVolumeHiring': False, 'isUrgentHire': False}, 'datePublished': '2026-04-09', 'expired': False, 'source': 'Indeed', 'age': 'a day ago', 'isRemote': False, 'locale': 'in', 'language': 'en', 'jobUrl': 'https://in.indeed.com/viewjob?jk=ea90ae9827e1f8c7', 'emails': [], 'companyAddresses': ['Mumbai'], 'companyNumEmployees': '51 to 200', 'companyDescription': 'It all began in May 2005, when Exhibit Magazine was founded by Ramesh Somani in the city of Kolkata. As things paced up, Exhibit HQ shifted to Mumbai with satellite presence in Singapore, USA, France, and UAE. Today, it’s one of the most respected names in the world of Tech and Lifestyle Media with a resonating tagline that also forms the DNA and core fabric of whatever Exhibit does – Where Tech meets Lifestyle.', 'companyLinks': {'facebook': None, 'instagram': None, 'twitter': None, 'customLinks': [], 'corporateWebsite': 'https://www.exhibit.co.in'}, 'companyCeo': {'name': None, 'photoUrl': None, 'startDate': None}, 'numOfCandidates': None, 'requirements': []}</t>
+  </si>
+  <si>
+    <t>4369073449</t>
+  </si>
+  <si>
+    <t>Full Stack Developer (Python + React)</t>
+  </si>
+  <si>
+    <t>Location: Sion, Mumbai, IN
+Type: Fulltime
+Work Hours: Mon–Fri, 11:00 AM – 8:00 PM
+Reports To: Engineering Manager
+About Decisions + Process Maker
+Decisions + ProcessMaker is a fast‑growing technology company reshaping how organizations automate processes and make smarter, faster business decisions. Our platform brings together workflow automation, rule engines, AI‑powered decisioning, and no‑code/low‑code tools to help enterprises modernize efficiently and at scale.
+We are seeking a skilled Full Stack Developer (Python / React / TypeScript) to join our team and contribute to the development of our Process Intelligence Platform. This role is more front-end-focused, with significant ownership in the evolution of our dashboard and user-facing features built with React and TypeScript. In addition to frontend development, you will also design and develop backend services in Python as part of a fully remote, English-speaking team.
+Key Responsibilities
+Take ownership of the development and evolution of the Process Intelligence dashboard and user-facing features built with React and TypeScript. Design and implement scalable, maintainable frontend architecture with a strong focus on performance and data visualization. Develop and maintain backend services in Python to support analytics, APIs, and data processing needs. Implement and integrate APIs between frontend and backend services, ensuring reliability and performance. Work with complex event log data and contribute to data transformation and processing pipelines. Optimize system performance and scalability across both frontend and backend components. Collaborate closely with product management, designers, and engineers in a fully remote, English-speaking team. Contribute to continuous improvement of code quality, architecture, and development practices. 
+Qualifications
+3+ years of professional experience in TypeScript development / Python (React, Django, Fast API frameworks). Strong experience building complex React/TypeScript enterprise applications using Redux Toolkit, RTK Query, and Tailwind CSS, with a focus on data visualization and scalable component architecture. Proficient in modern Python (3.10+) with strong experience in async programming, type annotations, Pydantic data modeling, and building data transformation pipelines. Bachelor's Degree in computer science, information systems, engineering, or math. Strong communication skills in English. Strong understanding of SDLC methodologies. Ability to manage workloads and conflicting priorities effectively, work both independently and collaboratively, and consistently meet firm deadlines. 
+Preferred Qualifications
+Experience working within cloud vendors (Azure/AWS) and MongoBD atlas. Experience with Chart.js (or similar libraries) for complex data visualizations. Experience in Task and Process Mining technologies. Experience in understanding of workflow technology and process automation methods, and best practices.</t>
+  </si>
+  <si>
+    <t>https://in.linkedin.com/jobs/view/full-stack-developer-python-%2B-react-at-decisions-4369073449?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=Ig137QMBxSCPDVKf%2BaAabw%3D%3D&amp;position=25&amp;pageNum=0</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>2026-04-09T12:40:27.000Z</t>
+  </si>
+  <si>
+    <t>{'id': '4369073449', 'trackingId': 'Ig137QMBxSCPDVKf+aAabw==', 'refId': 'RPfRiYbtzNIwL3U59dKY8w==', 'link': 'https://in.linkedin.com/jobs/view/full-stack-developer-python-%2B-react-at-decisions-4369073449?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=Ig137QMBxSCPDVKf%2BaAabw%3D%3D&amp;position=25&amp;pageNum=0', 'title': 'Full Stack Developer (Python + React)', 'companyName': 'Decisions', 'companyLinkedinUrl': 'https://www.linkedin.com/company/decisions?trk=public_jobs_jserp-result_job-search-card-subtitle', 'companyLogo': 'https://media.licdn.com/dms/image/v2/D4D0BAQFnX495gUTnDQ/company-logo_100_100/B4DZpuWK9oKUAQ-/0/1762787897468/decisions_logo?e=1777507200&amp;v=beta&amp;t=Ca6rOWpM41aAI8a35OIgTTIYqIBHz_miz06i5Cq04eY', 'location': 'Mumbai, Maharashtra, India', 'postedAt': '2026-04-09T12:40:27.000Z', 'benefits': [], 'descriptionHtml': "&lt;strong&gt;Location:&lt;/strong&gt; Sion, Mumbai, IN&lt;br&gt;&lt;br&gt;&lt;strong&gt;Type:&lt;/strong&gt; Fulltime&lt;br&gt;&lt;br&gt;&lt;strong&gt;Work Hours:&lt;/strong&gt; Mon–Fri, 11:00 AM – 8:00 PM&lt;br&gt;&lt;br&gt;&lt;strong&gt;Reports To:&lt;/strong&gt; Engineering Manager&lt;br&gt;&lt;br&gt;&lt;strong&gt;About Decisions + Process Maker&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Decisions + ProcessMaker is a fast‑growing technology company reshaping how organizations automate processes and make smarter, faster business decisions. Our platform brings together workflow automation, rule engines, AI‑powered decisioning, and no‑code/low‑code tools to help enterprises modernize efficiently and at scale.&lt;br&gt;&lt;br&gt;We are seeking a skilled Full Stack Developer (Python / React / TypeScript) to join our team and contribute to the development of our Process Intelligence Platform. This role is more front-end-focused, with significant ownership in the evolution of our dashboard and user-facing features built with React and TypeScript. In addition to frontend development, you will also design and develop backend services in Python as part of a fully remote, English-speaking team.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Key Responsibilities&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Take ownership of the development and evolution of the Process Intelligence dashboard and user-facing features built with React and TypeScript. &lt;/li&gt;&lt;li&gt;Design and implement scalable, maintainable frontend architecture with a strong focus on performance and data visualization. &lt;/li&gt;&lt;li&gt;Develop and maintain backend services in Python to support analytics, APIs, and data processing needs. &lt;/li&gt;&lt;li&gt;Implement and integrate APIs between frontend and backend services, ensuring reliability and performance. &lt;/li&gt;&lt;li&gt;Work with complex event log data and contribute to data transformation and processing pipelines. &lt;/li&gt;&lt;li&gt;Optimize system performance and scalability across both frontend and backend components. &lt;/li&gt;&lt;li&gt;Collaborate closely with product management, designers, and engineers in a fully remote, English-speaking team. &lt;/li&gt;&lt;li&gt;Contribute to continuous improvement of code quality, architecture, and development practices. &lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Qualifications&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;3+ years of professional experience in TypeScript development / Python (React, Django, Fast API frameworks). &lt;/li&gt;&lt;li&gt;Strong experience building complex React/TypeScript enterprise applications using Redux Toolkit, RTK Query, and Tailwind CSS, with a focus on data visualization and scalable component architecture. &lt;/li&gt;&lt;li&gt;Proficient in modern Python (3.10+) with strong experience in async programming, type annotations, Pydantic data modeling, and building data transformation pipelines. &lt;/li&gt;&lt;li&gt;Bachelor's Degree in computer science, information systems, engineering, or math. &lt;/li&gt;&lt;li&gt;Strong communication skills in English. &lt;/li&gt;&lt;li&gt;Strong understanding of SDLC methodologies. &lt;/li&gt;&lt;li&gt;Ability to manage workloads and conflicting priorities effectively, work both independently and collaboratively, and consistently meet firm deadlines. &lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Preferred Qualifications&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Experience working within cloud vendors (Azure/AWS) and MongoBD atlas. &lt;/li&gt;&lt;li&gt;Experience with Chart.js (or similar libraries) for complex data visualizations. &lt;/li&gt;&lt;li&gt;Experience in Task and Process Mining technologies. &lt;/li&gt;&lt;li&gt;Experience in understanding of workflow technology and process automation methods, and best practices.&lt;/li&gt;&lt;/ul&gt;", 'applicantsCount': '200', 'applyUrl': 'https://decisions.com/jobs-listing/5042394007?gh_jid=5042394007&amp;gh_src=8f2d3fd87us', 'salary': '', 'descriptionText': "Location: Sion, Mumbai, IN\n\nType: Fulltime\n\nWork Hours: Mon–Fri, 11:00 AM – 8:00 PM\n\nReports To: Engineering Manager\n\nAbout Decisions + Process Maker\n\nDecisions + ProcessMaker is a fast‑growing technology company reshaping how organizations automate processes and make smarter, faster business decisions. Our platform brings together workflow automation, rule engines, AI‑powered decisioning, and no‑code/low‑code tools to help enterprises modernize efficiently and at scale.\n\nWe are seeking a skilled Full Stack Developer (Python / React / TypeScript) to join our team and contribute to the development of our Process Intelligence Platform. This role is more front-end-focused, with significant ownership in the evolution of our dashboard and user-facing features built with React and TypeScript. In addition to frontend development, you will also design and develop backend services in Python as part of a fully remote, English-speaking team.\n\nKey Responsibilities\n\nTake ownership of the development and evolution of the Process Intelligence dashboard and user-facing features built with React and TypeScript. Design and implement scalable, maintainable frontend architecture with a strong focus on performance and data visualization. Develop and maintain backend services in Python to support analytics, APIs, and data processing needs. Implement and integrate APIs between frontend and backend services, ensuring reliability and performance. Work with complex event log data and contribute to data transformation and processing pipelines. Optimize system performance and scalability across both frontend and backend components. Collaborate closely with product management, designers, and engineers in a fully remote, English-speaking team. Contribute to continuous improvement of code quality, architecture, and development practices. \n\nQualifications\n\n3+ years of professional experience in TypeScript development / Python (React, Django, Fast API frameworks). Strong experience building complex React/TypeScript enterprise applications using Redux Toolkit, RTK Query, and Tailwind CSS, with a focus on data visualization and scalable component architecture. Proficient in modern Python (3.10+) with strong experience in async programming, type annotations, Pydantic data modeling, and building data transformation pipelines. Bachelor's Degree in computer science, information systems, engineering, or math. Strong communication skills in English. Strong understanding of SDLC methodologies. Ability to manage workloads and conflicting priorities effectively, work both independently and collaboratively, and consistently meet firm deadlines. \n\nPreferred Qualifications\n\nExperience working within cloud vendors (Azure/AWS) and MongoBD atlas. Experience with Chart.js (or similar libraries) for complex data visualizations. Experience in Task and Process Mining technologies. Experience in understanding of workflow technology and process automation methods, and best practices.", 'seniorityLevel': 'Mid-Senior level', 'employmentType': 'Full-time', 'jobFunction': 'Engineering and Information Technology', 'industries': 'Software Development', 'inputUrl': 'https://in.linkedin.com/jobs/search?keywords=AI%20Developer&amp;location=India&amp;geoId=102713980&amp;f_JT=F&amp;f_PP=105214831%2C105556991%2C103671728%2C106164952&amp;f_TPR=r86400&amp;position=1&amp;pageNum=0', 'salaryInsights': {}, 'applyMethod': 'OffsiteApply', 'expireAt': 1780575196000, 'postedAtTimestamp': 1775738427000, 'workplaceTypes': ['On-site'], 'workRemoteAllowed': False, 'standardizedTitle': 'Full Stack Engineer', 'country': 'IN', 'companyAddress': {'type': 'PostalAddress', 'streetAddress': '4588 Virginia Beach Blvd', 'addressLocality': 'Virginia Beach', 'addressRegion': 'Virginia', 'postalCode': '23462', 'addressCountry': 'US'}, 'companyWebsite': 'http://www.decisions.com', 'companySlogan': 'Automate Anything. Change Everything. React quickly with our low-code, rules-driven business process automation platform', 'companyDescription': "Decisions provides a rules-driven, no-code platform, enabling companies to drastically reduce their time to market for their applications. Decisions technology is deployed as the basis of multiple commercial applications in healthcare, life sciences, finance, logistics, and operations software. It is used directly by companies on almost every continent, ranging from mid-size companies to many Fortune 500 corporations.\n\nDecisions provides one no-code platform for all types of business processes. With our no-code visual designer you can deploy fast and empower business users to manage their own processes. There are thousands of features built-in, ready to drag and drop and you’re done! Our rules-driven automation allows you to adapt quickly to price changes, regulations, customer demands and more.\n\nWe have seen technology evolve rapidly during the past decade, and the disruption of Covid-19 cannot be understated. Entire industries have been forced to reengineer how they get work done. The chaos caused by the pandemic has shown how ill-prepared many businesses are to adapt to sudden changes. For example, processing paperwork is difficult when employees are remote and paper forms are physically at the office.\n\nWithout automation, these processes grind to a halt. Systems and processes that are inflexible and cannot scale break down when people change their behavior all at once. These are just some of the challenges presented by the global pandemic that are accelerating the adoption of automation and digital transformation.\n\nWe remain committed to delivering an experience that gives more control and configuration ability to administrators. Specifically, allowing programmers to build things that can be configured by non-programmers in a way that is safe, visible and flexible. This challenge has driven us to create numerous technologies in use today at some of the world's largest and most innovative companies.", 'companyEmployeesCount': 270}</t>
+  </si>
+  <si>
+    <t>4399883081</t>
+  </si>
+  <si>
+    <t>Software Engineer - Gen AI</t>
+  </si>
+  <si>
+    <t>About This Role
+Wells Fargo is seeking a Software Engineer - Gen AI. We believe in the power of working together because great ideas can come from anyone. Through collaboration, any employee can have an impact and make a difference for the entire company. Explore opportunities with us for a career in a supportive environment where you can learn and grow
+In This Role, You Will
+Participate in low to moderately complex initiatives and projects associated with the technology domain, including installation, upgrades, and deployment effortsIdentify opportunities for service quality and availability improvements within the technology domain environmentDesign, code, test, debug, and document for low to moderately complex projects and programs associated with technology domain, including upgrades and deploymentsReview and analyze technical assignments or challenges that are related to low to medium risk deliverables and that require research, evaluation, and selection of alternative technology domainsPresent recommendations for resolving issues or may escalate issues as needed to meet established service level agreementsExercise some independent judgment while also developing understanding of given technology domain in reference to security and compliance requirementsProvide information to technology colleagues, internal partners, and stakeholders
+Required Qualifications:
+2+ years of software engineering experience, or equivalent demonstrated through one or a combination of the following: work experience, training, military experience, education
+Desired Qualifications:
+2+ years of software engineering experience in a BFSI GCC or Product Engineering organization.Strong proficiency in Python/Java and LLM orchestration frameworks (LangChain, LangGraph)Basic Knowledge of model context protocols, RAG architectures, and embedding techniquesExperience with model evaluation frameworks and metrics for LLM performanceProficiency in frontend development with React.js for AI applicationsExperience with UI/UX design patterns specific to AI interfacesExperience with vector databases and efficient retrieval methodsKnowledge of prompt engineering techniques and best practicesExperience with containerization and microservices architectureStrong understanding of semantic search and document retrieval systemsWorking knowledge of both structured and unstructured data processingExperience with version control using GitHub and CI/CD pipelinesExperience working with globally distributed teams in Agile scrumsExperience with Google ADK &amp; A2A (preferred but not mandatory) AutoGen, and OpenAI APIsExperience with GCP Vertex AI &amp; Azure AI Foundry preferred. Experience with LLM inferencing (eg.vLLM) preferred Strong verbal and written communication skills
+Job Expectations:
+Understanding of enterprise use cases for Generative AIKnowledge of responsible AI practices and ethical considerationsAbility to optimize AI solutions for performance and costWell versed in MLOps concepts for LLM applicationsStaying current with rapidly evolving Gen AI technologies and best practicesExperience implementing security best practices for AI applications
+Posting End Date:
+14 Apr 2026
+Job posting may come down early due to volume of applicants.
+We Value Equal Opportunity
+Wells Fargo is an equal opportunity employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, status as a protected veteran, or any other legally protected characteristic.
+Employees support our focus on building strong customer relationships balanced with a strong risk mitigating and compliance-driven culture which firmly establishes those disciplines as critical to the success of our customers and company. They are accountable for execution of all applicable risk programs (Credit, Market, Financial Crimes, Operational, Regulatory Compliance), which includes effectively following and adhering to applicable Wells Fargo policies and procedures, appropriately fulfilling risk and compliance obligations, timely and effective escalation and remediation of issues, and making sound risk decisions. There is emphasis on proactive monitoring, governance, risk identification and escalation, as well as making sound risk decisions commensurate with the business unit's risk appetite and all risk and compliance program requirements.
+Candidates applying to job openings posted in Canada: Applications for employment are encouraged from all qualified candidates, including women, persons with disabilities, aboriginal peoples and visible minorities. Accommodation for applicants with disabilities is available upon request in connection with the recruitment process.
+Applicants With Disabilities
+To request a medical accommodation during the application or interview process, visit Disability Inclusion at Wells Fargo .
+Drug and Alcohol Policy
+Wells Fargo maintains a drug free workplace. Please see our Drug and Alcohol Policy to learn more.
+Wells Fargo Recruitment And Hiring Requirements
+ Third-Party recordings are prohibited unless authorized by Wells Fargo. Wells Fargo requires you to directly represent your own experiences during the recruiting and hiring process.
+Reference Number
+R-512208</t>
+  </si>
+  <si>
+    <t>https://in.linkedin.com/jobs/view/software-engineer-gen-ai-at-wells-fargo-4399883081?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=Q9wmQFgFu6Hh0t8B1NSrpA%3D%3D&amp;position=24&amp;pageNum=0</t>
+  </si>
+  <si>
+    <t>2026-04-09T09:39:35.000Z</t>
+  </si>
+  <si>
+    <t>{'id': '4399883081', 'trackingId': 'Q9wmQFgFu6Hh0t8B1NSrpA==', 'refId': 'RPfRiYbtzNIwL3U59dKY8w==', 'link': 'https://in.linkedin.com/jobs/view/software-engineer-gen-ai-at-wells-fargo-4399883081?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=Q9wmQFgFu6Hh0t8B1NSrpA%3D%3D&amp;position=24&amp;pageNum=0', 'title': 'Software Engineer - Gen AI', 'companyName': 'Wells Fargo', 'companyLinkedinUrl': 'https://www.linkedin.com/company/wellsfargo?trk=public_jobs_jserp-result_job-search-card-subtitle', 'companyLogo': 'https://media.licdn.com/dms/image/v2/C4D0BAQGLxWPpGqaVmw/company-logo_100_100/company-logo_100_100/0/1630471638964/wellsfargo_logo?e=1777507200&amp;v=beta&amp;t=VJcu0Iwt7wT3uHwrRKnz1Mt_jNRMxDxUTuJkb7XLHhw', 'location': 'Bengaluru, Karnataka, India', 'postedAt': '2026-04-09T09:39:35.000Z', 'benefits': ['Actively Hiring'], 'descriptionHtml': "&lt;strong&gt;About This Role&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Wells Fargo is seeking a Software Engineer - Gen AI. We believe in the power of working together because great ideas can come from anyone. Through collaboration, any employee can have an impact and make a difference for the entire company. Explore opportunities with us for a career in a supportive environment where you can learn and grow&lt;br&gt;&lt;br&gt;&lt;strong&gt;In This Role, You Will&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Participate in low to moderately complex initiatives and projects associated with the technology domain, including installation, upgrades, and deployment efforts&lt;/li&gt;&lt;li&gt;Identify opportunities for service quality and availability improvements within the technology domain environment&lt;/li&gt;&lt;li&gt;Design, code, test, debug, and document for low to moderately complex projects and programs associated with technology domain, including upgrades and deployments&lt;/li&gt;&lt;li&gt;Review and analyze technical assignments or challenges that are related to low to medium risk deliverables and that require research, evaluation, and selection of alternative technology domains&lt;/li&gt;&lt;li&gt;Present recommendations for resolving issues or may escalate issues as needed to meet established service level agreements&lt;/li&gt;&lt;li&gt;Exercise some independent judgment while also developing understanding of given technology domain in reference to security and compliance requirements&lt;/li&gt;&lt;li&gt;Provide information to technology colleagues, internal partners, and stakeholders&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Required Qualifications:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;2+ years of software engineering experience, or equivalent demonstrated through one or a combination of the following: work experience, training, military experience, education&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Desired Qualifications:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;2+ years of software engineering experience in a BFSI GCC or Product Engineering organization.&lt;/li&gt;&lt;li&gt;Strong proficiency in Python/Java and LLM orchestration frameworks (LangChain, LangGraph)&lt;/li&gt;&lt;li&gt;Basic Knowledge of model context protocols, RAG architectures, and embedding techniques&lt;/li&gt;&lt;li&gt;Experience with model evaluation frameworks and metrics for LLM performance&lt;/li&gt;&lt;li&gt;Proficiency in frontend development with React.js for AI applications&lt;/li&gt;&lt;li&gt;Experience with UI/UX design patterns specific to AI interfaces&lt;/li&gt;&lt;li&gt;Experience with vector databases and efficient retrieval methods&lt;/li&gt;&lt;li&gt;Knowledge of prompt engineering techniques and best practices&lt;/li&gt;&lt;li&gt;Experience with containerization and microservices architecture&lt;/li&gt;&lt;li&gt;Strong understanding of semantic search and document retrieval systems&lt;/li&gt;&lt;li&gt;Working knowledge of both structured and unstructured data processing&lt;/li&gt;&lt;li&gt;Experience with version control using GitHub and CI/CD pipelines&lt;/li&gt;&lt;li&gt;Experience working with globally distributed teams in Agile scrums&lt;/li&gt;&lt;li&gt;Experience with Google ADK &amp;amp; A2A (preferred but not mandatory) AutoGen, and OpenAI APIs&lt;/li&gt;&lt;li&gt;Experience with GCP Vertex AI &amp;amp; Azure AI Foundry preferred. &lt;/li&gt;&lt;li&gt;Experience with LLM inferencing (eg.vLLM) preferred &lt;/li&gt;&lt;li&gt;Strong verbal and written communication skills&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Job Expectations:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understanding of enterprise use cases for Generative AI&lt;/li&gt;&lt;li&gt;Knowledge of responsible AI practices and ethical considerations&lt;/li&gt;&lt;li&gt;Ability to optimize AI solutions for performance and cost&lt;/li&gt;&lt;li&gt;Well versed in MLOps concepts for LLM applications&lt;/li&gt;&lt;li&gt;Staying current with rapidly evolving Gen AI technologies and best practices&lt;/li&gt;&lt;li&gt;Experience implementing security best practices for AI applications&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Posting End Date:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;14 Apr 2026&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt;Job posting may come down early due to volume of applicants.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;We Value Equal Opportunity&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Wells Fargo is an equal opportunity employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, status as a protected veteran, or any other legally protected characteristic.&lt;br&gt;&lt;br&gt;Employees support our focus on building strong customer relationships balanced with a strong risk mitigating and compliance-driven culture which firmly establishes those disciplines as critical to the success of our customers and company. They are accountable for execution of all applicable risk programs (Credit, Market, Financial Crimes, Operational, Regulatory Compliance), which includes effectively following and adhering to applicable Wells Fargo policies and procedures, appropriately fulfilling risk and compliance obligations, timely and effective escalation and remediation of issues, and making sound risk decisions. There is emphasis on proactive monitoring, governance, risk identification and escalation, as well as making sound risk decisions commensurate with the business unit's risk appetite and all risk and compliance program requirements.&lt;br&gt;&lt;br&gt;Candidates applying to job openings posted in Canada: Applications for employment are encouraged from all qualified candidates, including women, persons with disabilities, aboriginal peoples and visible minorities. Accommodation for applicants with disabilities is available upon request in connection with the recruitment process.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Applicants With Disabilities&lt;br&gt;&lt;br&gt;&lt;/strong&gt;To request a medical accommodation during the application or interview process, visit Disability Inclusion at Wells Fargo .&lt;br&gt;&lt;br&gt;&lt;strong&gt;Drug and Alcohol Policy&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Wells Fargo maintains a drug free workplace. Please see our Drug and Alcohol Policy to learn more.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Wells Fargo Recruitment And Hiring Requirements&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt; Third-Party recordings are prohibited unless authorized by Wells Fargo.&lt;/li&gt;&lt;li&gt; Wells Fargo requires you to directly represent your own experiences during the recruiting and hiring process.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Reference Number&lt;br&gt;&lt;br&gt;&lt;/strong&gt;R-512208", 'applicantsCount': '200', 'applyUrl': 'https://tnl2.jometer.com/v2/job?jz=581jn87c367bb7342e679243e574ae612a1d0DQAJQAYBAACQAAAAAAAQ&amp;utm_source=joveo&amp;publisher=Linkedin%20Flat%20bid', 'salary': '', 'descriptionText': "About This Role\n\nWells Fargo is seeking a Software Engineer - Gen AI. We believe in the power of working together because great ideas can come from anyone. Through collaboration, any employee can have an impact and make a difference for the entire company. Explore opportunities with us for a career in a supportive environment where you can learn and grow\n\nIn This Role, You Will\n\nParticipate in low to moderately complex initiatives and projects associated with the technology domain, including installation, upgrades, and deployment effortsIdentify opportunities for service quality and availability improvements within the technology domain environmentDesign, code, test, debug, and document for low to moderately complex projects and programs associated with technology domain, including upgrades and deploymentsReview and analyze technical assignments or challenges that are related to low to medium risk deliverables and that require research, evaluation, and selection of alternative technology domainsPresent recommendations for resolving issues or may escalate issues as needed to meet established service level agreementsExercise some independent judgment while also developing understanding of given technology domain in reference to security and compliance requirementsProvide information to technology colleagues, internal partners, and stakeholders\n\nRequired Qualifications:\n\n2+ years of software engineering experience, or equivalent demonstrated through one or a combination of the following: work experience, training, military experience, education\n\nDesired Qualifications:\n\n2+ years of software engineering experience in a BFSI GCC or Product Engineering organization.Strong proficiency in Python/Java and LLM orchestration frameworks (LangChain, LangGraph)Basic Knowledge of model context protocols, RAG architectures, and embedding techniquesExperience with model evaluation frameworks and metrics for LLM performanceProficiency in frontend development with React.js for AI applicationsExperience with UI/UX design patterns specific to AI interfacesExperience with vector databases and efficient retrieval methodsKnowledge of prompt engineering techniques and best practicesExperience with containerization and microservices architectureStrong understanding of semantic search and document retrieval systemsWorking knowledge of both structured and unstructured data processingExperience with version control using GitHub and CI/CD pipelinesExperience working with globally distributed teams in Agile scrumsExperience with Google ADK &amp; A2A (preferred but not mandatory) AutoGen, and OpenAI APIsExperience with GCP Vertex AI &amp; Azure AI Foundry preferred. Experience with LLM inferencing (eg.vLLM) preferred Strong verbal and written communication skills\n\nJob Expectations:\n\nUnderstanding of enterprise use cases for Generative AIKnowledge of responsible AI practices and ethical considerationsAbility to optimize AI solutions for performance and costWell versed in MLOps concepts for LLM applicationsStaying current with rapidly evolving Gen AI technologies and best practicesExperience implementing security best practices for AI applications\n\nPosting End Date:\n\n14 Apr 2026\n\nJob posting may come down early due to volume of applicants.\n\nWe Value Equal Opportunity\n\nWells Fargo is an equal opportunity employer. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, status as a protected veteran, or any other legally protected characteristic.\n\nEmployees support our focus on building strong customer relationships balanced with a strong risk mitigating and compliance-driven culture which firmly establishes those disciplines as critical to the success of our customers and company. They are accountable for execution of all applicable risk programs (Credit, Market, Financial Crimes, Operational, Regulatory Compliance), which includes effectively following and adhering to applicable Wells Fargo policies and procedures, appropriately fulfilling risk and compliance obligations, timely and effective escalation and remediation of issues, and making sound risk decisions. There is emphasis on proactive monitoring, governance, risk identification and escalation, as well as making sound risk decisions commensurate with the business unit's risk appetite and all risk and compliance program requirements.\n\nCandidates applying to job openings posted in Canada: Applications for employment are encouraged from all qualified candidates, including women, persons with disabilities, aboriginal peoples and visible minorities. Accommodation for applicants with disabilities is available upon request in connection with the recruitment process.\n\nApplicants With Disabilities\n\nTo request a medical accommodation during the application or interview process, visit Disability Inclusion at Wells Fargo .\n\nDrug and Alcohol Policy\n\nWells Fargo maintains a drug free workplace. Please see our Drug and Alcohol Policy to learn more.\n\nWells Fargo Recruitment And Hiring Requirements\n\n Third-Party recordings are prohibited unless authorized by Wells Fargo. Wells Fargo requires you to directly represent your own experiences during the recruiting and hiring process.\n\nReference Number\n\nR-512208", 'seniorityLevel': 'Associate', 'employmentType': 'Full-time', 'jobFunction': 'Information Technology and Engineering', 'industries': 'Financial Services, Investment Management, and Banking', 'inputUrl': 'https://in.linkedin.com/jobs/search?keywords=AI%20Developer&amp;location=India&amp;geoId=102713980&amp;f_JT=F&amp;f_PP=105214831%2C105556991%2C103671728%2C106164952&amp;f_TPR=r86400&amp;position=1&amp;pageNum=0', 'salaryInsights': {}, 'applyMethod': 'OffsiteApply', 'expireAt': 1778319575000, 'postedAtTimestamp': 1775727575000, 'workplaceTypes': [], 'workRemoteAllowed': False, 'standardizedTitle': 'Artificial Intelligence Engineer', 'country': 'IN', 'companyAddress': {'type': 'PostalAddress', 'streetAddress': '420 Montgomery St', 'addressLocality': 'San Francisco', 'addressRegion': 'California', 'postalCode': '94103', 'addressCountry': 'US'}, 'companyWebsite': 'http://www.wellsfargo.com', 'companyDescription': 'Wells Fargo &amp; Company (NYSE: WFC) is a diversified, community-based financial services company with approximately $1.9 trillion in assets. Wells Fargo’s vision is to satisfy our customers’ financial needs and help them succeed financially. Founded in 1852 and headquartered in San Francisco, Wells Fargo provides banking, investment and mortgage products and services, as well as consumer and commercial finance, through more than 7,300 locations, 12,000 ATMs, the internet (wellsfargo.com) and mobile banking, and has offices in over 40 countries and territories to support customers who conduct business in the global economy. With approximately 250,000 team members, Wells Fargo serves one in three households in the United States. Wells Fargo &amp; Company was ranked No. 41 on Fortune’s 2022 rankings of America’s largest corporations. News, insights and perspectives from Wells Fargo are also available at Wells Fargo Stories. \n\nRelevant military experience is considered for veterans and transitioning service men and women. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, sexual orientation, gender identity, national origin, disability, status as a protected veteran, or any other legally protected characteristic.© 2016 Wells Fargo Bank, N.A. All rights reserved. Member FDIC.', 'companyEmployeesCount': 211283}</t>
+  </si>
+  <si>
+    <t>4362188585</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Engineer</t>
+  </si>
+  <si>
+    <t>JD for AI developer role: 
+Job Description: AI Developer
+Job Overview
+We are seeking a skilled AI Developer to design, build, and deploy autonomous AI agents from scratch. This role involves creating intelligent systems that can perceive environments, make decisions, and execute actions in real-world or simulated scenarios. You will leverage machine learning, Python, and specialized frameworks like LangChain and LangGraph to develop scalable AI agents for applications such as automation, robotics, virtual assistants, or multi-agent simulations.
+Key Responsibilities
+Architect and implement AI agents from the ground up using frameworks such as LangChain for chaining LLMs and tools, and LangGraph for stateful, graph-based agent workflows, including perception modules (e.g., using computer vision or NLP), decision-making logic (e.g., via reinforcement learning or planning algorithms), and action execution components.
+Develop and train machine learning models using frameworks like TensorFlow, PyTorch, or Scikit-learn to enable agent learning and adaptation, integrating with LangChain/LangGraph for advanced agent orchestration.
+Integrate AI agents with external systems, APIs, databases, and environments (e.g., simulation tools like OpenAI Gym or real-world interfaces), ensuring seamless tool usage and memory management via LangChain components.
+Optimize agents for performance, scalability, and robustness, including handling edge cases, ethical considerations, and safety protocols within graph-structured agent designs.
+Collaborate with cross-functional teams (e.g., data scientists, software engineers) to iterate on agent designs based on feedback and testing.
+Conduct experiments, simulations, and evaluations to refine agent behaviors and ensure reliability in production.
+Document code, architectures, and methodologies for reproducibility and team knowledge sharing.
+Stay current with advancements in AI agent technologies, such as large language models (LLMs), multi-agent systems, and emerging frameworks like LangChain and LangGraph.
+Required Skills and Qualifications
+Bachelor's or Master's degree in Computer Science, Artificial Intelligence, Machine Learning, or a related field.
+Proficiency in Python programming, with strong experience in ML libraries (e.g., TensorFlow, PyTorch, NumPy, Pandas) and agent-specific tools (e.g., LangChain, LangGraph, AutoGen, RLlib, Hugging Face Transformers).
+Hands-on experience building AI agents from scratch using LangChain for tool integration and agent chains, LangGraph for multi-step reasoning and state management, including reinforcement learning, state machines, graph-based planning, or evolutionary algorithms.
+Solid understanding of data structures, algorithms, software engineering principles, and version control (e.g., Git).
+Familiarity with cloud platforms (e.g., AWS, Google Cloud, Azure) for deploying agents, and tools like Docker/Kubernetes for containerization.
+Strong problem-solving skills, with the ability to debug complex systems and work in agile, fast-paced environments.
+Excellent communication skills to articulate technical designs and collaborate effectively.
+Preferred Qualifications
+Experience with specialized domains like natural language processing (NLP), computer vision, robotics (e.g., ROS), or game AI, integrated with LangChain/LangGraph.
+Knowledge of big data tools (e.g., Spark, Hadoop) or databases (SQL/NoSQL) for handling large-scale agent data.
+Prior work with multi-agent systems, ethical AI, or real-time applications using advanced frameworks.
+Contributions to open-source AI projects or a portfolio demonstrating agent-building expertise (e.g., GitHub repos showcasing LangChain/LangGraph implementations).</t>
+  </si>
+  <si>
+    <t>https://in.linkedin.com/jobs/view/artificial-intelligence-engineer-at-atc-4362188585?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=RWYdtPwA55HXJGj1iiD2zw%3D%3D&amp;position=23&amp;pageNum=0</t>
+  </si>
+  <si>
+    <t>2026-04-09T16:34:46.000Z</t>
+  </si>
+  <si>
+    <t>{'id': '4362188585', 'trackingId': 'RWYdtPwA55HXJGj1iiD2zw==', 'refId': 'RPfRiYbtzNIwL3U59dKY8w==', 'link': 'https://in.linkedin.com/jobs/view/artificial-intelligence-engineer-at-atc-4362188585?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=RWYdtPwA55HXJGj1iiD2zw%3D%3D&amp;position=23&amp;pageNum=0', 'title': 'Artificial Intelligence Engineer', 'companyName': 'ATC', 'companyLinkedinUrl': 'https://www.linkedin.com/company/american-technology-consulting?trk=public_jobs_jserp-result_job-search-card-subtitle', 'companyLogo': 'https://media.licdn.com/dms/image/v2/C4E0BAQHR71hWsUHv0g/company-logo_100_100/company-logo_100_100/0/1630586230009/american_technology_consulting_logo?e=1777507200&amp;v=beta&amp;t=HEZYoJy2fl6sDy3w00-xEgQxsmw8mYaV1NMBTDOBeZw', 'location': 'Hyderabad, Telangana, India', 'postedAt': '2026-04-09T16:34:46.000Z', 'benefits': ['Actively Hiring'], 'descriptionHtml': "&lt;p&gt;JD for AI developer role: &lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Job Description: AI Developer&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Job Overview&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;We are seeking a skilled AI Developer to design, build, and deploy autonomous AI agents from scratch. This role involves creating intelligent systems that can perceive environments, make decisions, and execute actions in real-world or simulated scenarios. You will leverage machine learning, Python, and specialized frameworks like LangChain and LangGraph to develop scalable AI agents for applications such as automation, robotics, virtual assistants, or multi-agent simulations.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Key Responsibilities&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Architect and implement AI agents from the ground up using frameworks such as LangChain for chaining LLMs and tools, and LangGraph for stateful, graph-based agent workflows, including perception modules (e.g., using computer vision or NLP), decision-making logic (e.g., via reinforcement learning or planning algorithms), and action execution components.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Develop and train machine learning models using frameworks like TensorFlow, PyTorch, or Scikit-learn to enable agent learning and adaptation, integrating with LangChain/LangGraph for advanced agent orchestration.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Integrate AI agents with external systems, APIs, databases, and environments (e.g., simulation tools like OpenAI Gym or real-world interfaces), ensuring seamless tool usage and memory management via LangChain components.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Optimize agents for performance, scalability, and robustness, including handling edge cases, ethical considerations, and safety protocols within graph-structured agent designs.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Collaborate with cross-functional teams (e.g., data scientists, software engineers) to iterate on agent designs based on feedback and testing.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Conduct experiments, simulations, and evaluations to refine agent behaviors and ensure reliability in production.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Document code, architectures, and methodologies for reproducibility and team knowledge sharing.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Stay current with advancements in AI agent technologies, such as large language models (LLMs), multi-agent systems, and emerging frameworks like LangChain and LangGraph.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Required Skills and Qualifications&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Bachelor's or Master's degree in Computer Science, Artificial Intelligence, Machine Learning, or a related field.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Proficiency in Python programming, with strong experience in ML libraries (e.g., TensorFlow, PyTorch, NumPy, Pandas) and agent-specific tools (e.g., LangChain, LangGraph, AutoGen, RLlib, Hugging Face Transformers).&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Hands-on experience building AI agents from scratch using LangChain for tool integration and agent chains, LangGraph for multi-step reasoning and state management, including reinforcement learning, state machines, graph-based planning, or evolutionary algorithms.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Solid understanding of data structures, algorithms, software engineering principles, and version control (e.g., Git).&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Familiarity with cloud platforms (e.g., AWS, Google Cloud, Azure) for deploying agents, and tools like Docker/Kubernetes for containerization.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Strong problem-solving skills, with the ability to debug complex systems and work in agile, fast-paced environments.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Excellent communication skills to articulate technical designs and collaborate effectively.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Preferred Qualifications&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Experience with specialized domains like natural language processing (NLP), computer vision, robotics (e.g., ROS), or game AI, integrated with LangChain/LangGraph.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Knowledge of big data tools (e.g., Spark, Hadoop) or databases (SQL/NoSQL) for handling large-scale agent data.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Prior work with multi-agent systems, ethical AI, or real-time applications using advanced frameworks.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Contributions to open-source AI projects or a portfolio demonstrating agent-building expertise (e.g., GitHub repos showcasing LangChain/LangGraph implementations).&lt;/p&gt;", 'applicantsCount': '200', 'salary': '', 'descriptionText': "JD for AI developer role: \nJob Description: AI Developer\nJob Overview\nWe are seeking a skilled AI Developer to design, build, and deploy autonomous AI agents from scratch. This role involves creating intelligent systems that can perceive environments, make decisions, and execute actions in real-world or simulated scenarios. You will leverage machine learning, Python, and specialized frameworks like LangChain and LangGraph to develop scalable AI agents for applications such as automation, robotics, virtual assistants, or multi-agent simulations.\nKey Responsibilities\nArchitect and implement AI agents from the ground up using frameworks such as LangChain for chaining LLMs and tools, and LangGraph for stateful, graph-based agent workflows, including perception modules (e.g., using computer vision or NLP), decision-making logic (e.g., via reinforcement learning or planning algorithms), and action execution components.\nDevelop and train machine learning models using frameworks like TensorFlow, PyTorch, or Scikit-learn to enable agent learning and adaptation, integrating with LangChain/LangGraph for advanced agent orchestration.\nIntegrate AI agents with external systems, APIs, databases, and environments (e.g., simulation tools like OpenAI Gym or real-world interfaces), ensuring seamless tool usage and memory management via LangChain components.\nOptimize agents for performance, scalability, and robustness, including handling edge cases, ethical considerations, and safety protocols within graph-structured agent designs.\nCollaborate with cross-functional teams (e.g., data scientists, software engineers) to iterate on agent designs based on feedback and testing.\nConduct experiments, simulations, and evaluations to refine agent behaviors and ensure reliability in production.\nDocument code, architectures, and methodologies for reproducibility and team knowledge sharing.\nStay current with advancements in AI agent technologies, such as large language models (LLMs), multi-agent systems, and emerging frameworks like LangChain and LangGraph.\nRequired Skills and Qualifications\nBachelor's or Master's degree in Computer Science, Artificial Intelligence, Machine Learning, or a related field.\nProficiency in Python programming, with strong experience in ML libraries (e.g., TensorFlow, PyTorch, NumPy, Pandas) and agent-specific tools (e.g., LangChain, LangGraph, AutoGen, RLlib, Hugging Face Transformers).\nHands-on experience building AI agents from scratch using LangChain for tool integration and agent chains, LangGraph for multi-step reasoning and state management, including reinforcement learning, state machines, graph-based planning, or evolutionary algorithms.\nSolid understanding of data structures, algorithms, software engineering principles, and version control (e.g., Git).\nFamiliarity with cloud platforms (e.g., AWS, Google Cloud, Azure) for deploying agents, and tools like Docker/Kubernetes for containerization.\nStrong problem-solving skills, with the ability to debug complex systems and work in agile, fast-paced environments.\nExcellent communication skills to articulate technical designs and collaborate effectively.\nPreferred Qualifications\nExperience with specialized domains like natural language processing (NLP), computer vision, robotics (e.g., ROS), or game AI, integrated with LangChain/LangGraph.\nKnowledge of big data tools (e.g., Spark, Hadoop) or databases (SQL/NoSQL) for handling large-scale agent data.\nPrior work with multi-agent systems, ethical AI, or real-time applications using advanced frameworks.\nContributions to open-source AI projects or a portfolio demonstrating agent-building expertise (e.g., GitHub repos showcasing LangChain/LangGraph implementations).", 'jobPosterName': 'Arthi Balasubramaniyan', 'jobPosterTitle': 'Talent Acquisition Specialist in ATC |  Intern at PVR inox Limited , “ MBA in Human resources &amp; Marketing |', 'jobPosterPhoto': 'https://media.licdn.com/dms/image/v2/D5603AQE21C3px_Ztcg/profile-displayphoto-shrink_100_100/B56ZeLAPVyHoAU-/0/1750383793452?e=1777507200&amp;v=beta&amp;t=4j9vr__THCIY4fVE-9mBCclpqxdEwnq6rZATvn3Grc4', 'jobPosterProfileUrl': 'https://in.linkedin.com/in/arthi-balasubramaniyan-650283268', 'seniorityLevel': 'Mid-Senior level', 'employmentType': 'Full-time', 'jobFunction': 'Engineering', 'industries': 'Information Services, Technology, Information and Media, and Information Technology &amp; Services', 'inputUrl': 'https://in.linkedin.com/jobs/search?keywords=AI%20Developer&amp;location=India&amp;geoId=102713980&amp;f_JT=F&amp;f_PP=105214831%2C105556991%2C103671728%2C106164952&amp;f_TPR=r86400&amp;position=1&amp;pageNum=0', 'salaryInsights': {}, 'applyMethod': 'ComplexOnsiteApply', 'expireAt': 1779474905000, 'postedAtTimestamp': 1775752486000, 'workplaceTypes': ['On-site'], 'workRemoteAllowed': False, 'standardizedTitle': 'Artificial Intelligence Engineer', 'country': 'IN', 'companyAddress': {'type': 'PostalAddress', 'streetAddress': '12951 University Ave', 'addressLocality': 'Clive', 'addressRegion': 'Iowa', 'postalCode': '50325', 'addressCountry': 'US'}, 'companyWebsite': 'http://www.atc.xyz', 'companySlogan': 'Enterprise AI | SaaS product Development\n ', 'companyDescription': 'Founded in the wake of the 2008 Great Recession, ATC has evolved into a dynamic tech company, known for its ability to adapt quickly to the ever-changing business landscape. For over a decade, we’ve been at the forefront of technological innovation, helping companies transform challenges into opportunities.\n\nIn a world where innovation is essential, ATC empowers businesses to stay ahead by creating cutting-edge software solutions that drive productivity and outperform the competition. We go beyond conventional software development to solve complex business problems with creativity and a passion for technology that enriches lives.\n\nOur comprehensive offerings span strategy, design, automation, custom software development, managed services, and advanced IT solutions, including chatbots and cloud transformations. Through ATC Ventures, we support visionary entrepreneurs, helping them build groundbreaking SaaS startups from the ground up.\n\nOur commitment to technology extends to our Training Division, which has trained over 10,000 professionals across various IT disciplines. As a proud Scaled Agile Gold Transformation Partner, we provide expert training, coaching, and consulting services.\n\nWith headquarters in Iowa and delivery centers across the U.S. and India, our talented, dedicated team is driven to bring bold ideas to life. ATC specializes in a wide range of services, including:\n\nEnterprise AI\nCybersecurity\nDevSecOps\nStaffing\nSoftware Testing &amp; Automation\nSaaS Product Development\nProduct Design (UX/UI)\nCustom AI Models\nPublic Sector Services (State and Federal)\n\nAt ATC, we don’t just build software – we create solutions that shape the future.', 'companyEmployeesCount': 1663}</t>
+  </si>
+  <si>
+    <t>4383721628</t>
+  </si>
+  <si>
+    <t>Applied AI Engineer II</t>
+  </si>
+  <si>
+    <t>Overview
+As an Applied AI Engineer 2 for CXA, you will play a pivotal role in advancing Microsoft's mission to empower every individual and organization on the planet to achieve more. You will contribute to the development and integration of cutting-edge AI technologies into Microsoft products and services, ensuring they are inclusive, ethical, and impactful.
+You will collaborate across product, research and engineering teams to bring innovative solutions to life, applying your expertise in machine learning, data science, and AI to solve complex problems. Your work will directly influence product direction and customer experiences.
+AI Mission and Impact
+We are in an era of unprecedented innovation and openness. As Microsoft continues to lead in AI, we are seeking individuals to help tackle some of the most exciting and meaningful challenges in the field. Our vision is to build a truly open architecture platform that enables users to summon tailored AI agents to drive real-world outcomes.
+We are looking for an Applied AI Scientist 2 to join our team
+This role will combine AI knowledge with applied science expertise, and demonstrate a growth mindset and customer empathy. Join us in shaping the future of AI agents.
+Microsoft’s mission is to empower every person and every organization on the planet to achieve more. As employees we come together with a growth mindset, innovate to empower others, and collaborate to realize our shared goals. Each day we build on our values of respect, integrity, and accountability to create a culture of inclusion where everyone can thrive at work and beyond.
+Responsibilities
+Bringing the State of the Art to Products
+Build collaborative relationships with product and business groups to deliver AI-driven impactResearch and implement state-of-the-art using foundation models, prompt engineering, RAG, graphs, multi-agent architectures, as well as classical machine learning techniques.Fine-tune foundation models using domain-specific datasets. - Evaluate model behavior on relevance, bias, hallucination, and response quality via offline evaluations, shadow experiments, online experiments, and ROI analysis.Apply strong software engineering skills in languages such as C# and Python to design, develop, and optimize scalable, reliable, and maintainable AI‑driven systems.Develop LLM prompts, agents, and query execution workflows, often with tight latency constraints.Build rapid AI solution prototypes, contribute to production deployment of these solutions, debug production code, support MLOps/AIOps. Contribute to papers, patents, and conference presentations. - Translate research into production-ready solutions and measure their impact through A/B testing and telemetry that address customer needs. Ability to use data to identify gaps in AI quality, uncover insights and implement PoCs to show proof of concepts.
+Leveraging Research in real-world problems
+Demonstrate deep expertise in AI subfields (e.g., deep learning, Generative AI, NLP, muti-modal models) to translate cutting-edge research into practical, real-world solutions that drive product innovation and business impact.Share insights on industry trends and applied technologies with engineering and product teams.Formulate strategic plans that integrate state-of-the-art research to meet business goals.
+Documentation
+Maintain clear documentation of experiments, results, and methodologies.Share findings through internal forums, newsletters, and demos to promote innovation and knowledge sharing 
+Ethics, Privacy and Security
+Apply a deep understanding of fairness and bias in AI by proactively identifying and mitigating ethical and security risks—including XPIA (Cross-Prompt Injection Attack) unfairness, bias, and privacy concerns—to ensure equitable and responsible outcomes.
+Ensure responsible AI practices throughout the development lifecycle, from data collection to deployment and monitoring.Contribute to internal ethics and privacy policies and ensure responsible AI practice throughout AI development cycle from data collection to model development, deployment, and monitoring. 
+Specialty Responsibilities
+Design, develop, and integrate generative AI solutions using foundation models and more.Deep understanding of small and large language models architecture, Deep learning, fine tuning techniques, multi-agent architectures, classical ML, and optimization techniques to adapt out-of-the-box solutions to particular business problemsPrepare and analyze data for machine learning, identifying optimal features and addressing data gaps.Develop, train, and evaluate machine learning models and algorithms to solve complex business problems, using modern frameworks and state-of-the-art models, open-source libraries, statistical tools, and rigorous metricsAddress scalability and performance issues using large-scale computing frameworks.Monitor model behavior, guide product monitoring and alerting, and adapt to changes in data streams.
+Qualifications
+Required Qualifications
+Bachelor’s degree in Computer Science, Statistics, Electrical/Computer Engineering, Physics, Mathematics or related field, OR Master’s degree OR PHD AND 1+ years of experience working with machine learning libraries to solve real world AI/ML problems
+Other Requirements
+Ability to meet Microsoft, customer and/or government security screening requirements are required for this role. These requirements include but are not limited to the following specialized security screenings:Microsoft Cloud Background Check: This position will be required to pass the Microsoft Cloud Background Check upon hire/transfer and every two years thereafter.
+Preferred Qualifications
+Experience with MLOps Workflows, including CI/CD, monitoring, and retraining pipelines.Familiarity with modern LLMOps frameworks (e.g., LangChain, PromptFlow)1+ years of experience publishing in peer-reviewed venues or filing patentsExperience presenting at conferences or industry events1+ years of experience conducting research in academic or industry settingsStrong software engineering skills, including hands‑on development experience in C# and Python for building scalable, high‑performance, and production‑ready systems.Experience in working with Generative AI models and ML stacksExperience across the product lifecycle from ideation to shipping
+This position will be open for a minimum of 5 days, with applications accepted on an ongoing basis until the position is filled.
+Microsoft is an equal opportunity employer. All qualified applicants will receive consideration for employment without regard to age, ancestry, citizenship, color, family or medical care leave, gender identity or expression, genetic information, immigration status, marital status, medical condition, national origin, physical or mental disability, political affiliation, protected veteran or military status, race, ethnicity, religion, sex (including pregnancy), sexual orientation, or any other characteristic protected by applicable local laws, regulations and ordinances. If you need assistance with religious accommodations and/or a reasonable accommodation due to a disability during the application process, read more about requesting accommodations.</t>
+  </si>
+  <si>
+    <t>https://in.linkedin.com/jobs/view/applied-ai-engineer-ii-at-microsoft-4383721628?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=hVcriHJY8UuCdWlh858pYQ%3D%3D&amp;position=22&amp;pageNum=0</t>
+  </si>
+  <si>
+    <t>2026-04-09T16:49:29.000Z</t>
+  </si>
+  <si>
+    <t>{'id': '4383721628', 'trackingId': 'hVcriHJY8UuCdWlh858pYQ==', 'refId': 'RPfRiYbtzNIwL3U59dKY8w==', 'link': 'https://in.linkedin.com/jobs/view/applied-ai-engineer-ii-at-microsoft-4383721628?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=hVcriHJY8UuCdWlh858pYQ%3D%3D&amp;position=22&amp;pageNum=0', 'title': 'Applied AI Engineer II', 'companyName': 'Microsoft', 'companyLinkedinUrl': 'https://www.linkedin.com/company/microsoft?trk=public_jobs_jserp-result_job-search-card-subtitle', 'companyLogo': 'https://media.licdn.com/dms/image/v2/D560BAQH32RJQCl3dDQ/company-logo_100_100/B56ZYQ0mrGGoAU-/0/1744038948046/microsoft_logo?e=1777507200&amp;v=beta&amp;t=w5cLA4v0uQc5rekDZijMu_DDZKYKKacQMlZu6z5LW4Y', 'location': 'Bengaluru, Karnataka, India', 'postedAt': '2026-04-09T16:49:29.000Z', 'benefits': ['Actively Hiring'], 'descriptionHtml': "&lt;strong&gt;Overview&lt;br&gt;&lt;br&gt;&lt;/strong&gt;As an Applied AI Engineer 2 for CXA, you will play a pivotal role in advancing Microsoft's mission to empower every individual and organization on the planet to achieve more. You will contribute to the development and integration of cutting-edge AI technologies into Microsoft products and services, ensuring they are inclusive, ethical, and impactful.&lt;br&gt;&lt;br&gt;You will collaborate across product, research and engineering teams to bring innovative solutions to life, applying your expertise in machine learning, data science, and AI to solve complex problems. Your work will directly influence product direction and customer experiences.&lt;br&gt;&lt;br&gt;&lt;strong&gt;AI Mission and Impact&lt;br&gt;&lt;br&gt;&lt;/strong&gt;We are in an era of unprecedented innovation and openness. As Microsoft continues to lead in AI, we are seeking individuals to help tackle some of the most exciting and meaningful challenges in the field. Our vision is to build a truly open architecture platform that enables users to summon tailored AI agents to drive real-world outcomes.&lt;br&gt;&lt;br&gt;We are looking for an Applied AI Scientist 2 to join our team&lt;br&gt;&lt;br&gt;This role will combine AI knowledge with applied science expertise, and demonstrate a growth mindset and customer empathy. Join us in shaping the future of AI agents.&lt;br&gt;&lt;br&gt;Microsoft’s mission is to empower every person and every organization on the planet to achieve more. As employees we come together with a growth mindset, innovate to empower others, and collaborate to realize our shared goals. Each day we build on our values of respect, integrity, and accountability to create a culture of inclusion where everyone can thrive at work and beyond.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Responsibilities&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;strong&gt;Bringing the State of the Art to Products&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build collaborative relationships with product and business groups to deliver AI-driven impact&lt;/li&gt;&lt;li&gt;Research and implement state-of-the-art using foundation models, prompt engineering, RAG, graphs, multi-agent architectures, as well as classical machine learning techniques.&lt;/li&gt;&lt;li&gt;Fine-tune foundation models using domain-specific datasets. - Evaluate model behavior on relevance, bias, hallucination, and response quality via offline evaluations, shadow experiments, online experiments, and ROI analysis.&lt;/li&gt;&lt;li&gt;Apply strong software engineering skills in languages such as C# and Python to design, develop, and optimize scalable, reliable, and maintainable AI‑driven systems.&lt;/li&gt;&lt;li&gt;Develop LLM prompts, agents, and query execution workflows, often with tight latency constraints.&lt;/li&gt;&lt;li&gt;Build rapid AI solution prototypes, contribute to production deployment of these solutions, debug production code, support MLOps/AIOps. Contribute to papers, patents, and conference presentations. - Translate research into production-ready solutions and measure their impact through A/B testing and telemetry that address customer needs. &lt;/li&gt;&lt;li&gt;Ability to use data to identify gaps in AI quality, uncover insights and implement PoCs to show proof of concepts.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Leveraging Research in real-world problems&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Demonstrate deep expertise in AI subfields (e.g., deep learning, Generative AI, NLP, muti-modal models) to translate cutting-edge research into practical, real-world solutions that drive product innovation and business impact.&lt;/li&gt;&lt;li&gt;Share insights on industry trends and applied technologies with engineering and product teams.&lt;/li&gt;&lt;li&gt;Formulate strategic plans that integrate state-of-the-art research to meet business goals.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Documentation&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Maintain clear documentation of experiments, results, and methodologies.&lt;/li&gt;&lt;li&gt;Share findings through internal forums, newsletters, and demos to promote innovation and knowledge sharing &lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Ethics, Privacy and Security&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Apply a deep understanding of fairness and bias in AI by proactively identifying and mitigating ethical and security risks—including XPIA (Cross-Prompt Injection Attack) unfairness, bias, and privacy concerns—to ensure equitable and responsible outcomes.&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt;Ensure responsible AI practices throughout the development lifecycle, from data collection to deployment and monitoring.&lt;/li&gt;&lt;li&gt;Contribute to internal ethics and privacy policies and ensure responsible AI practice throughout AI development cycle from data collection to model development, deployment, and monitoring. &lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Specialty Responsibilities&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Design, develop, and integrate generative AI solutions using foundation models and more.&lt;/li&gt;&lt;li&gt;Deep understanding of small and large language models architecture, Deep learning, fine tuning techniques, multi-agent architectures, classical ML, and optimization techniques to adapt out-of-the-box solutions to particular business problems&lt;/li&gt;&lt;li&gt;Prepare and analyze data for machine learning, identifying optimal features and addressing data gaps.&lt;/li&gt;&lt;li&gt;Develop, train, and evaluate machine learning models and algorithms to solve complex business problems, using modern frameworks and state-of-the-art models, open-source libraries, statistical tools, and rigorous metrics&lt;/li&gt;&lt;li&gt;Address scalability and performance issues using large-scale computing frameworks.&lt;/li&gt;&lt;li&gt;Monitor model behavior, guide product monitoring and alerting, and adapt to changes in data streams.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Qualifications&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;strong&gt;Required Qualifications&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Bachelor’s degree in Computer Science, Statistics, Electrical/Computer Engineering, Physics, Mathematics or related field, OR Master’s degree OR PHD AND 1+ years of experience working with machine learning libraries to solve real world AI/ML problems&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Other Requirements&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Ability to meet Microsoft, customer and/or government security screening requirements are required for this role. These requirements include but are not limited to the following specialized security screenings:&lt;/li&gt;&lt;ul&gt;&lt;li&gt;Microsoft Cloud Background Check: This position will be required to pass the Microsoft Cloud Background Check upon hire/transfer and every two years thereafter.&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/ul&gt;&lt;strong&gt;Preferred Qualifications&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Experience with MLOps Workflows, including CI/CD, monitoring, and retraining pipelines.&lt;/li&gt;&lt;li&gt;Familiarity with modern LLMOps frameworks (e.g., LangChain, PromptFlow)&lt;/li&gt;&lt;li&gt;1+ years of experience publishing in peer-reviewed venues or filing patents&lt;/li&gt;&lt;li&gt;Experience presenting at conferences or industry events&lt;/li&gt;&lt;li&gt;1+ years of experience conducting research in academic or industry settings&lt;/li&gt;&lt;li&gt;Strong software engineering skills, including hands‑on development experience in C# and Python for building scalable, high‑performance, and production‑ready systems.&lt;/li&gt;&lt;li&gt;Experience in working with Generative AI models and ML stacks&lt;/li&gt;&lt;li&gt;Experience across the product lifecycle from ideation to shipping&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;This position will be open for a minimum of 5 days, with applications accepted on an ongoing basis until the position is filled.&lt;br&gt;&lt;br&gt;Microsoft is an equal opportunity employer. All qualified applicants will receive consideration for employment without regard to age, ancestry, citizenship, color, family or medical care leave, gender identity or expression, genetic information, immigration status, marital status, medical condition, national origin, physical or mental disability, political affiliation, protected veteran or military status, race, ethnicity, religion, sex (including pregnancy), sexual orientation, or any other characteristic protected by applicable local laws, regulations and ordinances. If you need assistance with religious accommodations and/or a reasonable accommodation due to a disability during the application process, read more about &lt;strong&gt;requesting accommodations.&lt;/strong&gt;", 'applicantsCount': '200', 'applyUrl': 'https://apply.careers.microsoft.com/careers/job/1970393556735549?utm_source=linkedin&amp;domain=microsoft.com&amp;src=LinkedIn', 'salary': '', 'descriptionText': "Overview\n\nAs an Applied AI Engineer 2 for CXA, you will play a pivotal role in advancing Microsoft's mission to empower every individual and organization on the planet to achieve more. You will contribute to the development and integration of cutting-edge AI technologies into Microsoft products and services, ensuring they are inclusive, ethical, and impactful.\n\nYou will collaborate across product, research and engineering teams to bring innovative solutions to life, applying your expertise in machine learning, data science, and AI to solve complex problems. Your work will directly influence product direction and customer experiences.\n\nAI Mission and Impact\n\nWe are in an era of unprecedented innovation and openness. As Microsoft continues to lead in AI, we are seeking individuals to help tackle some of the most exciting and meaningful challenges in the field. Our vision is to build a truly open architecture platform that enables users to summon tailored AI agents to drive real-world outcomes.\n\nWe are looking for an Applied AI Scientist 2 to join our team\n\nThis role will combine AI knowledge with applied science expertise, and demonstrate a growth mindset and customer empathy. Join us in shaping the future of AI agents.\n\nMicrosoft’s mission is to empower every person and every organization on the planet to achieve more. As employees we come together with a growth mindset, innovate to empower others, and collaborate to realize our shared goals. Each day we build on our values of respect, integrity, and accountability to create a culture of inclusion where everyone can thrive at work and beyond.\n\nResponsibilities\n\nBringing the State of the Art to Products\n\nBuild collaborative relationships with product and business groups to deliver AI-driven impactResearch and implement state-of-the-art using foundation models, prompt engineering, RAG, graphs, multi-agent architectures, as well as classical machine learning techniques.Fine-tune foundation models using domain-specific datasets. - Evaluate model behavior on relevance, bias, hallucination, and response quality via offline evaluations, shadow experiments, online experiments, and ROI analysis.Apply strong software engineering skills in languages such as C# and Python to design, develop, and optimize scalable, reliable, and maintainable AI‑driven systems.Develop LLM prompts, agents, and query execution workflows, often with tight latency constraints.Build rapid AI solution prototypes, contribute to production deployment of these solutions, debug production code, support MLOps/AIOps. Contribute to papers, patents, and conference presentations. - Translate research into production-ready solutions and measure their impact through A/B testing and telemetry that address customer needs. Ability to use data to identify gaps in AI quality, uncover insights and implement PoCs to show proof of concepts.\n\nLeveraging Research in real-world problems\n\nDemonstrate deep expertise in AI subfields (e.g., deep learning, Generative AI, NLP, muti-modal models) to translate cutting-edge research into practical, real-world solutions that drive product innovation and business impact.Share insights on industry trends and applied technologies with engineering and product teams.Formulate strategic plans that integrate state-of-the-art research to meet business goals.\n\nDocumentation\n\nMaintain clear documentation of experiments, results, and methodologies.Share findings through internal forums, newsletters, and demos to promote innovation and knowledge sharing \n\nEthics, Privacy and Security\n\nApply a deep understanding of fairness and bias in AI by proactively identifying and mitigating ethical and security risks—including XPIA (Cross-Prompt Injection Attack) unfairness, bias, and privacy concerns—to ensure equitable and responsible outcomes.\n\nEnsure responsible AI practices throughout the development lifecycle, from data collection to deployment and monitoring.Contribute to internal ethics and privacy policies and ensure responsible AI practice throughout AI development cycle from data collection to model development, deployment, and monitoring. \n\nSpecialty Responsibilities\n\nDesign, develop, and integrate generative AI solutions using foundation models and more.Deep understanding of small and large language models architecture, Deep learning, fine tuning techniques, multi-agent architectures, classical ML, and optimization techniques to adapt out-of-the-box solutions to particular business problemsPrepare and analyze data for machine learning, identifying optimal features and addressing data gaps.Develop, train, and evaluate machine learning models and algorithms to solve complex business problems, using modern frameworks and state-of-the-art models, open-source libraries, statistical tools, and rigorous metricsAddress scalability and performance issues using large-scale computing frameworks.Monitor model behavior, guide product monitoring and alerting, and adapt to changes in data streams.\n\nQualifications\n\nRequired Qualifications\n\nBachelor’s degree in Computer Science, Statistics, Electrical/Computer Engineering, Physics, Mathematics or related field, OR Master’s degree OR PHD AND 1+ years of experience working with machine learning libraries to solve real world AI/ML problems\n\nOther Requirements\n\nAbility to meet Microsoft, customer and/or government security screening requirements are required for this role. These requirements include but are not limited to the following specialized security screenings:Microsoft Cloud Background Check: This position will be required to pass the Microsoft Cloud Background Check upon hire/transfer and every two years thereafter.\nPreferred Qualifications\n\nExperience with MLOps Workflows, including CI/CD, monitoring, and retraining pipelines.Familiarity with modern LLMOps frameworks (e.g., LangChain, PromptFlow)1+ years of experience publishing in peer-reviewed venues or filing patentsExperience presenting at conferences or industry events1+ years of experience conducting research in academic or industry settingsStrong software engineering skills, including hands‑on development experience in C# and Python for building scalable, high‑performance, and production‑ready systems.Experience in working with Generative AI models and ML stacksExperience across the product lifecycle from ideation to shipping\n\nThis position will be open for a minimum of 5 days, with applications accepted on an ongoing basis until the position is filled.\n\nMicrosoft is an equal opportunity employer. All qualified applicants will receive consideration for employment without regard to age, ancestry, citizenship, color, family or medical care leave, gender identity or expression, genetic information, immigration status, marital status, medical condition, national origin, physical or mental disability, political affiliation, protected veteran or military status, race, ethnicity, religion, sex (including pregnancy), sexual orientation, or any other characteristic protected by applicable local laws, regulations and ordinances. If you need assistance with religious accommodations and/or a reasonable accommodation due to a disability during the application process, read more about requesting accommodations.", 'seniorityLevel': 'Not Applicable', 'employmentType': 'Full-time', 'jobFunction': 'Engineering and Information Technology', 'industries': 'Software Development', 'inputUrl': 'https://in.linkedin.com/jobs/search?keywords=AI%20Developer&amp;location=India&amp;geoId=102713980&amp;f_JT=F&amp;f_PP=105214831%2C105556991%2C103671728%2C106164952&amp;f_TPR=r86400&amp;position=1&amp;pageNum=0', 'salaryInsights': {}, 'applyMethod': 'OffsiteApply', 'expireAt': 1780835514000, 'postedAtTimestamp': 1775753369000, 'workplaceTypes': ['Hybrid'], 'workRemoteAllowed': False, 'standardizedTitle': 'Artificial Intelligence Engineer', 'country': 'IN', 'companyAddress': {'type': 'PostalAddress', 'streetAddress': '1 Microsoft Way', 'addressLocality': 'Redmond', 'addressRegion': 'Washington', 'postalCode': '98052', 'addressCountry': 'US'}, 'companyWebsite': 'https://news.microsoft.com/', 'companyDescription': "Every company has a mission. What's ours? To empower every person and every organization to achieve more. We believe technology can and should be a force for good and that meaningful innovation contributes to a brighter world in the future and today. Our culture doesn’t just encourage curiosity; it embraces it. Each day we make progress together by showing up as our authentic selves. We show up with a learn-it-all mentality. We show up cheering on others, knowing their success doesn't diminish our own. We show up every day open to learning our own biases, changing our behavior, and inviting in differences. Because impact matters. \n\nMicrosoft operates in 190 countries and is made up of approximately 228,000 passionate employees worldwide.", 'companyEmployeesCount': 228950}</t>
+  </si>
+  <si>
+    <t>4397666814</t>
+  </si>
+  <si>
+    <t>Data Scientist</t>
+  </si>
+  <si>
+    <t>Join our Team
+About this opportunity:
+Welcome to an exciting opportunity at Ericsson, where you'll be stepping into the role of a Data Scientist. As part of our team, you'll have the opportunity to develop unique machine learning solutions that address complex business issues. You'll employ scientific methods, processes, and systems to reveal valuable insights and pave the way for the future of applied analytics. Direct your prowess in machine learning towards formulating innovative AI/ML solutions that are consistent with Ericsson's architectural and coding standards.
+What you will do:
+ Implement technical requirements by analyzing and optimizing their needs while managing any constraints effectively. Build predictive models, recommendation engines, anomaly detection systems, statistical models, deep learning models, and other machine learning systems. Proficiency in machine learning concepts and programming languages such as Python, Pyspark, SQL, amongst others. Develop solutions using on-premise and cloud-based machine learning. Collaborate with business leaders and decision-making personnel to define success metrics and originate ML solutions that fit the bill. Mentor emerging data scientists and foster a community of machine learning enthusiasts within Ericsson.
+The skills you bring:
+ DevSecOps. Business Understanding. Artificial Intelligence Systems. Software Engineering. Data Management. Ericsson Business Intelligence and Analytics Competence. Open-Source Programming Languages. Data Preprocessing. Statistics. Cloud Development. Machine Learning Algorithms.
+Why join Ericsson?At Ericsson, you´ll have an outstanding opportunity. The chance to use your skills and imagination to push the boundaries of what´s possible. To build solutions never seen before to some of the world’s toughest problems. You´ll be challenged, but you won’t be alone. You´ll be joining a team of diverse innovators, all driven to go beyond the status quo to craft what comes next.
+What happens once you apply?Click Here to find all you need to know about what our typical hiring process looks like.Encouraging a diverse and inclusive organization is core to our values at Ericsson, that's why we champion it in everything we do. We truly believe that by collaborating with people with different experiences we drive innovation, which is essential for our future growth. We encourage people from all backgrounds to apply and realize their full potential as part of our Ericsson team. Ericsson is proud to be an Equal Opportunity Employer. learn more.
+Primary country and city: India (IN) || Noida
+Req ID: 783603</t>
+  </si>
+  <si>
+    <t>https://in.linkedin.com/jobs/view/data-scientist-at-ericsson-4397666814?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=bIMml1tJ9DZT9WT9Br2Hdg%3D%3D&amp;position=20&amp;pageNum=0</t>
+  </si>
+  <si>
+    <t>2026-04-10T04:37:43.000Z</t>
+  </si>
+  <si>
+    <t>{'id': '4397666814', 'trackingId': 'bIMml1tJ9DZT9WT9Br2Hdg==', 'refId': 'RPfRiYbtzNIwL3U59dKY8w==', 'link': 'https://in.linkedin.com/jobs/view/data-scientist-at-ericsson-4397666814?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=bIMml1tJ9DZT9WT9Br2Hdg%3D%3D&amp;position=20&amp;pageNum=0', 'title': 'Data Scientist', 'companyName': 'Ericsson', 'companyLinkedinUrl': 'https://se.linkedin.com/company/ericsson?trk=public_jobs_jserp-result_job-search-card-subtitle', 'companyLogo': 'https://media.licdn.com/dms/image/v2/D4D0BAQE4si5Pr9mLOw/company-logo_100_100/B4DZ1CtTDxJQAQ-/0/1774940664616/ericsson_logo?e=1777507200&amp;v=beta&amp;t=w5oGJZeTVEYjR88WNdAOJzRV1HbrFHY7QN-p2BCPuBA', 'location': 'Bengaluru, Karnataka, India', 'postedAt': '2026-04-10T04:37:43.000Z', 'benefits': ['Actively Hiring'], 'descriptionHtml': "&lt;strong&gt;Join our Team&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;strong&gt;About this opportunity:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Welcome to an exciting opportunity at Ericsson, where you'll be stepping into the role of a Data Scientist. As part of our team, you'll have the opportunity to develop unique machine learning solutions that address complex business issues. You'll employ scientific methods, processes, and systems to reveal valuable insights and pave the way for the future of applied analytics. Direct your prowess in machine learning towards formulating innovative AI/ML solutions that are consistent with Ericsson's architectural and coding standards.&lt;br&gt;&lt;br&gt;&lt;strong&gt;What you will do:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt; Implement technical requirements by analyzing and optimizing their needs while managing any constraints effectively.&lt;/li&gt;&lt;li&gt; Build predictive models, recommendation engines, anomaly detection systems, statistical models, deep learning models, and other machine learning systems.&lt;/li&gt;&lt;li&gt; Proficiency in machine learning concepts and programming languages such as Python, Pyspark, SQL, amongst others.&lt;/li&gt;&lt;li&gt; Develop solutions using on-premise and cloud-based machine learning.&lt;/li&gt;&lt;li&gt; Collaborate with business leaders and decision-making personnel to define success metrics and originate ML solutions that fit the bill.&lt;/li&gt;&lt;li&gt; Mentor emerging data scientists and foster a community of machine learning enthusiasts within Ericsson.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;The skills you bring:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt; DevSecOps.&lt;/li&gt;&lt;li&gt; Business Understanding.&lt;/li&gt;&lt;li&gt; Artificial Intelligence Systems.&lt;/li&gt;&lt;li&gt; Software Engineering.&lt;/li&gt;&lt;li&gt; Data Management.&lt;/li&gt;&lt;li&gt; Ericsson Business Intelligence and Analytics Competence.&lt;/li&gt;&lt;li&gt; Open-Source Programming Languages.&lt;/li&gt;&lt;li&gt; Data Preprocessing.&lt;/li&gt;&lt;li&gt; Statistics.&lt;/li&gt;&lt;li&gt; Cloud Development.&lt;/li&gt;&lt;li&gt; Machine Learning Algorithms.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Why join Ericsson?&lt;/strong&gt;At Ericsson, you´ll have an outstanding opportunity. The chance to use your skills and imagination to push the boundaries of what´s possible. To build solutions never seen before to some of the world’s toughest problems. You´ll be challenged, but you won’t be alone. You´ll be joining a team of diverse innovators, all driven to go beyond the status quo to craft what comes next.&lt;br&gt;&lt;br&gt;&lt;strong&gt;What happens once you apply?&lt;/strong&gt;Click Here to find all you need to know about what our typical hiring process looks like.Encouraging a diverse and inclusive organization is core to our values at Ericsson, that's why we champion it in everything we do. We truly believe that by collaborating with people with different experiences we drive innovation, which is essential for our future growth. We encourage people from all backgrounds to apply and realize their full potential as part of our Ericsson team. Ericsson is proud to be an Equal Opportunity Employer. learn more.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Primary country and city:&lt;/strong&gt; India (IN) || Noida&lt;br&gt;&lt;br&gt;&lt;strong&gt;Req ID:&lt;/strong&gt; 783603", 'applicantsCount': '179', 'applyUrl': 'https://jobs.ericsson.com/careers/job/563121775522143?domain=ericsson.com&amp;jobPipeline=LinkedIn', 'salary': '', 'descriptionText': "Join our Team\n\nAbout this opportunity:\n\nWelcome to an exciting opportunity at Ericsson, where you'll be stepping into the role of a Data Scientist. As part of our team, you'll have the opportunity to develop unique machine learning solutions that address complex business issues. You'll employ scientific methods, processes, and systems to reveal valuable insights and pave the way for the future of applied analytics. Direct your prowess in machine learning towards formulating innovative AI/ML solutions that are consistent with Ericsson's architectural and coding standards.\n\nWhat you will do:\n\n Implement technical requirements by analyzing and optimizing their needs while managing any constraints effectively. Build predictive models, recommendation engines, anomaly detection systems, statistical models, deep learning models, and other machine learning systems. Proficiency in machine learning concepts and programming languages such as Python, Pyspark, SQL, amongst others. Develop solutions using on-premise and cloud-based machine learning. Collaborate with business leaders and decision-making personnel to define success metrics and originate ML solutions that fit the bill. Mentor emerging data scientists and foster a community of machine learning enthusiasts within Ericsson.\n\nThe skills you bring:\n\n DevSecOps. Business Understanding. Artificial Intelligence Systems. Software Engineering. Data Management. Ericsson Business Intelligence and Analytics Competence. Open-Source Programming Languages. Data Preprocessing. Statistics. Cloud Development. Machine Learning Algorithms.\n\nWhy join Ericsson?At Ericsson, you´ll have an outstanding opportunity. The chance to use your skills and imagination to push the boundaries of what´s possible. To build solutions never seen before to some of the world’s toughest problems. You´ll be challenged, but you won’t be alone. You´ll be joining a team of diverse innovators, all driven to go beyond the status quo to craft what comes next.\n\nWhat happens once you apply?Click Here to find all you need to know about what our typical hiring process looks like.Encouraging a diverse and inclusive organization is core to our values at Ericsson, that's why we champion it in everything we do. We truly believe that by collaborating with people with different experiences we drive innovation, which is essential for our future growth. We encourage people from all backgrounds to apply and realize their full potential as part of our Ericsson team. Ericsson is proud to be an Equal Opportunity Employer. learn more.\n\nPrimary country and city: India (IN) || Noida\n\nReq ID: 783603", 'seniorityLevel': 'Not Applicable', 'employmentType': 'Full-time', 'jobFunction': 'Other', 'industries': 'Telecommunications', 'inputUrl': 'https://in.linkedin.com/jobs/search?keywords=AI%20Developer&amp;location=India&amp;geoId=102713980&amp;f_JT=F&amp;f_PP=105214831%2C105556991%2C103671728%2C106164952&amp;f_TPR=r86400&amp;position=1&amp;pageNum=0', 'salaryInsights': {}, 'applyMethod': 'OffsiteApply', 'expireAt': 1778387863000, 'postedAtTimestamp': 1775795863000, 'workplaceTypes': [], 'workRemoteAllowed': False, 'standardizedTitle': 'Data Scientist', 'country': 'IN', 'companyAddress': {'type': 'PostalAddress', 'streetAddress': 'Torshamnsgatan 21', 'addressLocality': 'Kista', 'addressRegion': 'Stockholm', 'addressCountry': 'SE'}, 'companyWebsite': 'http://www.ericsson.com', 'companySlogan': 'We’re leading the next wave of mobile with 5G, AI, cloud, and network APIs, creating an open network ecosystem.', 'companyDescription': 'The future of mobile isn’t on the horizon, it’s happening now. At Ericsson, we’re building the foundation for an open network ecosystem where industries, developers, and enterprises thrive.\n\nThe convergence of 5G, AI, cloud, and network APIs isn’t just a technological shift; it’s a transformation that is redefining industries and enhancing everyday life. Open, programmable networks are enabling real-time innovation and unlocking new business models across the globe.\n\nImagine a world where developers can dynamically access network capabilities on demand, where enterprises don’t just use connectivity but shape it. This isn’t a distant vision, it’s the ecosystem we’re creating today.\n\nCollaboration fuels everything we do. By working across industries, we’re designing a future where connectivity isn’t just seamless. It’s intelligent, programmable, and transformative.\n\nThe shift is happening. Are you part of it?', 'companyEmployeesCount': 107343}</t>
+  </si>
+  <si>
+    <t>4369656518</t>
+  </si>
+  <si>
+    <t>Senior Software Engineer, Machine Learning</t>
+  </si>
+  <si>
+    <t>Teamwork makes the stream work. Roku is changing how the world watches TVRoku is the #1 TV streaming platform in the U.S., Canada, and Mexico, and we've set our sights on powering every television in the world. Roku pioneered streaming to the TV. Our mission is to be the TV streaming platform that connects the entire TV ecosystem. We connect consumers to the content they love, enable content publishers to build and monetize large audiences, and provide advertisers unique capabilities to engage consumers.From your first day at Roku, you'll make a valuable - and valued - contribution. We're a fast-growing public company where no one is a bystander. We offer you the opportunity to delight millions of TV streamers around the world while gaining meaningful experience across a variety of disciplines.  
+About the team The Advertising Performance group focuses on performance for all participants in the Advertising ecosystem - Advertisers, Publishers and Roku. The systems and solutions span across different disciplines and technologies to perform realtime multi-objective optimization with distributed systems at large scale and low latencies. We use Machine Learning, Reinforcement Learning, AI, Control and Optimization Systems and Auction Dynamics to solve a large set of complex problems. At the core of this is our Machine Learning, Experimentation and Inference Platform that powers the entire landscape which we continuously evolve over time. About the role In this role you will work on building out a SOTA machine learning platform and apply various methodologies to solve a large variety of challenging problems in Advertising related to conversion modeling aligned with attribution methodologies/models, calibration, dynamic creative generation and optimization, forecasting and timeseries modeling, yield and margin optimization and Experimentation for A/B and multivariate testing. We’re looking for strong engineers well versed with modern large scale machine learning platforms with a solid grasp of core statistical techniques and deep experience in SOTA Deep Learning discriminative and generative models.   What you’ll be doing  Building and evolving a SOTA Machine Learning Platform from feature generation to realtime inferencing that can optimize and deploy complex models at large scale and low latencies. Building SOTA Deep learning discriminative models and build generative models to generate image and video ads geared towards optimizing performance. Stay at the forefront of advancements in related areas.  We’re excited if you have 
+ BS or higher in CS, ECE or a related field. 5+ years of experience in building out Machine Learning platforms or applying Deep Learning methodologies. Excellent communication and collaboration skills. Preferred Qualifications: MS or higher CS, ECE or a related field. Experience in the Advertising domain. Contributions to open-source ML projects.     Our Hybrid Work ApproachRoku fosters an inclusive and collaborative environment where teams work in the office Monday through Thursday. Fridays are flexible for remote work except for employees whose roles are required to be in the office five days a week or employees who are in offices with a five day in office policy. BenefitsRoku is committed to offering a diverse range of benefits as part of our compensation package to support our employees and their families. Our comprehensive benefits include global access to mental health and financial wellness support and resources. Local benefits include statutory and voluntary benefits which may include healthcare (medical, dental, and vision), life, accident, disability, commuter, and retirement options (401(k)/pension). Our employees can take time off work for vacation and other personal reasons to balance their evolving work and life needs. It's important to note that not every benefit is available in all locations or for every role. For details specific to your location, please consult with your recruiter. AccommodationsRoku welcomes applicants of all backgrounds and provides reasonable accommodations and adjustments in accordance with applicable law. If you require reasonable accommodation at any point in the hiring process, please direct your inquiries to EmployeeRelations@Roku.com. The Roku CultureRoku is a great place for people who want to work in a fast-paced environment where everyone is focused on the company's success rather than their own. We try to surround ourselves with people who are great at their jobs, who are easy to work with, and who keep their egos in check. We appreciate a sense of humor. We believe a fewer number of very talented folks can do more for less cost than a larger number of less talented teams. We're independent thinkers with big ideas who act boldly, move fast and accomplish extraordinary things through collaboration and trust. In short, at Roku you'll be part of a company that's changing how the world watches TV. We have a unique culture that we are proud of. We think of ourselves primarily as problem-solvers, which itself is a two-part idea. We come up with the solution, but the solution isn't real until it is built and delivered to the customer. That penchant for action gives us a pragmatic approach to innovation, one that has served us well since 2002. To learn more about Roku, our global footprint, and how we've grown, visit https://www.weareroku.com/factsheet.By providing your information, you acknowledge that you want Roku to contact you about job roles, that you have read Roku's Applicant Privacy Notice, and understand that Roku will use your information as described in that notice. If you do not wish to receive any communications from Roku regarding this role or similar roles in the future, you may unsubscribe at any time by emailing WorkforcePrivacy@Roku.com.</t>
+  </si>
+  <si>
+    <t>https://in.linkedin.com/jobs/view/senior-software-engineer-machine-learning-at-roku-4369656518?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=%2B4UOnEIl6Gx%2BbIn86BgTfw%3D%3D&amp;position=21&amp;pageNum=0</t>
+  </si>
+  <si>
+    <t>2026-04-10T09:03:14.000Z</t>
+  </si>
+  <si>
+    <t>{'id': '4369656518', 'trackingId': '+4UOnEIl6Gx+bIn86BgTfw==', 'refId': 'RPfRiYbtzNIwL3U59dKY8w==', 'link': 'https://in.linkedin.com/jobs/view/senior-software-engineer-machine-learning-at-roku-4369656518?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=%2B4UOnEIl6Gx%2BbIn86BgTfw%3D%3D&amp;position=21&amp;pageNum=0', 'title': 'Senior Software Engineer, Machine Learning', 'companyName': 'Roku', 'companyLinkedinUrl': 'https://www.linkedin.com/company/roku?trk=public_jobs_jserp-result_job-search-card-subtitle', 'companyLogo': 'https://media.licdn.com/dms/image/v2/D560BAQGwtnEFj0grWQ/company-logo_100_100/B56ZaxohrVH0AU-/0/1746736913380/roku_logo?e=1777507200&amp;v=beta&amp;t=w0LzCPsUFNpfLVolWH5wJ8M2YqoOlvGF_O1wxUy1ekg', 'location': 'Bengaluru, Karnataka, India', 'postedAt': '2026-04-10T09:03:14.000Z', 'benefits': ['Actively Hiring'], 'descriptionHtml': "Teamwork makes the stream work.&lt;p&gt;\xa0&lt;/p&gt;&lt;strong&gt;Roku is changing how the world watches TV&lt;/strong&gt;&lt;p&gt;Roku is the #1 TV streaming platform in the U.S., Canada, and Mexico, and we've set our sights on powering every television in the world. Roku pioneered streaming to the TV. Our mission is to be the TV streaming platform that connects the entire TV ecosystem. We connect consumers to the content they love, enable content publishers to build and monetize large audiences, and provide advertisers unique capabilities to engage consumers.&lt;/p&gt;&lt;p&gt;From your first day at Roku, you'll make a valuable - and valued - contribution. We're a fast-growing public company where no one is a bystander. We offer you the opportunity to delight millions of TV streamers around the world while gaining meaningful experience across a variety of disciplines.&lt;/p&gt;&lt;p&gt;\xa0&lt;/p&gt; &lt;strong&gt;&lt;span&gt;&lt;span&gt;&lt;br&gt;&lt;br&gt;About the team&lt;/span&gt;&lt;/span&gt;&lt;/strong&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;p&gt;&lt;span&gt;The Advertising Performance group focuses on performance for all participants in the Advertising ecosystem - Advertisers,\xa0Publishers\xa0and Roku. The systems and solutions span across different disciplines and technologies to perform\xa0realtime\xa0multi-objective\xa0optimization with distributed systems at large scale and low latencies. We use Machine Learning, Reinforcement Learning, AI, Control and Optimization\xa0Systems\xa0and Auction Dynamics to solve a large set of complex problems. At the core of this is our Machine Learning, Experimentation\xa0and Inference Platform that powers the entire landscape\xa0which we continuously evolve over time.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/p&gt;&lt;strong&gt;&lt;span&gt;&lt;span&gt;About the role&lt;/span&gt;&lt;/span&gt;&lt;/strong&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;p&gt;&lt;span&gt;In this role you will\xa0work on\xa0building out a SOTA machine learning platform and apply various methodologies\xa0to\xa0solve a\xa0large variety\xa0of challenging\xa0problems\xa0in\xa0Advertising\xa0related to conversion modeling\xa0aligned with attribution methodologies/models,\xa0calibration,\xa0dynamic creative generation and optimization,\xa0forecasting and timeseries modeling,\xa0yield and margin optimization\xa0and Experimentation\xa0for A/B and multivariate testing.&lt;/span&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;We’re\xa0looking for strong\xa0engineers well versed with modern large scale machine learning platforms with a solid\xa0grasp\xa0of core statistical techniques and\xa0deep experience in\xa0SOTA Deep Learning\xa0discriminative\xa0and generative models.&lt;/span&gt; &lt;span&gt;\xa0&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/p&gt;&lt;strong&gt;&lt;span&gt;&lt;span&gt;What\xa0&lt;/span&gt;&lt;span&gt;you’ll&lt;/span&gt;&lt;span&gt;\xa0be doing&lt;/span&gt;&lt;/span&gt;&lt;/strong&gt; &lt;span&gt;\xa0&lt;/span&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Building\xa0and evolving\xa0a SOTA Machine Learning Platform from feature generation to\xa0realtime\xa0inferencing\xa0that can\xa0optimize\xa0and deploy\xa0complex models at large scale and low latencies.&lt;/span&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Building\xa0SOTA Deep learning discriminative models and\xa0build\xa0generative models\xa0to generate image and video ads\xa0geared towards\xa0optimizing\xa0performance.&lt;/span&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Stay at the forefront of\xa0advancements in\xa0related areas.&lt;/span&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/p&gt;&lt;strong&gt;&lt;span&gt;&lt;span&gt;We’re&lt;/span&gt;&lt;span&gt;\xa0excited if you have&lt;/span&gt;&lt;/span&gt;&lt;/strong&gt;\xa0&lt;br&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;BS or higher\xa0in\xa0CS,\xa0ECE or a related field.&lt;/span&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;5+ years of experience in\xa0building out Machine Learning platforms or applying Deep\xa0Learning\xa0\xa0methodologies.&lt;/span&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Excellent communication and collaboration skills.&lt;/span&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;&lt;span&gt;Preferred Qualifications:&lt;/span&gt;&lt;/strong&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;MS or higher\xa0CS, ECE or\xa0a related\xa0field.&lt;/span&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Experience in the Advertising domain.&lt;/span&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Contributions to open-source ML projects.&lt;/span&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;\xa0&lt;/span&gt;&lt;/p&gt;&lt;p&gt;\xa0&lt;/p&gt; &lt;p&gt;\xa0&lt;/p&gt;&lt;strong&gt;Our Hybrid Work Approach&lt;/strong&gt;&lt;p&gt;Roku fosters an inclusive and collaborative environment where teams work in the office Monday through Thursday. Fridays are flexible for remote work except for employees whose roles are required to be in the office five days a week or employees who are in offices with a five day in office policy.&lt;/p&gt;&lt;p&gt;\xa0&lt;/p&gt;&lt;strong&gt;Benefits&lt;/strong&gt;&lt;p&gt;Roku is committed to offering a diverse range of benefits as part of our compensation package to support our employees and their families. Our comprehensive benefits include global access to mental health and financial wellness support and resources. Local benefits include statutory and voluntary benefits which may include healthcare (medical, dental, and vision), life, accident, disability, commuter, and retirement options (401(k)/pension). Our employees can take time off work for vacation and other personal reasons to balance their evolving work and life needs. It's important to note that not every benefit is available in all locations or for every role. For details specific to your location, please consult with your recruiter.&lt;/p&gt;&lt;p&gt;\xa0&lt;/p&gt;&lt;strong&gt;Accommodations&lt;/strong&gt;&lt;p&gt;Roku welcomes applicants of all backgrounds and provides reasonable accommodations and adjustments in accordance with applicable law. If you require reasonable accommodation at any point in the hiring process, please direct your inquiries to EmployeeRelations@Roku.com.&lt;/p&gt;&lt;p&gt;\xa0&lt;/p&gt;&lt;strong&gt;The Roku Culture&lt;/strong&gt;&lt;p&gt;Roku is a great place for people who want to work in a fast-paced environment where everyone is focused on the company's success rather than their own. We try to surround ourselves with people who are great at their jobs, who are easy to work with, and who keep their egos in check. We appreciate a sense of humor. We believe a fewer number of very talented folks can do more for less cost than a larger number of less talented teams. We're independent thinkers with big ideas who act boldly, move fast and accomplish extraordinary things through collaboration and trust. In short, at Roku you'll be part of a company that's changing how the world watches TV.\u202f&lt;/p&gt;&lt;p&gt;We have a unique culture that we are proud of. We think of ourselves primarily as problem-solvers, which itself is a two-part idea. We come up with the solution, but the solution isn't real until it is built and delivered to the customer. That penchant for action gives us a pragmatic approach to innovation, one that has served us well since 2002.\u202f&lt;/p&gt;&lt;p&gt;To learn more about Roku, our global footprint, and how we've grown, visit https://www.weareroku.com/factsheet.&lt;/p&gt;&lt;p&gt;By providing your information, you acknowledge that you want Roku to contact you about job roles, that you have read Roku's Applicant Privacy Notice, and understand that Roku will use your information as described in that notice. If you do not wish to receive any communications from Roku regarding this role or similar roles in the future, you may unsubscribe at any time by emailing WorkforcePrivacy@Roku.com.&lt;/p&gt;", 'applicantsCount': '105', 'applyUrl': 'https://grnh.se/3b3owttd1us?gh_src=7c8c68a71us&amp;source=LinkedIn', 'salary': '', 'descriptionText': "Teamwork makes the stream work. Roku is changing how the world watches TVRoku is the #1 TV streaming platform in the U.S., Canada, and Mexico, and we've set our sights on powering every television in the world. Roku pioneered streaming to the TV. Our mission is to be the TV streaming platform that connects the entire TV ecosystem. We connect consumers to the content they love, enable content publishers to build and monetize large audiences, and provide advertisers unique capabilities to engage consumers.From your first day at Roku, you'll make a valuable - and valued - contribution. We're a fast-growing public company where no one is a bystander. We offer you the opportunity to delight millions of TV streamers around the world while gaining meaningful experience across a variety of disciplines.  \n\nAbout the team The Advertising Performance group focuses on performance for all participants in the Advertising ecosystem - Advertisers, Publishers and Roku. The systems and solutions span across different disciplines and technologies to perform realtime multi-objective optimization with distributed systems at large scale and low latencies. We use Machine Learning, Reinforcement Learning, AI, Control and Optimization Systems and Auction Dynamics to solve a large set of complex problems. At the core of this is our Machine Learning, Experimentation and Inference Platform that powers the entire landscape which we continuously evolve over time. About the role In this role you will work on building out a SOTA machine learning platform and apply various methodologies to solve a large variety of challenging problems in Advertising related to conversion modeling aligned with attribution methodologies/models, calibration, dynamic creative generation and optimization, forecasting and timeseries modeling, yield and margin optimization and Experimentation for A/B and multivariate testing. We’re looking for strong engineers well versed with modern large scale machine learning platforms with a solid grasp of core statistical techniques and deep experience in SOTA Deep Learning discriminative and generative models.   What you’ll be doing  Building and evolving a SOTA Machine Learning Platform from feature generation to realtime inferencing that can optimize and deploy complex models at large scale and low latencies. Building SOTA Deep learning discriminative models and build generative models to generate image and video ads geared towards optimizing performance. Stay at the forefront of advancements in related areas.  We’re excited if you have \n BS or higher in CS, ECE or a related field. 5+ years of experience in building out Machine Learning platforms or applying Deep Learning methodologies. Excellent communication and collaboration skills. Preferred Qualifications: MS or higher CS, ECE or a related field. Experience in the Advertising domain. Contributions to open-source ML projects.     Our Hybrid Work ApproachRoku fosters an inclusive and collaborative environment where teams work in the office Monday through Thursday. Fridays are flexible for remote work except for employees whose roles are required to be in the office five days a week or employees who are in offices with a five day in office policy. BenefitsRoku is committed to offering a diverse range of benefits as part of our compensation package to support our employees and their families. Our comprehensive benefits include global access to mental health and financial wellness support and resources. Local benefits include statutory and voluntary benefits which may include healthcare (medical, dental, and vision), life, accident, disability, commuter, and retirement options (401(k)/pension). Our employees can take time off work for vacation and other personal reasons to balance their evolving work and life needs. It's important to note that not every benefit is available in all locations or for every role. For details specific to your location, please consult with your recruiter. AccommodationsRoku welcomes applicants of all backgrounds and provides reasonable accommodations and adjustments in accordance with applicable law. If you require reasonable accommodation at any point in the hiring process, please direct your inquiries to EmployeeRelations@Roku.com. The Roku CultureRoku is a great place for people who want to work in a fast-paced environment where everyone is focused on the company's success rather than their own. We try to surround ourselves with people who are great at their jobs, who are easy to work with, and who keep their egos in check. We appreciate a sense of humor. We believe a fewer number of very talented folks can do more for less cost than a larger number of less talented teams. We're independent thinkers with big ideas who act boldly, move fast and accomplish extraordinary things through collaboration and trust. In short, at Roku you'll be part of a company that's changing how the world watches TV.\u202fWe have a unique culture that we are proud of. We think of ourselves primarily as problem-solvers, which itself is a two-part idea. We come up with the solution, but the solution isn't real until it is built and delivered to the customer. That penchant for action gives us a pragmatic approach to innovation, one that has served us well since 2002.\u202fTo learn more about Roku, our global footprint, and how we've grown, visit https://www.weareroku.com/factsheet.By providing your information, you acknowledge that you want Roku to contact you about job roles, that you have read Roku's Applicant Privacy Notice, and understand that Roku will use your information as described in that notice. If you do not wish to receive any communications from Roku regarding this role or similar roles in the future, you may unsubscribe at any time by emailing WorkforcePrivacy@Roku.com.", 'seniorityLevel': 'Mid-Senior level', 'employmentType': 'Full-time', 'jobFunction': 'Engineering and Information Technology', 'industries': 'Software Development', 'inputUrl': 'https://in.linkedin.com/jobs/search?keywords=AI%20Developer&amp;location=India&amp;geoId=102713980&amp;f_JT=F&amp;f_PP=105214831%2C105556991%2C103671728%2C106164952&amp;f_TPR=r86400&amp;position=1&amp;pageNum=0', 'salaryInsights': {}, 'applyMethod': 'ComplexOnsiteApply', 'expireAt': 1780687838000, 'postedAtTimestamp': 1775811794000, 'workplaceTypes': ['Hybrid'], 'workRemoteAllowed': False, 'standardizedTitle': 'Senior Software Engineer', 'country': 'IN', 'companyAddress': {'type': 'PostalAddress', 'addressLocality': 'San Jose', 'addressRegion': 'California', 'addressCountry': 'US'}, 'companyWebsite': 'https://www.weareroku.com/', 'companySlogan': 'Amazing Individuals. Unstoppable Team.', 'companyDescription': "With the #1 platform for streaming television in the U.S., Roku wants to revolutionize the way the world watches TV. \n\nOur Roku-branded TVs, Roku TV models, Smart Home system, streaming players, audio equipment, and the purpose-built operating system that powers it all can turn any home into a home theater, with seamless integration of hardware and software. Our commitment to our users extends to our brand studio, which creates innovative Roku Originals exclusively for The Roku Channel, a free channel that reaches approximately 80 million households in the U.S. and Mexico.   \n\nJoin us and you'll have the chance to delight millions of TV streamers around the world while gaining meaningful experience across a variety of disciplines. Be a part of shaping the future of streaming at weareroku.com. ", 'companyEmployeesCount': 4286}</t>
+  </si>
+  <si>
+    <t>4397687383</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence (AI) Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Job Description: AI Engineer (RAG &amp; Agentic AI Specialist)
+Work Location: Mumbai
+Why would you like to join us?
+TransOrg Analytics specializes in Data Science, Data Engineering and Generative AI, providing advanced analytics solutions to industry leaders and Fortune 500 companies across India, US, APAC and the Middle East. We leverage data science to streamline, optimize, and accelerate our clients' businesses. Visit at www.transorg.ai to know more about us.
+Job ObjectiveTo build enterprise-grade AI solutions that leverage Retrieval-Augmented Generation (RAG), Agentic AI frameworks, and large language models (LLMs). The candidate will be responsible for end-to-end solutioning using modern tools and platforms, interacting with business teams, and driving innovation within the Microsoft and Azure ecosystem.
+Essential Job Tasks
+Build and deploy scalable AI solutions, from RAG systems to complex agent-based architectures using LangChain, CrewAI, AutoGen, or low code solutions like Copilot Studio, Azure AI Foundry.Leverage MCP, A2A, Microsoft Flows, and M365 Copilot for reasoning-based process automation.Collaborate with business to gather requirements and recommend best fit AI solutions.Work with the cloud infra team to set up secure, scalable AI systems on Azure.Ensure production-readiness and scalability of deployed AI solutions.
+Areas of Responsibility
+End-to-end ownership of AI product delivery.Integration of AI agents and retrieval mechanisms.Enabling adoption and training of AI practice across the organization.Design, develop, and maintain backend services and APIs to support AI/ML applications at scale.Productionize ML and deep learning models, ensuring efficiency, reliability, and low-latency inference.Build scalable microservices and REST/gRPC APIs for deploying AI solutions in enterprise environments.Optimize AI model serving using frameworks such as TensorRT, ONNX Runtime, Triton Inference Server, or FastAPI.Implement MLOps practices including model versioning, monitoring, and automated deployments.Collaborate with AI researchers, data scientists, and product managers to translate prototypes into production-ready systems.Ensure robustness, fault tolerance, and security in backend AI systems.Integrate AI services with enterprise data platforms, cloud systems, and third-party APIs.Contribute to architecture discussions, design reviews, and performance tuning.Mentor junior engineers and contribute to best practices in AI software engineering.
+Required Qualifications &amp; Work Experience
+2-5 years overall experience in AI/ML or related fields.2-3 years hands-on experience in RAG and agentic AI solutions.B.E./B.Tech or M.Sc./B.Sc. in Computer Science, Data Science, or related field.Generative AI certifications are an advantage.
+Technical Knowledge
+LangChain, CrewAI, AutoGen, Copilot Studio, Azure AI Foundry.Creation and deployment of APIs using FastAPI or similar frameworks.OpenAI, Hugging Face, GPT4 APIs.Azure cloud (preferred).Working knowledge of Databricks and Azure Synapse.Power Platform (Power Automate, M365 Copilot Chat).Agent workflow orchestration, prompt design, RAG architecture, vector databases.Strong proficiency in Python and backend frameworks (FastAPI).Expertise in Prompt engineering and working with various LLMs.Experience in productionizing AI/ML models with efficient inference pipelines.Hands-on experience with model deployment frameworks (Triton, TensorRT, TorchServe, ONNX Runtime).Knowledge of cloud platforms (Azure, GCP) and container technologies (Docker).Strong experience with microservices architecture, CI/CD pipelines, and monitoring tools (Prometheus, Grafana).Familiarity with databases (SQL/NoSQL) and scalable data storage solutions.Exposure to LLMs, SLMs, and GenAI model integration into backend systems is a plus.Understanding of security, authentication, and performance optimization in large-scale systems.Experience with version control (Git) and Agile development practices.
+Other:
+Excellent problem-solving skills and attention to detail.Strong written and verbal communication skills in English.Ability to work collaboratively in cross-functional teams.Passion for building reliable backend systems that bring AI models into real-world impact.
+</t>
+  </si>
+  <si>
+    <t>https://in.linkedin.com/jobs/view/artificial-intelligence-ai-engineer-at-transorg-analytics-4397687383?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=RgZOM9MIkG79qMJckonqqw%3D%3D&amp;position=19&amp;pageNum=0</t>
+  </si>
+  <si>
+    <t>2026-04-10T09:16:28.000Z</t>
+  </si>
+  <si>
+    <t>{'id': '4397687383', 'trackingId': 'RgZOM9MIkG79qMJckonqqw==', 'refId': 'RPfRiYbtzNIwL3U59dKY8w==', 'link': 'https://in.linkedin.com/jobs/view/artificial-intelligence-ai-engineer-at-transorg-analytics-4397687383?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=RgZOM9MIkG79qMJckonqqw%3D%3D&amp;position=19&amp;pageNum=0', 'title': 'Artificial Intelligence (AI) Engineer', 'companyName': 'TransOrg Analytics', 'companyLinkedinUrl': 'https://in.linkedin.com/company/transorg-solutions-&amp;-services?trk=public_jobs_jserp-result_job-search-card-subtitle', 'companyLogo': 'https://media.licdn.com/dms/image/v2/C510BAQECF0X93D4lwA/company-logo_100_100/company-logo_100_100/0/1630611038116/transorg_solutions__services_logo?e=1777507200&amp;v=beta&amp;t=ymPsb92APkzifA9GplF0EEB-foM3Atbe0n1aBoKeOKU', 'location': 'Mumbai, Maharashtra, India', 'postedAt': '2026-04-10T09:16:28.000Z', 'benefits': ['Actively Hiring'], 'descriptionHtml': "&lt;br&gt;&lt;p&gt;&lt;strong&gt;Job Description: AI Engineer (RAG &amp;amp; Agentic AI Specialist)&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Work Location: Mumbai&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Why would you like to join us?&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;TransOrg Analytics specializes in Data Science, Data Engineering and Generative AI, providing advanced analytics solutions to industry leaders and Fortune 500 companies across India, US, APAC and the Middle East. We leverage data science to streamline, optimize, and accelerate our clients' businesses. Visit at www.transorg.ai to know more about us.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Job Objective&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;To build enterprise-grade AI solutions that leverage Retrieval-Augmented Generation (RAG), Agentic AI frameworks, and large language models (LLMs). The candidate will be responsible for end-to-end solutioning using modern tools and platforms, interacting with business teams, and driving innovation within the Microsoft and Azure ecosystem.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Essential Job Tasks&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Build and deploy scalable AI solutions, from RAG systems to complex agent-based architectures using LangChain, CrewAI, AutoGen, or low code solutions like Copilot Studio, Azure AI Foundry.&lt;/li&gt;&lt;li&gt;Leverage MCP, A2A, Microsoft Flows, and M365 Copilot for reasoning-based process automation.&lt;/li&gt;&lt;li&gt;Collaborate with business to gather requirements and recommend best fit AI solutions.&lt;/li&gt;&lt;li&gt;Work with the cloud infra team to set up secure, scalable AI systems on Azure.&lt;/li&gt;&lt;li&gt;Ensure production-readiness and scalability of deployed AI solutions.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Areas of Responsibility&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;End-to-end ownership of AI product delivery.&lt;/li&gt;&lt;li&gt;Integration of AI agents and retrieval mechanisms.&lt;/li&gt;&lt;li&gt;Enabling adoption and training of AI practice across the organization.&lt;/li&gt;&lt;li&gt;Design, develop, and maintain&amp;nbsp;&lt;strong&gt;backend services and APIs&lt;/strong&gt;&amp;nbsp;to support AI/ML applications at scale.&lt;/li&gt;&lt;li&gt;Productionize ML and deep learning models, ensuring efficiency, reliability, and low-latency inference.&lt;/li&gt;&lt;li&gt;Build scalable&amp;nbsp;&lt;strong&gt;microservices and REST/gRPC APIs&lt;/strong&gt;&amp;nbsp;for deploying AI solutions in enterprise environments.&lt;/li&gt;&lt;li&gt;Optimize AI model serving using frameworks such as&amp;nbsp;&lt;strong&gt;TensorRT, ONNX Runtime, Triton Inference Server, or FastAPI&lt;/strong&gt;.&lt;/li&gt;&lt;li&gt;Implement MLOps practices including model versioning, monitoring, and automated deployments.&lt;/li&gt;&lt;li&gt;Collaborate with AI researchers, data scientists, and product managers to translate prototypes into production-ready systems.&lt;/li&gt;&lt;li&gt;Ensure robustness, fault tolerance, and security in backend AI systems.&lt;/li&gt;&lt;li&gt;Integrate AI services with enterprise data platforms, cloud systems, and third-party APIs.&lt;/li&gt;&lt;li&gt;Contribute to architecture discussions, design reviews, and performance tuning.&lt;/li&gt;&lt;li&gt;Mentor junior engineers and contribute to best practices in AI software engineering.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Required Qualifications &amp;amp; Work Experience&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;2-5 years overall experience in AI/ML or related fields.&lt;/li&gt;&lt;li&gt;2-3 years hands-on experience in RAG and agentic AI solutions.&lt;/li&gt;&lt;li&gt;B.E./B.Tech or M.Sc./B.Sc. in Computer Science, Data Science, or related field.&lt;/li&gt;&lt;li&gt;Generative AI certifications are an advantage.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Technical Knowledge&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;LangChain, CrewAI, AutoGen, Copilot Studio, Azure AI Foundry.&lt;/li&gt;&lt;li&gt;Creation and deployment of APIs using FastAPI or similar frameworks.&lt;/li&gt;&lt;li&gt;OpenAI, Hugging Face, GPT4 APIs.&lt;/li&gt;&lt;li&gt;Azure cloud (preferred).&lt;/li&gt;&lt;li&gt;Working knowledge of Databricks and Azure Synapse.&lt;/li&gt;&lt;li&gt;Power Platform (Power Automate, M365 Copilot Chat).&lt;/li&gt;&lt;li&gt;Agent workflow orchestration, prompt design, RAG architecture, vector databases.&lt;/li&gt;&lt;li&gt;Strong proficiency in&amp;nbsp;&lt;strong&gt;Python&lt;/strong&gt;&amp;nbsp;and backend frameworks (FastAPI).&lt;/li&gt;&lt;li&gt;Expertise in Prompt engineering and working with various LLMs&lt;strong&gt;.&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Experience in&amp;nbsp;&lt;strong&gt;productionizing AI/ML models&lt;/strong&gt;&amp;nbsp;with efficient inference pipelines.&lt;/li&gt;&lt;li&gt;Hands-on experience with&amp;nbsp;&lt;strong&gt;model deployment frameworks&lt;/strong&gt;&amp;nbsp;(Triton, TensorRT, TorchServe, ONNX Runtime).&lt;/li&gt;&lt;li&gt;Knowledge of&amp;nbsp;&lt;strong&gt;cloud platforms&lt;/strong&gt;&amp;nbsp;(Azure, GCP) and container technologies (&lt;strong&gt;Docker&lt;/strong&gt;).&lt;/li&gt;&lt;li&gt;Strong experience with&amp;nbsp;&lt;strong&gt;microservices architecture, CI/CD pipelines, and monitoring tools&lt;/strong&gt;&amp;nbsp;(Prometheus, Grafana).&lt;/li&gt;&lt;li&gt;Familiarity with&amp;nbsp;&lt;strong&gt;databases&lt;/strong&gt;&amp;nbsp;(SQL/NoSQL) and scalable data storage solutions.&lt;/li&gt;&lt;li&gt;Exposure to&amp;nbsp;&lt;strong&gt;LLMs, SLMs, and GenAI model integration&lt;/strong&gt;&amp;nbsp;into backend systems is a plus.&lt;/li&gt;&lt;li&gt;Understanding of security, authentication, and performance optimization in large-scale systems.&lt;/li&gt;&lt;li&gt;Experience with version control (Git) and Agile development practices.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Other:&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Excellent problem-solving skills and attention to detail.&lt;/li&gt;&lt;li&gt;Strong written and verbal communication skills in English.&lt;/li&gt;&lt;li&gt;Ability to work collaboratively in cross-functional teams.&lt;/li&gt;&lt;li&gt;Passion for building reliable backend systems that bring AI models into real-world impact.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;", 'applicantsCount': '34', 'salary': '', 'descriptionText': "\nJob Description: AI Engineer (RAG &amp; Agentic AI Specialist)\nWork Location: Mumbai\nWhy would you like to join us?\nTransOrg Analytics specializes in Data Science, Data Engineering and Generative AI, providing advanced analytics solutions to industry leaders and Fortune 500 companies across India, US, APAC and the Middle East. We leverage data science to streamline, optimize, and accelerate our clients' businesses. Visit at www.transorg.ai to know more about us.\nJob ObjectiveTo build enterprise-grade AI solutions that leverage Retrieval-Augmented Generation (RAG), Agentic AI frameworks, and large language models (LLMs). The candidate will be responsible for end-to-end solutioning using modern tools and platforms, interacting with business teams, and driving innovation within the Microsoft and Azure ecosystem.\nEssential Job Tasks\nBuild and deploy scalable AI solutions, from RAG systems to complex agent-based architectures using LangChain, CrewAI, AutoGen, or low code solutions like Copilot Studio, Azure AI Foundry.Leverage MCP, A2A, Microsoft Flows, and M365 Copilot for reasoning-based process automation.Collaborate with business to gather requirements and recommend best fit AI solutions.Work with the cloud infra team to set up secure, scalable AI systems on Azure.Ensure production-readiness and scalability of deployed AI solutions.\nAreas of Responsibility\nEnd-to-end ownership of AI product delivery.Integration of AI agents and retrieval mechanisms.Enabling adoption and training of AI practice across the organization.Design, develop, and maintain backend services and APIs to support AI/ML applications at scale.Productionize ML and deep learning models, ensuring efficiency, reliability, and low-latency inference.Build scalable microservices and REST/gRPC APIs for deploying AI solutions in enterprise environments.Optimize AI model serving using frameworks such as TensorRT, ONNX Runtime, Triton Inference Server, or FastAPI.Implement MLOps practices including model versioning, monitoring, and automated deployments.Collaborate with AI researchers, data scientists, and product managers to translate prototypes into production-ready systems.Ensure robustness, fault tolerance, and security in backend AI systems.Integrate AI services with enterprise data platforms, cloud systems, and third-party APIs.Contribute to architecture discussions, design reviews, and performance tuning.Mentor junior engineers and contribute to best practices in AI software engineering.\nRequired Qualifications &amp; Work Experience\n2-5 years overall experience in AI/ML or related fields.2-3 years hands-on experience in RAG and agentic AI solutions.B.E./B.Tech or M.Sc./B.Sc. in Computer Science, Data Science, or related field.Generative AI certifications are an advantage.\nTechnical Knowledge\nLangChain, CrewAI, AutoGen, Copilot Studio, Azure AI Foundry.Creation and deployment of APIs using FastAPI or similar frameworks.OpenAI, Hugging Face, GPT4 APIs.Azure cloud (preferred).Working knowledge of Databricks and Azure Synapse.Power Platform (Power Automate, M365 Copilot Chat).Agent workflow orchestration, prompt design, RAG architecture, vector databases.Strong proficiency in Python and backend frameworks (FastAPI).Expertise in Prompt engineering and working with various LLMs.Experience in productionizing AI/ML models with efficient inference pipelines.Hands-on experience with model deployment frameworks (Triton, TensorRT, TorchServe, ONNX Runtime).Knowledge of cloud platforms (Azure, GCP) and container technologies (Docker).Strong experience with microservices architecture, CI/CD pipelines, and monitoring tools (Prometheus, Grafana).Familiarity with databases (SQL/NoSQL) and scalable data storage solutions.Exposure to LLMs, SLMs, and GenAI model integration into backend systems is a plus.Understanding of security, authentication, and performance optimization in large-scale systems.Experience with version control (Git) and Agile development practices.\nOther:\nExcellent problem-solving skills and attention to detail.Strong written and verbal communication skills in English.Ability to work collaboratively in cross-functional teams.Passion for building reliable backend systems that bring AI models into real-world impact.\n", 'jobPosterName': 'Swati Verma', 'jobPosterTitle': 'Strategic HR leader | HR Business Partner | Driving People Strategy, Organizational Development &amp; Talent Transformation', 'jobPosterPhoto': 'https://media.licdn.com/dms/image/v2/D5603AQGlsmYEtyMMWg/profile-displayphoto-shrink_100_100/profile-displayphoto-shrink_100_100/0/1715251761545?e=1777507200&amp;v=beta&amp;t=MdBrTQVHxtvppGPIvZ-cT5_Onmqhq6SbmnVjcPgrAVE', 'jobPosterProfileUrl': 'https://in.linkedin.com/in/swativerma4', 'employmentType': 'Full-time', 'inputUrl': 'https://in.linkedin.com/jobs/search?keywords=AI%20Developer&amp;location=India&amp;geoId=102713980&amp;f_JT=F&amp;f_PP=105214831%2C105556991%2C103671728%2C106164952&amp;f_TPR=r86400&amp;position=1&amp;pageNum=0', 'salaryInsights': {}, 'applyMethod': 'SimpleOnsiteApply', 'expireAt': 1791364588000, 'postedAtTimestamp': 1775812588000, 'workplaceTypes': ['On-site'], 'workRemoteAllowed': False, 'standardizedTitle': 'Artificial Intelligence Engineer', 'country': 'IN', 'companyAddress': {'type': 'PostalAddress', 'streetAddress': '1st Floor, Phase- II, Plot No- 34, Institutional Area', 'addressLocality': 'Gurgaon', 'addressRegion': 'Haryana', 'postalCode': '122003', 'addressCountry': 'IN'}, 'companyWebsite': 'https://transorg.ai/', 'companySlogan': 'Leverages machine learning and artificial intelligence as a medium to drive business growth', 'companyDescription': 'TransOrg Analytics is pushing the boundaries of what is possible with AI and Advanced Analytics for its global enterprise and large corporate clients.\n\nAt TransOrg, we focus on delivering measurable impact at scale from enhancing customer engagement and marketing effectiveness to transforming risk management. Our solutions are built on a strong foundation of domain expertise, machine learning, cloud technologies, and our cutting-edge Agentic AI platform, TransOrgIQ.\n\nWith TransOrgIQ, client organizations are moving beyond traditional analytics to adopting intelligent, adaptive systems that drive real business value.\n\nLearn more about our vision and solutions at https://www.transorg.ai', 'companyEmployeesCount': 116}</t>
+  </si>
+  <si>
+    <t>4387195956</t>
+  </si>
+  <si>
+    <t>AI Data Scientist - Officer</t>
+  </si>
+  <si>
+    <t>We’re currently looking for a high caliber professional to join our team as an Officer, AI Data Scientist - Hybrid based in Bangalore, India. Being part of our team means that we’ll provide you with the resources to meet your unique needs, empower you to make healthy decision and manage your financial well-being to help plan for your future. For instance:
+Citi provides access to an array of learning and development resources to help broaden and deepen your skills and knowledge as your career progresses.We offer our employees resources and tools to volunteer in the communities in which they live and work. In 2019, Citi employee volunteers contributed more than 1 million volunteer hours around the world.
+Through this opportunity, you join the Citi Global Data Insights team within Marketing &amp; Content unit of our Client Division. The successful candidate will be a curious and critical thinker eager to solve a wide variety of analytical challenges, while communicating any output in simple terms; verbally, through visualizations, effective summary statistics, and external content.
+You will work with internal and external clients to execute on their bespoke projects and content generation by utilizing alternative datasets, different data platforms and data science techniques. Based in Bangalore, this role will appeal to a highly motivated individual looking to leverage their strong quantitative skillset in a highly visible and growing front-office department.
+In this role, you’re expected to: 
+You will help to drive the development and implementation of GenAI and Agentic AI tools for Marketing and Content departmentYou will be a visible data science expert, working closely with other team members across the globe to help with requests from external clients in interpreting their briefs and converting them into high quality actionable data science projects.You will support existing data analytics and data science projects, participate in investigating new project ideas, design a framework of a solution, evaluate its effort and feasibility and provide recommendations to management who will align against financial value.You will work on all stages of the data analysis cycle - collect, process and enrich data of different formats from multiple sources using a variety of technologies and platforms; load, manipulate data using free SQL writing; analyze the data using various analysis tools and visualize data.You will contribute, from an analytics and content perspective, towards external publications and work closely with Client Division and other LOB stakeholders on these publications.Help to improve the derived data assets available within the team, to effectively push a project from data curation to data analysis and execute on the agreed form of output and into production.Create a strong relationship with the different stakeholders of each project updating on the progress and consulting iteratively when necessary.Gather, validate, and analyze large complex information sets; understand the meaning of the data and how it applies to end users; identify and trouble-shoot / problem solve issues with data or results.
+Development Value:
+The role will give you exposure to world's largest asset management firms, hedge funds, sovereign wealth funds, other institutional and corporate clients. You will be exposed to the strategic plans and considerations of senior management. You will also work with proprietary datasets from other divisions across Citi franchise to provide unique insights to clients.
+As a successful candidate, you’d ideally have the following skills and exposure
+2-5 years’ experience of Agentic AI and Generative AI and toolsBSc or MSc degree with emphasis on one or more of the following: big data, data science, computer science, computer engineering, statistics, mathematics or equivalent quantitative discipline.Expertise in Data Science tools and machine learning techniques like Arima, regime-based models, VAR, error correction models, multivariate time series models, neural networks, decision trees, clustering and pattern recognitionProven experience with working on various databases including Big Data platforms. This includes data engineering, analysis and modeling.Strong knowledge and experience of statistical and data mining, machine learning and generative AIProgramming experience with Python, R, Java or other related toolsStrong working knowledge of SQL, ETL and BI toolsStrong analytical and project management skills, including a thorough understanding of how to interpret business requirements and provide data to help observe trends and identify anomalies.Financial industry knowledge; an understanding of, and keen interest in, investment management and financial markets highly desirableExperience in producing dynamic visualizations of complex data – a strong advantage
+This job description provides a high-level review of the types of work performed. Other job-related duties may be assigned as required.
+Working at Citi is far more than just a job. A career with us means joining a family of more than 230,000 dedicated people from around the globe. At Citi, you’ll have the opportunity to grow your career, give back to your community and make a real impact.
+------------------------------------------------------
+Job Family Group: 
+Decision Management
+------------------------------------------------------
+Job Family:
+Specialized Analytics (Data Science/Computational Statistics)
+------------------------------------------------------
+Time Type:
+Full time
+------------------------------------------------------
+Most Relevant Skills
+Please see the requirements listed above.
+------------------------------------------------------
+Other Relevant Skills
+For complementary skills, please see above and/or contact the recruiter.
+------------------------------------------------------
+Citi is an equal opportunity employer, and qualified candidates will receive consideration without regard to their race, color, religion, sex, sexual orientation, gender identity, national origin, disability, status as a protected veteran, or any other characteristic protected by law.
+If you are a person with a disability and need a reasonable accommodation to use our search tools and/or apply for a career opportunity review Accessibility at Citi.
+View Citi’s EEO Policy Statement and the Know Your Rights poster.</t>
+  </si>
+  <si>
+    <t>https://in.linkedin.com/jobs/view/ai-data-scientist-officer-at-citi-4387195956?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=i1RA6vATO79E1O3EG3sA9w%3D%3D&amp;position=18&amp;pageNum=0</t>
+  </si>
+  <si>
+    <t>2026-04-09T14:43:00.000Z</t>
+  </si>
+  <si>
+    <t>{'id': '4387195956', 'trackingId': 'i1RA6vATO79E1O3EG3sA9w==', 'refId': 'RPfRiYbtzNIwL3U59dKY8w==', 'link': 'https://in.linkedin.com/jobs/view/ai-data-scientist-officer-at-citi-4387195956?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=i1RA6vATO79E1O3EG3sA9w%3D%3D&amp;position=18&amp;pageNum=0', 'title': 'AI Data Scientist - Officer', 'companyName': 'Citi', 'companyLinkedinUrl': 'https://www.linkedin.com/company/citi?trk=public_jobs_jserp-result_job-search-card-subtitle', 'companyLogo': 'https://media.licdn.com/dms/image/v2/D4E0BAQFgF4xtqyXBcg/company-logo_100_100/company-logo_100_100/0/1719257286385/citi_logo?e=1777507200&amp;v=beta&amp;t=I4WsdK-vVb04LT1WSGDi0MMe7IfvNlF4rSyfaHKJeZ4', 'location': 'Bengaluru, Karnataka, India', 'postedAt': '2026-04-09T14:43:00.000Z', 'benefits': ['Actively Hiring'], 'descriptionHtml': "We’re currently looking for a high caliber professional to join our team as an &lt;strong&gt;Officer&lt;/strong&gt;&lt;strong&gt;, &lt;/strong&gt;&lt;strong&gt;AI Data Scientist -&lt;/strong&gt; &lt;strong&gt;Hybrid&lt;/strong&gt; based in Bangalore, India. Being part of our team means that we’ll provide you with the resources to meet your unique needs, empower you to make healthy decision and manage your financial well-being to help plan for your future. For instance:&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt;Citi provides access to an array of learning and development resources to help broaden and deepen your skills and knowledge as your career progresses.&lt;/li&gt;&lt;li&gt;We offer our employees resources and tools to volunteer in the communities in which they live and work. In 2019, Citi employee volunteers contributed more than 1 million volunteer hours around the world.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;Through this opportunity, you join the Citi Global Data Insights team within Marketing &amp;amp; Content unit of our Client Division. The successful candidate will be a curious and critical thinker eager to solve a wide variety of analytical challenges, while communicating any output in simple terms; verbally, through visualizations, effective summary statistics, and external content.&lt;br&gt;&lt;br&gt;You will work with internal and external clients to execute on their bespoke projects and content generation by utilizing alternative datasets, different data platforms and data science techniques. Based in Bangalore, this role will appeal to a highly motivated individual looking to leverage their strong quantitative skillset in a highly visible and growing front-office department.&lt;br&gt;&lt;br&gt;&lt;strong&gt;In this role, you’re expected to: &lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;You will help to drive the development and implementation of GenAI and Agentic AI tools for Marketing and Content department&lt;/li&gt;&lt;li&gt;You will be a visible data science expert, working closely with other team members across the globe to help with requests from external clients in interpreting their briefs and converting them into high quality actionable data science projects.&lt;/li&gt;&lt;li&gt;You will support existing data analytics and data science projects, participate in investigating new project ideas, design a framework of a solution, evaluate its effort and feasibility and provide recommendations to management who will align against financial value.&lt;/li&gt;&lt;li&gt;You will work on all stages of the data analysis cycle - collect, process and enrich data of different formats from multiple sources using a variety of technologies and platforms; load, manipulate data using free SQL writing; analyze the data using various analysis tools and visualize data.&lt;/li&gt;&lt;li&gt;You will contribute, from an analytics and content perspective, towards external publications and work closely with Client Division and other LOB stakeholders on these publications.&lt;/li&gt;&lt;li&gt;Help to improve the derived data assets available within the team, to effectively push a project from data curation to data analysis and execute on the agreed form of output and into production.&lt;/li&gt;&lt;li&gt;Create a strong relationship with the different stakeholders of each project updating on the progress and consulting iteratively when necessary.&lt;/li&gt;&lt;li&gt;Gather, validate, and analyze large complex information sets; understand the meaning of the data and how it applies to end users; identify and trouble-shoot / problem solve issues with data or results.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Development Value:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;The role will give you exposure to world's largest asset management firms, hedge funds, sovereign wealth funds, other institutional and corporate clients. You will be exposed to the strategic plans and considerations of senior management. You will also work with proprietary datasets from other divisions across Citi franchise to provide unique insights to clients.&lt;br&gt;&lt;br&gt;&lt;strong&gt;As a successful candidate, you’d ideally have the following skills and exposure&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;2-5 years’ experience of Agentic AI and Generative AI and tools&lt;/li&gt;&lt;li&gt;BSc or MSc degree with emphasis on one or more of the following: big data, data science, computer science, computer engineering, statistics, mathematics or equivalent quantitative discipline.&lt;/li&gt;&lt;li&gt;Expertise in Data Science tools and machine learning techniques like Arima, regime-based models, VAR, error correction models, multivariate time series models, neural networks, decision trees, clustering and pattern recognition&lt;/li&gt;&lt;li&gt;Proven experience with working on various databases including Big Data platforms. This includes data engineering, analysis and modeling.&lt;/li&gt;&lt;li&gt;Strong knowledge and experience of statistical and data mining, machine learning and generative AI&lt;/li&gt;&lt;li&gt;Programming experience with Python, R, Java or other related tools&lt;/li&gt;&lt;li&gt;Strong working knowledge of SQL, ETL and BI tools&lt;/li&gt;&lt;li&gt;Strong analytical and project management skills, including a thorough understanding of how to interpret business requirements and provide data to help observe trends and identify anomalies.&lt;/li&gt;&lt;li&gt;Financial industry knowledge; an understanding of, and keen interest in, investment management and financial markets highly desirable&lt;/li&gt;&lt;li&gt;Experience in producing dynamic visualizations of complex data – a strong advantage&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;This job description provides a high-level review of the types of work performed. Other job-related duties may be assigned as required.&lt;br&gt;&lt;br&gt;Working at Citi is far more than just a job. A career with us means joining a family of more than 230,000 dedicated people from around the globe. At Citi, you’ll have the opportunity to grow your career, give back to your community and make a real impact.&lt;br&gt;&lt;br&gt;------------------------------------------------------&lt;br&gt;&lt;br&gt;&lt;strong&gt;Job Family Group: &lt;br&gt;&lt;br&gt;&lt;/strong&gt;Decision Management&lt;br&gt;&lt;br&gt;------------------------------------------------------&lt;br&gt;&lt;br&gt;&lt;strong&gt;Job Family:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Specialized Analytics (Data Science/Computational Statistics)&lt;br&gt;&lt;br&gt;------------------------------------------------------&lt;br&gt;&lt;br&gt;&lt;strong&gt;Time Type:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Full time&lt;br&gt;&lt;br&gt;------------------------------------------------------&lt;br&gt;&lt;br&gt;&lt;strong&gt;Most Relevant Skills&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Please see the requirements listed above.&lt;br&gt;&lt;br&gt;------------------------------------------------------&lt;br&gt;&lt;br&gt;&lt;strong&gt;Other Relevant Skills&lt;br&gt;&lt;br&gt;&lt;/strong&gt;For complementary skills, please see above and/or contact the recruiter.&lt;br&gt;&lt;br&gt;------------------------------------------------------&lt;br&gt;&lt;br&gt;&lt;em&gt;Citi is an equal opportunity employer, and qualified candidates will receive consideration without regard to their race, color, religion, sex, sexual orientation, gender identity, national origin, disability, status as a protected veteran, or any other characteristic protected by law.&lt;br&gt;&lt;br&gt;&lt;/em&gt;&lt;em&gt;If you are a person with a disability and need a reasonable accommodation to use our search tools and/or apply for a career opportunity review &lt;/em&gt;&lt;em&gt;Accessibility at Citi.&lt;br&gt;&lt;br&gt;&lt;/em&gt;&lt;em&gt;View Citi’s EEO Policy Statement and the Know Your Rights poster.&lt;/em&gt;", 'applicantsCount': '200', 'applyUrl': 'https://ad.doubleclick.net/ddm/trackclk/N4789.466581LINKEDIN.COM/B31905581.393693070;dc_trk_aid=614356665;dc_trk_cid=216798306;dc_lat=;dc_rdid=;tag_for_child_directed_treatment=;tfua=;ltd=;dc_tdv=1;dc_transparent=1;?https://jobs.citi.com/job/-/-/287/89829600608?source=APPLICANT_SOURCE-3-354&amp;utm_medium=job_posting&amp;utm_campaign=apac_experienced&amp;utm_content=social_media&amp;utm_term=393693070&amp;ss=paid&amp;utm_source=linkedin', 'salary': '', 'descriptionText': "We’re currently looking for a high caliber professional to join our team as an Officer, AI Data Scientist - Hybrid based in Bangalore, India. Being part of our team means that we’ll provide you with the resources to meet your unique needs, empower you to make healthy decision and manage your financial well-being to help plan for your future. For instance:\n\nCiti provides access to an array of learning and development resources to help broaden and deepen your skills and knowledge as your career progresses.We offer our employees resources and tools to volunteer in the communities in which they live and work. In 2019, Citi employee volunteers contributed more than 1 million volunteer hours around the world.\n\nThrough this opportunity, you join the Citi Global Data Insights team within Marketing &amp; Content unit of our Client Division. The successful candidate will be a curious and critical thinker eager to solve a wide variety of analytical challenges, while communicating any output in simple terms; verbally, through visualizations, effective summary statistics, and external content.\n\nYou will work with internal and external clients to execute on their bespoke projects and content generation by utilizing alternative datasets, different data platforms and data science techniques. Based in Bangalore, this role will appeal to a highly motivated individual looking to leverage their strong quantitative skillset in a highly visible and growing front-office department.\n\nIn this role, you’re expected to: \n\nYou will help to drive the development and implementation of GenAI and Agentic AI tools for Marketing and Content departmentYou will be a visible data science expert, working closely with other team members across the globe to help with requests from external clients in interpreting their briefs and converting them into high quality actionable data science projects.You will support existing data analytics and data science projects, participate in investigating new project ideas, design a framework of a solution, evaluate its effort and feasibility and provide recommendations to management who will align against financial value.You will work on all stages of the data analysis cycle - collect, process and enrich data of different formats from multiple sources using a variety of technologies and platforms; load, manipulate data using free SQL writing; analyze the data using various analysis tools and visualize data.You will contribute, from an analytics and content perspective, towards external publications and work closely with Client Division and other LOB stakeholders on these publications.Help to improve the derived data assets available within the team, to effectively push a project from data curation to data analysis and execute on the agreed form of output and into production.Create a strong relationship with the different stakeholders of each project updating on the progress and consulting iteratively when necessary.Gather, validate, and analyze large complex information sets; understand the meaning of the data and how it applies to end users; identify and trouble-shoot / problem solve issues with data or results.\n\nDevelopment Value:\n\nThe role will give you exposure to world's largest asset management firms, hedge funds, sovereign wealth funds, other institutional and corporate clients. You will be exposed to the strategic plans and considerations of senior management. You will also work with proprietary datasets from other divisions across Citi franchise to provide unique insights to clients.\n\nAs a successful candidate, you’d ideally have the following skills and exposure\n\n2-5 years’ experience of Agentic AI and Generative AI and toolsBSc or MSc degree with emphasis on one or more of the following: big data, data science, computer science, computer engineering, statistics, mathematics or equivalent quantitative discipline.Expertise in Data Science tools and machine learning techniques like Arima, regime-based models, VAR, error correction models, multivariate time series models, neural networks, decision trees, clustering and pattern recognitionProven experience with working on various databases including Big Data platforms. This includes data engineering, analysis and modeling.Strong knowledge and experience of statistical and data mining, machine learning and generative AIProgramming experience with Python, R, Java or other related toolsStrong working knowledge of SQL, ETL and BI toolsStrong analytical and project management skills, including a thorough understanding of how to interpret business requirements and provide data to help observe trends and identify anomalies.Financial industry knowledge; an understanding of, and keen interest in, investment management and financial markets highly desirableExperience in producing dynamic visualizations of complex data – a strong advantage\n\nThis job description provides a high-level review of the types of work performed. Other job-related duties may be assigned as required.\n\nWorking at Citi is far more than just a job. A career with us means joining a family of more than 230,000 dedicated people from around the globe. At Citi, you’ll have the opportunity to grow your career, give back to your community and make a real impact.\n\n------------------------------------------------------\n\nJob Family Group: \n\nDecision Management\n\n------------------------------------------------------\n\nJob Family:\n\nSpecialized Analytics (Data Science/Computational Statistics)\n\n------------------------------------------------------\n\nTime Type:\n\nFull time\n\n------------------------------------------------------\n\nMost Relevant Skills\n\nPlease see the requirements listed above.\n\n------------------------------------------------------\n\nOther Relevant Skills\n\nFor complementary skills, please see above and/or contact the recruiter.\n\n------------------------------------------------------\n\nCiti is an equal opportunity employer, and qualified candidates will receive consideration without regard to their race, color, religion, sex, sexual orientation, gender identity, national origin, disability, status as a protected veteran, or any other characteristic protected by law.\n\nIf you are a person with a disability and need a reasonable accommodation to use our search tools and/or apply for a career opportunity review Accessibility at Citi.\n\nView Citi’s EEO Policy Statement and the Know Your Rights poster.", 'seniorityLevel': 'Not Applicable', 'employmentType': 'Full-time', 'jobFunction': 'Engineering and Information Technology', 'industries': 'Banking, Financial Services, and Investment Banking', 'inputUrl': 'https://in.linkedin.com/jobs/search?keywords=AI%20Developer&amp;location=India&amp;geoId=102713980&amp;f_JT=F&amp;f_PP=105214831%2C105556991%2C103671728%2C106164952&amp;f_TPR=r86400&amp;position=1&amp;pageNum=0', 'salaryInsights': {}, 'applyMethod': 'OffsiteApply', 'expireAt': 1779072604000, 'postedAtTimestamp': 1775745780000, 'workplaceTypes': ['On-site'], 'workRemoteAllowed': False, 'standardizedTitle': 'Data Scientist', 'country': 'IN', 'companyAddress': {'type': 'PostalAddress', 'streetAddress': '388 Greenwich Street', 'addressLocality': 'New York', 'addressRegion': 'New York', 'postalCode': '10013', 'addressCountry': 'US'}, 'companyWebsite': 'http://www.citigroup.com', 'companyDescription': "Citi's mission is to serve as a trusted partner to our clients by responsibly providing financial services that enable growth and economic progress. Our core activities are safeguarding assets, lending money, making payments and accessing the capital markets on behalf of our clients. We have over 200 years of experience helping our clients meet the world's toughest challenges and embrace its greatest opportunities. We are Citi, the global bank – an institution connecting millions of people across hundreds of countries and cities.\n\nFor information on Citi’s commitment to privacy, visit on.citi/privacy.", 'companyEmployeesCount': 186220}</t>
+  </si>
+  <si>
+    <t>4398827484</t>
+  </si>
+  <si>
+    <t>ML Engineer-Advanced Analytics</t>
+  </si>
+  <si>
+    <t>Introduction
+A career in IBM Consulting is built on long-term client relationships and close collaboration worldwide. You’ll work with leading companies across industries, helping them shape their hybrid cloud and AI journeys. With support from our strategic partners, robust IBM technology, and Red Hat, you’ll have the tools to drive meaningful change and accelerate client impact. At IBM Consulting, curiosity fuels success. You’ll be encouraged to challenge the norm, explore new ideas, and create innovative solutions that deliver real results. Our culture of growth and empathy focuses on your long-term career development while valuing your unique skills and experiences.
+Your Role And Responsibilities
+ Lead IBM into the future by translating system requirements into the design and development of customized systems in an agile environment. The success of IBM is in your hands as you transform vital business needs into code and drive innovation. Your work will power IBM and its clients globally, collaborating and integrating code into enterprise systems. You will have access to the latest education, tools and technology, and a limitless career path with the world’s technology leader
+Preferred Education
+Master's Degree
+Required Technical And Professional Expertise
+ Develop and deploy models using CML workspaces, Build CI/CD pipelines for ML lifecycle Integrate with governance and monitoring tools,Enable secure model serving via REST APIs
+Preferred Technical And Professional Experience
+ Model governance, lineage, and versioning API exposure for real-time inference</t>
+  </si>
+  <si>
+    <t>https://in.linkedin.com/jobs/view/ml-engineer-advanced-analytics-at-ibm-4398827484?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=e2T%2BYkwaSXN4XNYt%2BEScVQ%3D%3D&amp;position=17&amp;pageNum=0</t>
+  </si>
+  <si>
+    <t>2026-04-09T14:45:29.000Z</t>
+  </si>
+  <si>
+    <t>{'id': '4398827484', 'trackingId': 'e2T+YkwaSXN4XNYt+EScVQ==', 'refId': 'RPfRiYbtzNIwL3U59dKY8w==', 'link': 'https://in.linkedin.com/jobs/view/ml-engineer-advanced-analytics-at-ibm-4398827484?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=e2T%2BYkwaSXN4XNYt%2BEScVQ%3D%3D&amp;position=17&amp;pageNum=0', 'title': 'ML Engineer-Advanced Analytics', 'companyName': 'IBM', 'companyLinkedinUrl': 'https://www.linkedin.com/company/ibm?trk=public_jobs_jserp-result_job-search-card-subtitle', 'companyLogo': 'https://media.licdn.com/dms/image/v2/D560BAQGiz5ecgpCtkA/company-logo_100_100/company-logo_100_100/0/1688684715866/ibm_logo?e=1777507200&amp;v=beta&amp;t=TfktOX6EKpN2wP_S-85vs9vxXtj97AwM3Yeoic7klsA', 'location': 'Bengaluru, Karnataka, India', 'postedAt': '2026-04-09T14:45:29.000Z', 'benefits': ['Actively Hiring'], 'descriptionHtml': "&lt;strong&gt;Introduction&lt;br&gt;&lt;br&gt;&lt;/strong&gt;A career in IBM Consulting is built on long-term client relationships and close collaboration worldwide. You’ll work with leading companies across industries, helping them shape their hybrid cloud and AI journeys. With support from our strategic partners, robust IBM technology, and Red Hat, you’ll have the tools to drive meaningful change and accelerate client impact. At IBM Consulting, curiosity fuels success. You’ll be encouraged to challenge the norm, explore new ideas, and create innovative solutions that deliver real results. Our culture of growth and empathy focuses on your long-term career development while valuing your unique skills and experiences.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Your Role And Responsibilities&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt; Lead IBM into the future by translating system requirements into the design and development of customized systems in an agile environment. The success of IBM is in your hands as you transform vital business needs into code and drive innovation.&lt;/li&gt;&lt;li&gt; Your work will power IBM and its clients globally, collaborating and integrating code into enterprise systems. You will have access to the latest education, tools and technology, and a limitless career path with the world’s technology leader&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Preferred Education&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Master's Degree&lt;br&gt;&lt;br&gt;&lt;strong&gt;Required Technical And Professional Expertise&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt; Develop and deploy models using CML workspaces, Build CI/CD pipelines for ML lifecycle&lt;/li&gt;&lt;li&gt; Integrate with governance and monitoring tools,Enable secure model serving via REST APIs&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Preferred Technical And Professional Experience&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt; Model governance, lineage, and versioning&lt;/li&gt;&lt;li&gt; API exposure for real-time inference&lt;/li&gt;&lt;/ul&gt;", 'applicantsCount': '27', 'applyUrl': 'https://ibmglobal.avature.net/en_US/careers/JobDetail?jobId=83707&amp;source=SN_LinkedIn', 'salary': '', 'descriptionText': "Introduction\n\nA career in IBM Consulting is built on long-term client relationships and close collaboration worldwide. You’ll work with leading companies across industries, helping them shape their hybrid cloud and AI journeys. With support from our strategic partners, robust IBM technology, and Red Hat, you’ll have the tools to drive meaningful change and accelerate client impact. At IBM Consulting, curiosity fuels success. You’ll be encouraged to challenge the norm, explore new ideas, and create innovative solutions that deliver real results. Our culture of growth and empathy focuses on your long-term career development while valuing your unique skills and experiences.\n\nYour Role And Responsibilities\n\n Lead IBM into the future by translating system requirements into the design and development of customized systems in an agile environment. The success of IBM is in your hands as you transform vital business needs into code and drive innovation. Your work will power IBM and its clients globally, collaborating and integrating code into enterprise systems. You will have access to the latest education, tools and technology, and a limitless career path with the world’s technology leader\n\nPreferred Education\n\nMaster's Degree\n\nRequired Technical And Professional Expertise\n\n Develop and deploy models using CML workspaces, Build CI/CD pipelines for ML lifecycle Integrate with governance and monitoring tools,Enable secure model serving via REST APIs\n\nPreferred Technical And Professional Experience\n\n Model governance, lineage, and versioning API exposure for real-time inference", 'seniorityLevel': 'Mid-Senior level', 'employmentType': 'Full-time', 'jobFunction': 'Engineering and Information Technology', 'industries': 'IT Services and IT Consulting', 'inputUrl': 'https://in.linkedin.com/jobs/search?keywords=AI%20Developer&amp;location=India&amp;geoId=102713980&amp;f_JT=F&amp;f_PP=105214831%2C105556991%2C103671728%2C106164952&amp;f_TPR=r86400&amp;position=1&amp;pageNum=0', 'salaryInsights': {}, 'applyMethod': 'OffsiteApply', 'expireAt': 1778337929000, 'postedAtTimestamp': 1775745929000, 'workplaceTypes': ['Hybrid'], 'workRemoteAllowed': False, 'standardizedTitle': 'Machine Learning Engineer', 'country': 'IN', 'companyAddress': {'type': 'PostalAddress', 'streetAddress': 'International Business Machines Corp.', 'addressLocality': 'Armonk, New York', 'addressRegion': 'NY', 'postalCode': '10504', 'addressCountry': 'US'}, 'companyWebsite': 'http://www.ibm.com', 'companyDescription': 'At IBM, we do more than work. We create. We create as technologists, developers, and engineers. We create with our partners. We create with our competitors. If you\'re searching for ways to make the world work better through technology and infrastructure, software and consulting, then we want to work with you.\n\nWe\'re here to help every creator turn their "what if" into what is. Let\'s create something that will change everything.', 'companyEmployeesCount': 329219}</t>
+  </si>
+  <si>
+    <t>4397268784</t>
+  </si>
+  <si>
+    <t>Full Stack Agentic AI Engineer</t>
+  </si>
+  <si>
+    <t>Line of Service: Advisory – Data, Analytics &amp; AISpecialization: Agentic AI, Full Stack DevelopmentManagement Level: Senior AssociateExperience: 6–8 YearsLocation: Mumbai(Hybrid)
+Job Description &amp; SummaryA career within PwC’s Data, Analytics &amp; AI practice provides opportunities to help organisations unlock enterprise value using advanced analytics, cloud platforms, and intelligent AI systems. We combine cutting-edge Agentic AI, Full Stack Engineering, and Cloud technologies to build scalable, secure, and innovative solutions that drive real business outcomes.As a Senior Associate – Full Stack Agentic AI Engineer, you will design, build, and deploy end‑to‑end AI‑powered applications by integrating large language models (LLMs), agentic workflows, APIs, and modern front-end frameworks. You will work closely with data scientists, architects, and business stakeholders to deliver intelligent, production‑ready AI solutions at scale.
+Why PwCAt PwC, you’ll be part of a global community of problem solvers who lead with trust and deliver distinctive value. Our purpose‑led culture, combined with technology and innovation, empowers you to make a meaningful impact while continuously growing your skills.PwC is an equal opportunity employer. We promote an inclusive workplace with zero tolerance for discrimination or harassment, enabling everyone to bring their authentic selves to work and thrive professionally and personally.
+About the RoleWe are looking for a hands-on Full Stack Agentic AI Engineer with strong expertise in Python, cloud platforms, AI/ML, and front-end development. The ideal candidate is passionate about building intelligent, user‑centric applications, implementing agent-based AI systems, and operating AI solutions responsibly at enterprise scale.Key ResponsibilitiesDesign, develop, and maintain end‑to‑end full stack AI applications using Python-based back-end frameworks (FastAPI / Flask / Django) and modern front-end frameworks (Angular / React, TypeScript, HTML5, CSS)Build and integrate Agentic AI systems, LLMs, and generative AI models into enterprise applicationsDevelop and expose RESTful APIs to support AI-driven workflows and system integrationDeploy and manage AI applications on cloud platforms (Azure / AWS), ensuring scalability, security, and performanceImplement MLOps / LLMOps practices including model versioning, monitoring, evaluation, and retrainingManage data pipelines required for AI/ML workloads and inferenceEnsure adherence to data privacy, security, governance, and compliance standardsOptimize system performance, reliability, and cost efficiency across AI and application layersCollaborate with data scientists, architects, product owners, and business stakeholders to translate requirements into technical solutionsStay current with advancements in Agentic AI, Generative AI, and full stack technologies, and contribute to innovation initiatives
+Mandatory Skillsets6+ years of experience in Full Stack Development and AI/ML solution deliveryStrong expertise in Python and back-end frameworks (FastAPI, Flask, Django)Experience building and integrating LLMs, Generative AI, and Agentic AI workflowsSolid knowledge of REST APIs, microservices architecture, and system integrationHands-on experience with cloud platforms (Azure/AWS), including AI and data servicesExperience with containerization and DevOps practices (Docker, CI/CD pipelines)Proficiency in front-end development using Angular or React, TypeScript, HTML5, and CSSStrong understanding of software engineering best practices, secure coding, testing, and performance optimizationExcellent analytical, problem-solving, and communication skills
+Preferred SkillsetsExperience with MLOps / LLMOps frameworks and toolsExposure to Databricks, ML pipelines, or AI orchestration frameworksKnowledge of classical ML techniques, forecasting, or time-series analysisFamiliarity with event-driven architectures and messaging systemsCloud or AI certifications (Azure AI Engineer, Azure Solutions Architect, AWS ML, etc.)
+QualificationsBachelor’s or Master’s degree in Computer Science, Engineering, or a related fieldAbility to work effectively in agile, cross‑functional, global teams</t>
+  </si>
+  <si>
+    <t>https://in.linkedin.com/jobs/view/full-stack-agentic-ai-engineer-at-pwc-india-4397268784?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=sa1%2BlGsDMAiFvZhtWbZ1Wg%3D%3D&amp;position=14&amp;pageNum=0</t>
+  </si>
+  <si>
+    <t>2026-04-09T14:21:40.000Z</t>
+  </si>
+  <si>
+    <t>{'id': '4397268784', 'trackingId': 'sa1+lGsDMAiFvZhtWbZ1Wg==', 'refId': 'RPfRiYbtzNIwL3U59dKY8w==', 'link': 'https://in.linkedin.com/jobs/view/full-stack-agentic-ai-engineer-at-pwc-india-4397268784?refId=RPfRiYbtzNIwL3U59dKY8w%3D%3D&amp;trackingId=sa1%2BlGsDMAiFvZhtWbZ1Wg%3D%3D&amp;position=14&amp;pageNum=0', 'title': 'Full Stack Agentic AI Engineer', 'companyName': 'PwC India', 'companyLinkedinUrl': 'https://in.linkedin.com/company/pwc-india?trk=public_jobs_jserp-result_job-search-card-subtitle', 'companyLogo': 'https://media.licdn.com/dms/image/v2/D4D0BAQHftNJPUMdOaw/company-logo_100_100/B4DZaB7vDpG8AQ-/0/1745936642766/pwc_india_logo?e=1777507200&amp;v=beta&amp;t=NLgGZQLtNq77hcUJhk7Nqfl-ylu9LrsarpBIozf-F3s', 'location': 'Mumbai, Maharashtra, India', 'postedAt': '2026-04-09T14:21:40.000Z', 'benefits': ['Actively Hiring'], 'descriptionHtml': '&lt;p&gt;&lt;strong&gt;Line of Service:&lt;/strong&gt; Advisory – Data, Analytics &amp;amp; AI&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Specialization:&lt;/strong&gt; Agentic AI, Full Stack Development&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Management Level:&lt;/strong&gt; Senior Associate&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Experience:&lt;/strong&gt; 6–8 Years&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Location:&lt;/strong&gt; Mumbai(Hybrid)&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Job Description &amp;amp; Summary&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A career within PwC’s &lt;strong&gt;Data, Analytics &amp;amp; AI&lt;/strong&gt; practice provides opportunities to help organisations unlock enterprise value using advanced analytics, cloud platforms, and intelligent AI systems. We combine cutting-edge &lt;strong&gt;Agentic AI, Full Stack Engineering, and Cloud technologies&lt;/strong&gt; to build scalable, secure, and innovative solutions that drive real business outcomes.&lt;/p&gt;&lt;p&gt;As a &lt;strong&gt;Senior Associate – Full Stack Agentic AI Engineer&lt;/strong&gt;, you will design, build, and deploy end‑to‑end AI‑powered applications by integrating &lt;strong&gt;large language models (LLMs), agentic workflows, APIs, and modern front-end frameworks&lt;/strong&gt;. You will work closely with data scientists, architects, and business stakeholders to deliver intelligent, production‑ready AI solutions at scale.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Why PwC&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;At PwC, you’ll be part of a global community of problem solvers who lead with trust and deliver distinctive value. Our purpose‑led culture, combined with technology and innovation, empowers you to make a meaningful impact while continuously growing your skills.&lt;/p&gt;&lt;p&gt;PwC is an equal opportunity employer. We promote an inclusive workplace with &lt;strong&gt;zero tolerance for discrimination or harassment&lt;/strong&gt;, enabling everyone to bring their authentic selves to work and thrive professionally and personally.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;About the Role&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We are looking for a &lt;strong&gt;hands-on Full Stack Agentic AI Engineer&lt;/strong&gt; with strong expertise in &lt;strong&gt;Python, cloud platforms, AI/ML, and front-end development&lt;/strong&gt;. The ideal candidate is passionate about building intelligent, user‑centric applications, implementing &lt;strong&gt;agent-based AI systems&lt;/strong&gt;, and operating AI solutions responsibly at enterprise scale.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Key Responsibilities&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Design, develop, and maintain &lt;strong&gt;end‑to‑end full stack AI applications&lt;/strong&gt; using Python-based back-end frameworks (FastAPI / Flask / Django) and modern front-end frameworks (Angular / React, TypeScript, HTML5, CSS)&lt;/li&gt;&lt;li&gt;Build and integrate &lt;strong&gt;Agentic AI systems&lt;/strong&gt;, LLMs, and generative AI models into enterprise applications&lt;/li&gt;&lt;li&gt;Develop and expose &lt;strong&gt;RESTful APIs&lt;/strong&gt; to support AI-driven workflows and system integration&lt;/li&gt;&lt;li&gt;Deploy and manage AI applications on cloud platforms (Azure / AWS), ensuring scalability, security, and performance&lt;/li&gt;&lt;li&gt;Implement &lt;strong&gt;MLOps / LLMOps&lt;/strong&gt; practices including model versioning, monitoring, evaluation, and retraining&lt;/li&gt;&lt;li&gt;Manage data pipelines required for AI/ML workloads and inference&lt;/li&gt;&lt;li&gt;Ensure adherence to &lt;strong&gt;data privacy, security, governance, and compliance&lt;/strong&gt; standards&lt;/li&gt;&lt;li&gt;Optimize system performance, reliability, and cost efficiency across AI and application layers&lt;/li&gt;&lt;li&gt;Collaborate with data scientists, architects, product owners, and business stakeholders to translate requirements into technical solutions&lt;/li&gt;&lt;li&gt;Stay current with advancements in &lt;strong&gt;Agentic AI, Generative AI, and full stack technologies&lt;/strong&gt;, and contribute to innovation initiatives&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Mandatory Skillsets&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;6+ years of experience in &lt;strong&gt;Full Stack Development and AI/ML solution delivery&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Strong expertise in &lt;strong&gt;Python&lt;/strong&gt; and back-end frameworks (FastAPI, Flask, Django)&lt;/li&gt;&lt;li&gt;Experience building and integrating &lt;strong&gt;LLMs, Generative AI, and Agentic AI workflows&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Solid knowledge of &lt;strong&gt;REST APIs&lt;/strong&gt;, microservices architecture, and system integration&lt;/li&gt;&lt;li&gt;Hands-on experience with &lt;strong&gt;cloud platforms&lt;/strong&gt; (Azure/AWS), including AI and data services&lt;/li&gt;&lt;li&gt;Experience with &lt;strong&gt;containerization and DevOps&lt;/strong&gt; practices (Docker, CI/CD pipelines)&lt;/li&gt;&lt;li&gt;Proficiency in &lt;strong&gt;front-end development&lt;/strong&gt; using Angular or React, TypeScript, HTML5, and CSS&lt;/li&gt;&lt;li&gt;Strong understanding of &lt;strong&gt;software engineering best practices&lt;/strong&gt;, secure coding, testing, and performance optimization&lt;/li&gt;&lt;li&gt;Excellent analytical, problem-solving, and communication skills&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Preferred Skillsets&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Experience with &lt;strong&gt;MLOps / LLMOps frameworks and tools&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Exposure to &lt;strong&gt;Databricks&lt;/strong&gt;, ML pipelines, or AI orchestration frameworks&lt;/li&gt;&lt;li&gt;Knowledge of classical ML techniques, forecasting, or time-series analysis&lt;/li&gt;&lt;li&gt;Familiarity with &lt;strong&gt;event-driven architectures&lt;/strong&gt; and messaging systems&lt;/li&gt;&lt;li&gt;Cloud or AI certifications (Azure AI Engineer, Azure Solutions Architect, AWS ML, etc.)&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qualifications&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Bachelor’s or Master’s degree in &lt;strong&gt;Computer Science, Engineering, or a related field&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Ability to work effectively in &lt;strong&gt;agile, cross‑functional, global teams&lt;/strong&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;/p&gt;', 'applicantsCount': '132', 'salary': '', 'descriptionText': 'Line of Service: Advisory – Data, Analytics &amp; AISpecialization: Agentic AI, Full Stack DevelopmentManagement Level: Senior AssociateExperience: 6–8 YearsLocation: Mumbai(Hybrid)\nJob Description &amp; SummaryA career within PwC’s Data, Analytics &amp; AI practice provides opportunities to help organisations unlock enterprise value using advanced analytics, cloud platforms, and intelligent AI systems. We combine cutting-edge Agentic AI, Full Stack Engineering, and Cloud technologies to build scalable, secure, and innovative solutions that drive real business outcomes.As a Senior Associate – Full Stack Agentic AI Engineer, you will design, build, and deploy end‑to‑end AI‑powered applications by integrating large language models (LLMs), agentic workflows, APIs, and modern front-end frameworks. You will work closely with data scientists, architects, and business stakeholders to deliver intelligent, production‑ready AI solutions at scale.\nWhy PwCAt PwC, you’ll be part of a global community of problem solvers who lead with trust and deliver distinctive value. Our purpose‑led culture, combined with technology and innovation, empowers you to make a meaningful impact while continuously growing your skills.PwC is an equal opportunity employer. We promote an inclusive workplace with zero tolerance for discrimination or harassment, enabling everyone to bring their authentic selves to work and thrive professionally and personally.\nAbout the RoleWe are looking for a hands-on Full Stack Agentic AI Engineer with strong expertise in Python, cloud platforms, AI/ML, and front-end development. The ideal candidate is passionate about building intelligent, user‑centric applications, implementing agent-based AI systems, and operating AI solutions responsibly at enterprise scale.Key ResponsibilitiesDesign, develop, and maintain end‑to‑end full stack AI applications using Python-based back-end frameworks (FastAPI / Flask / Django) and modern front-end frameworks (Angular / React, TypeScript, HTML5, CSS)Build and integrate Agentic AI systems, LLMs, and generative AI models into enterprise applicationsDevelop and expose RESTful APIs to support AI-driven workflows and system integrationDeploy and manage AI applications on cloud platforms (Azure / AWS), ensuring scalability, security, and performanceImplement MLOps / LLMOps practices including model versioning, monitoring, evaluation, and retrainingManage data pipelines required for AI/ML workloads and inferenceEnsure adherence to data privacy, security, governance, and compliance standardsOptimize system performance, reliability, and cost efficiency across AI and application layersCollaborate with data scientists, architects, product owners, and business stakeholders to translate requirements into technical solutionsStay current with advancements in Agentic AI, Generative AI, and full stack technologies, and contribute to innovation initiatives\nMandatory Skillsets6+ years of experience in Full Stack Development and AI/ML solution deliveryStrong expertise in Python and back-end frameworks (FastAPI, Flask, Django)Experience building and integrating LLMs, Generative AI, and Agentic AI workflowsSolid knowledge of REST APIs, microservices architecture, and system integrationHands-on experience with cloud platforms (Azure/AWS), including AI and data servicesExperience with containerization and DevOps practices (Docker, CI/CD pipelines)Proficiency in front-end development using Angular or React, TypeScript, HTML5, and CSSStrong understanding of software engineering best practices, secure coding, testing, and performance optimizationExcellent analytical, problem-solving, and communication skills\nPreferred SkillsetsExperience with MLOps / LLMOps frameworks and toolsExposure to Databricks, ML pipelines, or AI orchestration frameworksKnowledge of classical ML techniques, forecasting, or time-series analysisFamiliarity with event-driven architectures and messaging systemsCloud or AI certifications (Azure AI Engineer, Azure Solutions Architect, AWS ML, etc.)\nQualificationsBachelor’s or Master’s degree in Computer Science, Engineering, or a related fieldAbility to work effectively in agile, cross‑functional, global teams', 'seniorityLevel': 'Mid-Senior level', 'employmentType': 'Full-time', 'jobFunction': 'Information Technology', 'industries': 'Professional Services', 'inputUrl': 'https://in.linkedin.com/jobs/search?keywords=AI%20Developer&amp;location=India&amp;geoId=102713980&amp;f_JT=F&amp;f_PP=105214831%2C105556991%2C103671728%2C106164952&amp;f_TPR=r86400&amp;position=1&amp;pageNum=0', 'salaryInsights': {}, 'applyMethod': 'ComplexOnsiteApply', 'expireAt': 1778336499000, 'postedAtTimestamp': 1775744500000, 'workplaceTypes': ['Hybrid'], 'workRemoteAllowed': False, 'standardizedTitle': 'Full Stack Engineer', 'country': 'IN', 'companyAddress': {'type': 'PostalAddress', 'streetAddress': 'Sector V, Salt Lake', 'addressLocality': 'Kolkata', 'addressRegion': 'West Bengal', 'postalCode': '700091', 'addressCountry': 'IN'}, 'companyWebsite': 'http://www.pwc.in', 'companySlogan': 'At PwC, our purpose is to build trust in society and solve important problems', 'companyDescription': 'At PwC, we help clients build trust and reinvent so they can turn complexity into competitive advantage. We’re a tech-forward, people-empowered network with more than 364,000 people in 136 countries and 137 territories. Across audit and assurance, tax and legal, deals and consulting, we help clients build, accelerate, and sustain momentum. Find out more at\u202fwww.pwc.com.\u202f\u202f \n\nPwC refers to the PwC network and/or one or more of its member firms, each of which is a separate legal entity. Please see www.pwc.com/structure for further details.', 'companyEmployeesCount': 27469}</t>
+  </si>
+  <si>
+    <t>Analyst</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;We are looking for a highly skilled and experienced Analyst to join our team in [location to be specified]. The ideal candidate will have a strong background in analysis and problem-solving, with excellent communication skills. As an Analyst, you will play a key role in driving business growth and improvement.&lt;/p&gt;&lt;br&gt;&lt;h3&gt;Roles and Responsibility&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Conduct thorough analysis of complex data sets to identify trends and patterns.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Develop and implement effective analytical models and tools to drive business decisions.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Collaborate with cross-functional teams to design and implement process improvements.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Analyze and interpret large datasets to extract valuable insights and recommendations.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Develop and maintain detailed reports and presentations to communicate findings to stakeholders.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Stay up-to-date with industry trends and emerging technologies to continuously improve analytical capabilities.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;&lt;br&gt;&lt;h3&gt;Job Requirements&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Strong understanding of analytical principles and techniques, including statistical modeling and machine learning.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Proficiency in programming languages such as Python, R, or SAS, with experience in data visualization tools like Tableau or Power BI.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Excellent communication and interpersonal skills, with the ability to work effectively with diverse stakeholders.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Strong problem-solving skills, with the ability to analyze complex problems and develop creative solutions.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Ability to work in a fast-paced environment, prioritizing multiple tasks and meeting deadlines.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Strong attention to detail, with a focus on delivering high-quality results and maintaining accurate records.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;&lt;br&gt;&lt;h3&gt;About Company&lt;/h3&gt;&lt;br&gt;&lt;p&gt;Firstsource Solutions Ltd is a leading company in the industry, committed to driving business growth and improvement through innovative solutions. We offer a dynamic and supportive work environment, with opportunities for professional development and growth.&lt;/p&gt;&lt;br&gt;&lt;br&gt;Disclaimer: This job description has been sourced from a public domain and may have been modified by Naukri.com to improve clarity for our users. We encourage job seekers to verify all details directly with the employer via their official channels before applying.</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426502667?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['Any Postgraduate'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 1094, 'groupId': 162228, 'roleCategory': 'Business Intelligence &amp; Analytics', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'Data Analyst', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 0, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/162228.gif', 'wfhType': '0', 'companyDetail': {'name': 'Firstsource', 'details': 'Firstsource is a specialized global business process management partner, and an RP-Sanjiv Goenka Group company. We provide transformational solutions and services spanning the customer lifecycle across Healthcare, Banking and Financial Services, Communications, Media and Technology, and other diverse industries. With an established presence in the US, the UK, India, Mexico, Australia, and the Philippines, we act as a trusted growth partner for leading global brands, including several Fortune 500 and FTSE 100 companies.', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': 'Strong understanding of analytical principles and techniques,including statistical modeling and machine learning.  .  Proficiency in programming languages such as Python,R,or SAS,with experience in data visualization tools like Tableau or Power BI.', 'consent': False, 'jobId': '090426502667', 'showEducationAsPlaceholder': False, 'companyId': 1877722, 'brandingTags': [], 'functionalArea': 'Data Science &amp; Analytics', 'fatFooter': {}, 'experienceText': '0-3 Yrs', 'referenceCode': '', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://careers.firstsource.com/job/Bangalore-Analyst-KA/54798944/', 'locationGids': ['97'], 'description': '&lt;p&gt;We are looking for a highly skilled and experienced Analyst to join our team in [location to be specified]. The ideal candidate will have a strong background in analysis and problem-solving, with excellent communication skills. As an Analyst, you will play a key role in driving business growth and improvement.&lt;/p&gt;&lt;br&gt;&lt;h3&gt;Roles and Responsibility&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Conduct thorough analysis of complex data sets to identify trends and patterns.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Develop and implement effective analytical models and tools to drive business decisions.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Collaborate with cross-functional teams to design and implement process improvements.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Analyze and interpret large datasets to extract valuable insights and recommendations.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Develop and maintain detailed reports and presentations to communicate findings to stakeholders.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Stay up-to-date with industry trends and emerging technologies to continuously improve analytical capabilities.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;&lt;br&gt;&lt;h3&gt;Job Requirements&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Strong understanding of analytical principles and techniques, including statistical modeling and machine learning.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Proficiency in programming languages such as Python, R, or SAS, with experience in data visualization tools like Tableau or Power BI.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Excellent communication and interpersonal skills, with the ability to work effectively with diverse stakeholders.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Strong problem-solving skills, with the ability to analyze complex problems and develop creative solutions.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Ability to work in a fast-paced environment, prioritizing multiple tasks and meeting deadlines.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Strong attention to detail, with a focus on delivering high-quality results and maintaining accurate records.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;&lt;br&gt;&lt;h3&gt;About Company&lt;/h3&gt;&lt;br&gt;&lt;p&gt;Firstsource Solutions Ltd is a leading company in the industry, committed to driving business growth and improvement through innovative solutions. We offer a dynamic and supportive work environment, with opportunities for professional development and growth.&lt;/p&gt;&lt;br&gt;&lt;br&gt;Disclaimer: This job description has been sourced from a public domain and may have been modified by Naukri.com to improve clarity for our users. We encourage job seekers to verify all details directly with the employer via their official channels before applying.', 'staticCompanyName': 'firstsource-jobs-careers-99763', 'industry': 'Banking', 'staticUrl': 'https://www.naukri.com/job-listings-analyst-firstsource-solutions-ltd-bengaluru-0-to-3-years-090426502667', 'title': 'Analyst', 'walkIn': False, 'maximumExperience': 3, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 2549, 'jobType': 'fulltime', 'companyPageUrl': 'firstsource-overview-162228', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/162228.gif', 'microsite': False, 'createdDate': '2026-04-09 16:28:27', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/162228.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Bengaluru', 'url': 'https://www.naukri.com/jobs-in-bangalore'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426502667&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': '', 'label': 'emerging technologies'}, {'clickable': 'python', 'label': 'python'}, {'clickable': 'power bi', 'label': 'power bi'}, {'clickable': '', 'label': 'visualization tools'}, {'clickable': '', 'label': 'communication and interpersonal skills'}, {'clickable': 'machine learning', 'label': 'machine learning'}, {'clickable': 'programming', 'label': 'programming languages'}, {'clickable': 'r', 'label': 'r'}, {'clickable': 'tableau', 'label': 'tableau'}, {'clickable': 'statistical modeling', 'label': 'statistical modeling'}, {'clickable': 'business growth', 'label': 'business growth'}, {'clickable': 'data visualization', 'label': 'data visualization'}, {'clickable': 'programming', 'label': 'programming'}, {'clickable': 'communication skills', 'label': 'communication skills'}], 'preferred': []}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Analyst', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/162228.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/162228.gif', 'jobId': '090426502667', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Firstsource', 'isSaved': False, 'tagsAndSkills': 'emerging technologies,python,power bi,visualization tools,communication and interpersonal skills,machine learning,programming languages,r', 'placeholders': [{'type': 'experience', 'label': '0-3 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Bengaluru'}], 'companyId': 1877722, 'jdURL': '/job-listings-analyst-firstsource-solutions-ltd-bengaluru-0-to-3-years-090426502667', 'staticUrl': 'firstsource-jobs-careers-99763', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/first-source-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 5734, 'AggregateRating': '3.6', 'Title': 'Firstsource Solutions Reviews by Employees'}, 'jobDescription': '  Strong understanding of analytical principles and techniques,including statistical modeling and machine learning.  .  Proficiency in programming languages such as Python,R,or SAS,with experience in data visualization tools like Tableau or Power BI.', 'showMultipleApply': False, 'groupId': 162228, 'isTopGroup': 0, 'createdDate': 1775732307000, 'mode': 'crawled', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-3 Yrs', 'minimumExperience': '0', 'maximumExperience': '3', 'applyByTime': '8:28 PM', 'companyApplyJob': True, 'walkinJob': False, 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426502667&amp;logstr=srprestapi', 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:51:58.863Z', 'url': 'https://www.nma.mobi/post/v4/job/090426502667?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>Machine Learning Scientist I</t>
+  </si>
+  <si>
+    <t>&lt;div&gt; &lt;span&gt; As our Machine Learning Engineer, you will join our Applied Machine Learning Team in India, who develops machine learning and computer vision algorithms to monitor and assess the state of drivers and their environments to identify risk and improve safety for our clients. You will contribute to all aspects of the DL/ML model development and deployment cycle to improve the accuracy and throughput at reduced latency to help enhance and differentiate us as the leader in the Video Safety and Telematics industry. If this sounds like you, we encourage you to apply &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; What you'll Do &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Develop ML/DL models end-to-end problem formulation, data engineering, prototyping, training, evaluation, and iteration. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Implement, debug, and improve DL models using frameworks such as PyTorch or TensorFlow. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Optimize &amp; deploy models on cloud/edge &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Continuous improvement of models using large scale field data &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Leverage GenAI tools and LLM APIs (eg, Claude) to build solutions for internal and customer-facing use cases. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Build and iterate on prompt engineering workflows, RAG pipelines, and LLM-powe'red applications along with AI agents for task/workflow automation &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Communicate findings and technical trade-offs to internal teams. &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; &lt;/span&gt; &lt;/b&gt;   &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; What you'll Need &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;strong&gt; Required &lt;/strong&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Bachelors or Masters degree in CS, EE, ECE, or a related field. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; 0 2 years of experience (including internships or academic work) in ML or DL. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Hands-on experience with at least one DL framework (PyTorch or TensorFlow). &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Proficiency in Python; familiarity with C/C++. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Strong foundations in mathematics, probability, statistics, and algorithms. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Solid understanding of core ML concepts (supervised/unsupervised learning, model evaluation, regularization, etc). &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Strong analytical and problem-solving skills; ability to thrive in a collaborative, fast-paced environment. &lt;/div&gt; &lt;div&gt; &lt;strong&gt; &lt;span&gt; &lt;/span&gt; &lt;/strong&gt;   &lt;/div&gt; &lt;div&gt; &lt;strong&gt; &lt;span&gt; Preferred &lt;/span&gt; &lt;/strong&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Experience using GenAI tools and LLM APIs (eg, Claude, OpenAI, Gemini) to build applications or automate workflows, along with familiarity with AI coding tools like Claude Code/GitHub Copilot &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Experience with model deployment tools (ONNX, TensorRT, Docker) or cloud ML platforms. &lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426501209?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['LLM in Law', 'Any Postgraduate'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 446, 'groupId': 6601387, 'roleCategory': 'Data Science &amp; Machine Learning', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'Data Science &amp; Machine Learning - Other', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 0, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/6601387.gif', 'wfhType': '0', 'companyDetail': {'name': 'Lytx', 'details': 'Lytx is the global leader in fleet management technologies. Our solutions harness the power of video to empower drivers and fleets to be safer and more efficient, productive, and profitable so they can thrive in today??s competitive environment. Through the Lytx platform, direct and reseller clients access our customizable services and programs spanning driver safety, risk detection, fleet tracking, compliance, preventative maintenance, and fuel management. Using the world??s largest driving database of its kind, along with proprietary machine vision and artificial intelligence technology, we help protect and connect thousands of fleets and 1.6 million drivers in more than 60 countries worldwide. Lytx is privately held and headquartered in San Diego, California.', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': '', 'consent': False, 'jobId': '090426501209', 'showEducationAsPlaceholder': False, 'companyId': 123692763, 'brandingTags': [], 'functionalArea': 'Data Science &amp; Analytics', 'fatFooter': {}, 'experienceText': '0-2 Yrs', 'referenceCode': 'R-4176', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://lytx.wd1.myworkdayjobs.com/en-US/Lytx/job/Office---Bangalore-India/Machine-Learning-Scientist-I_R-4176', 'locationGids': ['97'], 'description': "&lt;div&gt; &lt;span&gt; As our Machine Learning Engineer, you will join our Applied Machine Learning Team in India, who develops machine learning and computer vision algorithms to monitor and assess the state of drivers and their environments to identify risk and improve safety for our clients. You will contribute to all aspects of the DL/ML model development and deployment cycle to improve the accuracy and throughput at reduced latency to help enhance and differentiate us as the leader in the Video Safety and Telematics industry. If this sounds like you, we encourage you to apply &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; What you'll Do &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Develop ML/DL models end-to-end problem formulation, data engineering, prototyping, training, evaluation, and iteration. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Implement, debug, and improve DL models using frameworks such as PyTorch or TensorFlow. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Optimize &amp; deploy models on cloud/edge &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Continuous improvement of models using large scale field data &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Leverage GenAI tools and LLM APIs (eg, Claude) to build solutions for internal and customer-facing use cases. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Build and iterate on prompt engineering workflows, RAG pipelines, and LLM-powe'red applications along with AI agents for task/workflow automation &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Communicate findings and technical trade-offs to internal teams. &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; &lt;/span&gt; &lt;/b&gt; \xa0 &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; What you'll Need &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;strong&gt; Required &lt;/strong&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Bachelors or Masters degree in CS, EE, ECE, or a related field. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; 0 2 years of experience (including internships or academic work) in ML or DL. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Hands-on experience with at least one DL framework (PyTorch or TensorFlow). &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Proficiency in Python; familiarity with C/C++. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Strong foundations in mathematics, probability, statistics, and algorithms. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Solid understanding of core ML concepts (supervised/unsupervised learning, model evaluation, regularization, etc). &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Strong analytical and problem-solving skills; ability to thrive in a collaborative, fast-paced environment. &lt;/div&gt; &lt;div&gt; &lt;strong&gt; &lt;span&gt; &lt;/span&gt; &lt;/strong&gt; \xa0 &lt;/div&gt; &lt;div&gt; &lt;strong&gt; &lt;span&gt; Preferred &lt;/span&gt; &lt;/strong&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Experience using GenAI tools and LLM APIs (eg, Claude, OpenAI, Gemini) to build applications or automate workflows, along with familiarity with AI coding tools like Claude Code/GitHub Copilot &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Experience with model deployment tools (ONNX, TensorRT, Docker) or cloud ML platforms. &lt;/div&gt;", 'staticCompanyName': 'lytx-jobs-careers-123692763', 'industry': 'IT Services &amp; Consulting', 'staticUrl': 'https://www.naukri.com/job-listings-machine-learning-scientist-i-lytx-bengaluru-0-to-2-years-090426501209', 'title': 'Machine Learning Scientist I', 'walkIn': False, 'maximumExperience': 2, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 979, 'jobType': 'fulltime', 'companyPageUrl': 'lytx-overview-6601387', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/6601387.gif', 'microsite': False, 'createdDate': '2026-04-09 16:07:23', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/6601387.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Bengaluru', 'url': 'https://www.naukri.com/jobs-in-bangalore'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426501209&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': 'computer vision', 'label': 'Computer vision'}, {'clickable': 'automation', 'label': 'Automation'}, {'clickable': 'cpp', 'label': 'C++'}, {'clickable': 'coding', 'label': 'Coding'}, {'clickable': 'analytical', 'label': 'Analytical'}, {'clickable': 'machine learning', 'label': 'Machine learning'}, {'clickable': 'telematics', 'label': 'Telematics'}, {'clickable': 'continuous improvement', 'label': 'Continuous improvement'}, {'clickable': 'python', 'label': 'Python'}], 'preferred': []}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Machine Learning Scientist I', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/6601387.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/6601387.gif', 'jobId': '090426501209', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Lytx', 'isSaved': False, 'tagsAndSkills': 'Computer vision,Automation,C++,Coding,Analytical,Machine learning,Telematics,Continuous improvement', 'placeholders': [{'type': 'experience', 'label': '0-2 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Bengaluru'}], 'companyId': 123692763, 'jdURL': '/job-listings-machine-learning-scientist-i-lytx-bengaluru-0-to-2-years-090426501209', 'staticUrl': 'lytx-jobs-careers-123692763', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/lytx-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 9, 'AggregateRating': '3.9', 'Title': 'Lytx Reviews by Employees'}, 'jobDescription': "&lt;div&gt; &lt;span&gt; As our Machine Learning Engineer, you will join our Applied Machine Learning Team in India, who develops machine learning and computer vision algorithms to monitor and assess the state of drivers and their environments to identify risk and improve safety for our clients. You will contribute to all aspects of the DL/ML model development and deployment cycle to improve the accuracy and throughput at reduced latency to help enhance and differentiate us as the leader in the Video Safety and Telematics industry. If this sounds like you, we encourage you to apply &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; What you'll Do &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Develop ML/DL models end-to-end problem formulation, data engineering, prototyping, training, evaluation, and iteration. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Implement, debug, and improve DL models using frameworks such as PyTorch or TensorFlow. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Optimize &amp; deploy models on cloud/edge &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Continuous improvement of models using large scale field data &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Leverage GenAI tools and LLM APIs (eg, Claude) to build solutions for internal and customer-facing use cases. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Build and iterate on prompt engineering workflows, RAG pipelines, and LLM-powe'red applications along with AI agents for task/workflow automation &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Communicate findings and technical trade-offs to internal teams. &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; &lt;/span&gt; &lt;/b&gt; \xa0 &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; What you'll Need &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;strong&gt; Required &lt;/strong&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Bachelors or Masters degree in CS, EE, ECE, or a related field. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; 0 2 years of experience (including internships or academic work) in ML or DL. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Hands-on experience with at least one DL framework (PyTorch or TensorFlow). &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Proficiency in Python; familiarity with C/C++. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Strong foundations in mathematics, probability, statistics, and algorithms. &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Solid understanding of core ML concepts (supervised/unsupervised learning, model evaluation, regularization, etc). &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Strong analytical and problem-solving skills; ability to thrive in a collaborative, fast-paced environment. &lt;/div&gt; &lt;div&gt; &lt;strong&gt; &lt;span&gt; &lt;/span&gt; &lt;/strong&gt; \xa0 &lt;/div&gt; &lt;div&gt; &lt;strong&gt; &lt;span&gt; Preferred &lt;/span&gt; &lt;/strong&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Experience using GenAI tools and LLM APIs (eg, Claude, OpenAI, Gemini) to build applications or automate workflows, along with familiarity with AI coding tools like Claude Code/GitHub Copilot &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/span&gt; Experience with model deployment tools (ONNX, TensorRT, Docker) or cloud ML platforms. &lt;/div&gt;", 'showMultipleApply': False, 'groupId': 6601387, 'isTopGroup': 0, 'createdDate': 1775731043000, 'mode': 'crawled', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-2 Yrs', 'minimumExperience': '0', 'maximumExperience': '2', 'applyByTime': '8:07 PM', 'companyApplyJob': True, 'walkinJob': False, 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426501209&amp;logstr=srprestapi', 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:51:59.114Z', 'url': 'https://www.nma.mobi/post/v4/job/090426501209?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>AI Benchmarking Specialist</t>
+  </si>
+  <si>
+    <t>&lt;p&gt; &lt;strong&gt; Key job responsibilities &lt;/strong&gt; &lt;br /&gt; &lt;/p&gt; &lt;ul&gt; &lt;li&gt; As part of your role, you will have the opportunity to, &lt;br /&gt; Assist in planning and executing benchmarking exercises for AI models, including defining test plans, metrics, and acceptance criteria across accuracy, robustness, bias, and reliability &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Support content accuracy, relevancy, and privacy checks by reviewing datasets, model outputs, and data handling practices, escalating potential regulatory risks. &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Validate data based on specific annotation guidelines, ensuring the accuracy and quality of the collected information &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Prepare clear audit and benchmarking reports, including error ratings, root-cause analysis, and recommendations, and contribute to presentations for senior stakeholders &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Maintain organized audit documentation, evidence, and benchmarking datasets to support internal review &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; You will work closely with your team members and managers to drive process efficiencies and explore opportunities for automation &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; You will strive to enhance the productivity and effectiveness of the data generation by contributing to the development and continuous improvement of AI audit methodologies, checklists, and test frameworks as regulations and best practices evolve. &lt;br /&gt; &lt;/li&gt; &lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426503472?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['LLM in Law'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 16, 'groupId': 398058, 'roleCategory': 'Non Voice', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'Technical Support - Non Voice', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 1, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/398058.gif', 'wfhType': '0', 'companyDetail': {'name': 'Amazon', 'details': 'Amazon is guided by four principles: customer obsession rather than competitor focus, passion for invention, commitment to operational excellence, and long-term thinking. We are driven by the excitement of building technologies, inventing products, and providing services that change lives. We embrace new ways of doing things, make decisions quickly, and are not afraid to fail. We have the scope and capabilities of a large company, and the spirit and heart of a small one.', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': '', 'consent': False, 'jobId': '090426503472', 'showEducationAsPlaceholder': False, 'companyId': 728574, 'brandingTags': [], 'functionalArea': 'Customer Success, Service &amp; Operations', 'fatFooter': {}, 'experienceText': '0-7 Yrs', 'referenceCode': '', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://www.amazon.jobs/en/jobs/10385865/ai-benchmarking-specialist-sp-support-spanish-international-seller-growth', 'locationGids': ['97'], 'description': '&lt;p&gt; &lt;strong&gt; Key job responsibilities &lt;/strong&gt; &lt;br /&gt; &lt;/p&gt; &lt;ul&gt; &lt;li&gt; As part of your role, you will have the opportunity to, &lt;br /&gt; Assist in planning and executing benchmarking exercises for AI models, including defining test plans, metrics, and acceptance criteria across accuracy, robustness, bias, and reliability &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Support content accuracy, relevancy, and privacy checks by reviewing datasets, model outputs, and data handling practices, escalating potential regulatory risks. &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Validate data based on specific annotation guidelines, ensuring the accuracy and quality of the collected information &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Prepare clear audit and benchmarking reports, including error ratings, root-cause analysis, and recommendations, and contribute to presentations for senior stakeholders &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Maintain organized audit documentation, evidence, and benchmarking datasets to support internal review &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; You will work closely with your team members and managers to drive process efficiencies and explore opportunities for automation &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; You will strive to enhance the productivity and effectiveness of the data generation by contributing to the development and continuous improvement of AI audit methodologies, checklists, and test frameworks as regulations and best practices evolve. &lt;br /&gt; &lt;/li&gt; &lt;/ul&gt;', 'staticCompanyName': 'amazon-jobs-careers-93000', 'industry': 'Internet', 'staticUrl': 'https://www.naukri.com/job-listings-ai-benchmarking-specialist-amazon-development-centre-india-pvt-ltd-bengaluru-0-to-7-years-090426503472', 'title': 'AI Benchmarking Specialist', 'walkIn': False, 'maximumExperience': 7, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 98, 'jobType': 'fulltime', 'companyPageUrl': 'amazon-overview-398058', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/398058.gif', 'microsite': False, 'createdDate': '2026-04-09 18:06:28', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/398058.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Bengaluru', 'url': 'https://www.naukri.com/jobs-in-bangalore'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426503472&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': 'root cause analysis', 'label': 'Root cause analysis'}, {'clickable': 'automation', 'label': 'Automation'}, {'clickable': '', 'label': 'Manager Quality Assurance'}, {'clickable': 'audit documentation', 'label': 'Audit documentation'}, {'clickable': 'artificial intelligence', 'label': 'Artificial Intelligence'}, {'clickable': 'machine learning', 'label': 'Machine learning'}, {'clickable': 'spanish', 'label': 'Spanish'}, {'clickable': 'continuous improvement', 'label': 'Continuous improvement'}, {'clickable': 'quality compliance', 'label': 'Quality compliance'}, {'clickable': 'recruitment', 'label': 'Recruitment'}], 'preferred': []}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'AI Benchmarking Specialist', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/398058.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/398058.gif', 'jobId': '090426503472', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Amazon', 'isSaved': False, 'tagsAndSkills': 'Root cause analysis,Automation,Manager Quality Assurance,Audit documentation,Artificial Intelligence,Machine learning,Spanish,Continuous improvement', 'placeholders': [{'type': 'experience', 'label': '0-7 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Bengaluru'}], 'companyId': 728574, 'jdURL': '/job-listings-ai-benchmarking-specialist-amazon-development-centre-india-pvt-ltd-bengaluru-0-to-7-years-090426503472', 'staticUrl': 'amazon-jobs-careers-93000', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/amazon-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 31423, 'AggregateRating': '3.9', 'Title': 'Amazon Reviews by Employees'}, 'jobDescription': '&lt;p&gt; &lt;strong&gt; Key job responsibilities &lt;/strong&gt; &lt;br /&gt; &lt;/p&gt; &lt;ul&gt; &lt;li&gt; As part of your role, you will have the opportunity to, &lt;br /&gt; Assist in planning and executing benchmarking exercises for AI models, including defining test plans, metrics, and acceptance criteria across accuracy, robustness, bias, and reliability &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Support content accuracy, relevancy, and privacy checks by reviewing datasets, model outputs, and data handling practices, escalating potential regulatory risks. &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Validate data based on specific annotation guidelines, ensuring the accuracy and quality of the collected information &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Prepare clear audit and benchmarking reports, including error ratings, root-cause analysis, and recommendations, and contribute to presentations for senior stakeholders &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Maintain organized audit documentation, evidence, and benchmarking datasets to support internal review &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; You will work closely with your team members and managers to drive process efficiencies and explore opportunities for automation &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;li&gt; You will strive to enhance the productivity and effectiveness of the data generation by contributing to the development and continuous improvement of AI audit methodologies, checklists, and test frameworks as regulations and best practices evolve. &lt;br /&gt; &lt;/li&gt; &lt;/ul&gt;', 'showMultipleApply': False, 'groupId': 398058, 'isTopGroup': 0, 'createdDate': 1775738188000, 'mode': 'crawled', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-7 Yrs', 'minimumExperience': '0', 'maximumExperience': '7', 'applyByTime': '10:06 PM', 'companyApplyJob': True, 'walkinJob': False, 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426503472&amp;logstr=srprestapi', 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:51:59.174Z', 'url': 'https://www.nma.mobi/post/v4/job/090426503472?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>Java FullStack Developer</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;&lt;li&gt; Fullstack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles  &lt;/li&gt;&lt;li&gt; Extensive experience working with most if not all the technologies listed below: Java Core with extensive hands-on experience with concurrent programming.  &lt;/li&gt;&lt;li&gt; Spring Framework including Core, Integration, Batch, JDBC, Hibernate  &lt;/li&gt;&lt;li&gt; Good development experience in Angular and Angular components Good  &lt;/li&gt;&lt;li&gt; Knowledge in RxJS, Router and micro-frontend architecure  &lt;/li&gt;&lt;li&gt; Distributed Caching frameworks such as Redis or equivalent.  &lt;/li&gt;&lt;li&gt; Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes)  &lt;/li&gt;&lt;li&gt; Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB  &lt;/li&gt;&lt;li&gt; Familiarity with Linux environment including scripting skills  &lt;/li&gt;&lt;li&gt; SDLC/Dev Ops - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits &lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426919758?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['B.Tech / B.E. in Any Specialization'], 'pg': ['Any Postgraduate'], 'degreeCombination': 'ugorpgorppg', 'premiumProcessed': False, 'eduPlaceholderText': '', 'ppg': [], 'label': '', 'isSchool': None}, 'hideApplyButton': False, 'applyCount': 1627, 'groupId': 1186200, 'roleCategory': 'Software Development', 'mode': 'jp', 'tagLabels': [], 'jobRole': 'Full Stack Developer', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 1, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'wfhType': '0', 'companyDetail': {'name': 'Virtusa', 'websiteUrl': '', 'details': 'Virtusa Corporation (NASDAQ: VRTU) is a global information technology (IT) services company providing IT consulting, technology and outsourcing services. Using our enhanced global delivery model, innovative platforming approach and industry expertise, we provide cost-effective services that enable our clients to use IT to enhance business performance, accelerate time-to-market, increase productivity and improve customer service. We serve Global 2000 enterprises and the leading software vendors in communications &amp; technology; banking, financial services &amp; insurance; and media &amp; information industries. We build and sustain application platforms for our clients that create competitive advantage.&lt;br&gt;&lt;br&gt;&lt;br&gt;Founded in 1996 and headquartered in Massachusetts, we have offices and technology centers throughout the U.S., U.K. and Asia. Globally, Virtusa has been acknowledged and recognized by customers, industry associations and media among others. Some of the awards and recognitions include Dataquest-CMR €“ IT Best Employers Survey -2012 (Ranked No. 5), International Business Award €“ 2012(Stevie awards) , Britain€™s Top Employers- 2012, American Business Award€“ 2012,Boston Business Journal€™s Fastest Growing Public Companies, Global Services 100, Fintech 100, Sri Lanka National HRM and others.', 'address': 'Sy.No.115/Part,Plot No.10,Virtusa IT Park,Nanakram  guda Village,Serilingampally Mandal  , Hyderabad, Telangana, India', 'media': {'ppt': [], 'video': [], 'photos': []}, 'hiringFor': '', 'isKycSuccessful': True}, 'jobIconType': '', 'shortDescription': 'Experienced Fullstack developer skilled in Java Core concurrency, Spring Framework, Angular, RxJS, micro-frontend architecture, Redis, Docker, Kubernetes, Oracle and MongoDB databases|Design and develop scalable, maintainable applications using OOP principles and work with cloud, containerization, microservices, and CI/CD pipelines', 'consent': False, 'jobId': '090426919758', 'showEducationAsPlaceholder': False, 'companyId': 1354, 'brandingTags': [], 'functionalArea': 'Engineering - Software &amp; QA', 'fatFooter': {}, 'experienceText': '0-5 Yrs', 'referenceCode': 'CREQ252206', 'vacancy': 0, 'template': '', 'locationGids': ['139'], 'description': '&lt;ul&gt;&lt;li&gt; Fullstack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles  &lt;/li&gt;&lt;li&gt; Extensive experience working with most if not all the technologies listed below: Java Core with extensive hands-on experience with concurrent programming.  &lt;/li&gt;&lt;li&gt; Spring Framework including Core, Integration, Batch, JDBC, Hibernate  &lt;/li&gt;&lt;li&gt; Good development experience in Angular and Angular components Good  &lt;/li&gt;&lt;li&gt; Knowledge in RxJS, Router and micro-frontend architecure  &lt;/li&gt;&lt;li&gt; Distributed Caching frameworks such as Redis or equivalent.  &lt;/li&gt;&lt;li&gt; Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes)  &lt;/li&gt;&lt;li&gt; Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB  &lt;/li&gt;&lt;li&gt; Familiarity with Linux environment including scripting skills  &lt;/li&gt;&lt;li&gt; SDLC/Dev Ops - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits &lt;/li&gt;&lt;/ul&gt;', 'staticCompanyName': 'virtusa-jobs-careers-1354', 'industry': 'Banking', 'staticUrl': 'https://www.naukri.com/job-listings-java-fullstack-developer-virtusa-consulting-services-pvt-ltd-pune-0-to-5-years-090426919758', 'title': 'Java FullStack Developer', 'walkIn': False, 'maximumExperience': 5, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 2469, 'jobType': 'fulltime', 'companyPageUrl': 'virtusa-overview-1186200', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'microsite': False, 'createdDate': '2026-04-09 14:22:26', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Pune', 'url': 'https://www.naukri.com/jobs-in-pune'}], 'keySkills': {'other': [{'clickable': '', 'label': 'kubernetes'}, {'clickable': '', 'label': 'bitbucket'}, {'clickable': 'redis', 'label': 'redis'}, {'clickable': 'nosql', 'label': 'nosql'}, {'clickable': 'microservices', 'label': 'microservices'}, {'clickable': 'docker', 'label': 'docker'}, {'clickable': '', 'label': 'angular'}, {'clickable': 'git', 'label': 'git'}, {'clickable': 'linux', 'label': 'linux'}, {'clickable': 'jenkins', 'label': 'jenkins'}, {'clickable': 'cloud computing', 'label': 'cloud computing'}, {'clickable': 'sdlc', 'label': 'sdlc'}, {'clickable': 'mongodb', 'label': 'mongodb'}, {'clickable': 'jira', 'label': 'jira'}], 'preferred': [{'clickable': 'java', 'label': 'java'}]}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Java FullStack Developer', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'jobId': '090426919758', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Virtusa', 'isSaved': False, 'tagsAndSkills': 'java,kubernetes,bitbucket,redis,nosql,microservices,docker,angular', 'placeholders': [{'type': 'experience', 'label': '0-5 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Pune'}], 'companyId': 1354, 'jdURL': '/job-listings-java-fullstack-developer-virtusa-consulting-services-pvt-ltd-pune-0-to-5-years-090426919758', 'staticUrl': 'virtusa-jobs-careers-1354', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/virtusa-consulting-services-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 6077, 'AggregateRating': '3.7', 'Title': 'Virtusa Consulting Services Reviews by Employees'}, 'jobDescription': 'Fullstack developer with experience in designing and developing robust,scalable,and maintainable applications applying Object Oriented Design principles &lt;br&gt;&lt;br&gt;Spring Framework including Core,Integration,Batch,JDBC,Hibernate &lt;br&gt;&lt;br&gt;Databases - RDBMS preferably Oracle,NoSQL preferably MongoDB &lt;br&gt;&lt;br&gt;Good development experience in Angular and Angular components Good', 'showMultipleApply': False, 'groupId': 1186200, 'isTopGroup': 0, 'createdDate': 1775724746037, 'mode': 'jp', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-5 Yrs', 'minimumExperience': '0', 'maximumExperience': '5', 'applyByTime': '6:22 PM', 'companyApplyJob': False, 'walkinJob': False, 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:51:59.450Z', 'url': 'https://www.nma.mobi/post/v4/job/090426919758?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;span&gt;&lt;span&gt;Full-stack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles Extensive experience working with most if not all the technologies listed below: Java Core with extensive hands-on experience with concurrent programming. &lt;br /&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;li&gt;Spring Framework including Core, Integration, Batch, JDBC, Hibernate Good development experience in Angular and Angular components Good Knowledge in RxJS, Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent. &lt;/li&gt;&lt;li&gt;Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes) Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB Familiarity with Linux environment including scripting skills SDLC/Dev Ops - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits&lt;/li&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426927521?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['B.Tech / B.E. in Any Specialization'], 'pg': ['Any Postgraduate'], 'degreeCombination': 'ugorpgorppg', 'premiumProcessed': False, 'eduPlaceholderText': '', 'ppg': [], 'label': '', 'isSchool': None}, 'hideApplyButton': False, 'applyCount': 1416, 'groupId': 1186200, 'roleCategory': 'Software Development', 'mode': 'jp', 'tagLabels': [], 'jobRole': 'Full Stack Developer', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 1, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'wfhType': '0', 'companyDetail': {'name': 'Virtusa', 'websiteUrl': '', 'details': 'Virtusa Corporation (NASDAQ: VRTU) is a global information technology (IT) services company providing IT consulting, technology and outsourcing services. Using our enhanced global delivery model, innovative platforming approach and industry expertise, we provide cost-effective services that enable our clients to use IT to enhance business performance, accelerate time-to-market, increase productivity and improve customer service. We serve Global 2000 enterprises and the leading software vendors in communications &amp; technology; banking, financial services &amp; insurance; and media &amp; information industries. We build and sustain application platforms for our clients that create competitive advantage.&lt;br&gt;&lt;br&gt;&lt;br&gt;Founded in 1996 and headquartered in Massachusetts, we have offices and technology centers throughout the U.S., U.K. and Asia. Globally, Virtusa has been acknowledged and recognized by customers, industry associations and media among others. Some of the awards and recognitions include Dataquest-CMR €“ IT Best Employers Survey -2012 (Ranked No. 5), International Business Award €“ 2012(Stevie awards) , Britain€™s Top Employers- 2012, American Business Award€“ 2012,Boston Business Journal€™s Fastest Growing Public Companies, Global Services 100, Fintech 100, Sri Lanka National HRM and others.', 'address': 'Sy.No.115/Part,Plot No.10,Virtusa IT Park,Nanakram  guda Village,Serilingampally Mandal  , Hyderabad, Telangana, India', 'media': {'ppt': [], 'video': [], 'photos': []}, 'hiringFor': '', 'isKycSuccessful': True}, 'jobIconType': '', 'shortDescription': 'Experienced full-stack developer skilled in Java concurrent programming, Spring Framework, Angular, RxJS, micro-frontend architecture, Redis, Docker, Kubernetes, Oracle and MongoDB databases|Design and develop scalable, maintainable applications using OOP principles; work with microservices, distributed caching, cloud technologies, and CI/CD pipelines', 'consent': False, 'jobId': '090426927521', 'showEducationAsPlaceholder': False, 'companyId': 1354, 'brandingTags': [], 'functionalArea': 'Engineering - Software &amp; QA', 'fatFooter': {}, 'experienceText': '0-1 Yrs', 'referenceCode': 'CREQ252191', 'vacancy': 0, 'template': '', 'locationGids': ['139'], 'description': '&lt;p&gt;&lt;span&gt;&lt;span&gt;Full-stack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles Extensive experience working with most if not all the technologies listed below: Java Core with extensive hands-on experience with concurrent programming. &lt;br /&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;&lt;li&gt;Spring Framework including Core, Integration, Batch, JDBC, Hibernate Good development experience in Angular and Angular components Good Knowledge in RxJS, Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent. &lt;/li&gt;&lt;li&gt;Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes) Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB Familiarity with Linux environment including scripting skills SDLC/Dev Ops - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits&lt;/li&gt;', 'staticCompanyName': 'virtusa-jobs-careers-1354', 'industry': 'Banking', 'staticUrl': 'https://www.naukri.com/job-listings-java-fullstack-developer-virtusa-consulting-services-pvt-ltd-pune-0-to-1-years-090426927521', 'title': 'Java FullStack Developer', 'walkIn': False, 'maximumExperience': 1, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 2104, 'jobType': 'fulltime', 'companyPageUrl': 'virtusa-overview-1186200', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'microsite': False, 'createdDate': '2026-04-09 17:42:23', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Pune', 'url': 'https://www.naukri.com/jobs-in-pune'}], 'keySkills': {'other': [{'clickable': 'hibernate framework', 'label': 'Hibernate'}, {'clickable': 'programming', 'label': 'Programming'}, {'clickable': '', 'label': 'Full Stack'}, {'clickable': 'redis', 'label': 'Redis'}, {'clickable': 'jira', 'label': 'Jira'}, {'clickable': '', 'label': 'Angular'}, {'clickable': 'microservices', 'label': 'Microservices'}, {'clickable': 'sdlc', 'label': 'Sdlc'}, {'clickable': 'scripting', 'label': 'Scripting'}, {'clickable': 'jenkins', 'label': 'Jenkins'}, {'clickable': '', 'label': 'Full Stack Developer'}, {'clickable': 'nosql', 'label': 'Nosql'}, {'clickable': 'git', 'label': 'Git'}, {'clickable': 'cloud computing', 'label': 'Cloud Computing'}, {'clickable': 'docker', 'label': 'Docker'}, {'clickable': 'linux', 'label': 'Linux'}, {'clickable': 'caching', 'label': 'Caching'}, {'clickable': 'cloud', 'label': 'Cloud'}, {'clickable': 'spring framework', 'label': 'Spring Framework'}, {'clickable': 'mongodb', 'label': 'Mongodb'}, {'clickable': '', 'label': 'Bitbucket'}, {'clickable': 'oracle', 'label': 'Oracle'}, {'clickable': '', 'label': 'Kubernetes'}], 'preferred': [{'clickable': 'java', 'label': 'Java'}]}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Java FullStack Developer', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'jobId': '090426927521', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Virtusa', 'isSaved': False, 'tagsAndSkills': 'Java,Hibernate,Programming,Full Stack,Redis,Jira,Angular,Microservices', 'placeholders': [{'type': 'experience', 'label': '0-1 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Pune'}], 'companyId': 1354, 'jdURL': '/job-listings-java-fullstack-developer-virtusa-consulting-services-pvt-ltd-pune-0-to-1-years-090426927521', 'staticUrl': 'virtusa-jobs-careers-1354', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/virtusa-consulting-services-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 6077, 'AggregateRating': '3.7', 'Title': 'Virtusa Consulting Services Reviews by Employees'}, 'jobDescription': 'Cloud computing technologies with practical experience working with containers,microservices and large datasets (Docker,Kubernetes) Databases - RDBMS preferably Oracle,NoSQL preferably MongoDB Familiarity with Linux environment including scripting skills SDLC / Dev Ops - Git / BitBucket,CI / CD pipeline frameworks such as Jenkins,SonarQube,JIRA,any secure coding toolkits', 'showMultipleApply': False, 'groupId': 1186200, 'isTopGroup': 0, 'createdDate': 1775736743803, 'mode': 'jp', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-1 Yrs', 'minimumExperience': '0', 'maximumExperience': '1', 'applyByTime': '9:42 PM', 'companyApplyJob': False, 'walkinJob': False, 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:51:59.538Z', 'url': 'https://www.nma.mobi/post/v4/job/090426927521?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>Senior .NET Full-Stack Developer</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;We are looking for a skilled Senior .NET Full-Stack Developer with 1 opening to join our team at Vakils Premedia Pvt. Ltd.&lt;/p&gt;&lt;br&gt;&lt;h3&gt;Roles and Responsibility&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Design, develop, and maintain high-quality software applications using .NET technologies.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Collaborate with cross-functional teams to identify and prioritize project requirements.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Develop and implement robust, scalable, and efficient codebases.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Troubleshoot and resolve technical issues efficiently.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Participate in code reviews and contribute to improving overall code quality.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Stay updated with industry trends and emerging technologies to enhance skills and knowledge.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;&lt;br&gt;&lt;h3&gt;Job Requirements&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Strong proficiency in .NET languages such as C#, VB.NET, and F#.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Experience with full-stack development frameworks and tools.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Excellent problem-solving skills and attention to detail.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Strong communication and teamwork skills.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Ability to work in an agile environment and adapt to changing priorities.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Familiarity with database management systems and querying languages.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426500106?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['Any Postgraduate'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 152, 'groupId': 4638005, 'roleCategory': 'Software Development', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'Full Stack Developer', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 0, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4638005.gif', 'wfhType': '0', 'companyDetail': {'name': 'Vakils Premedia', 'details': 'Vakils Premedia creates, manages and processes information through its integrated premedia services including packaging, prepress, page composition, colour management, data conversion, ePublishing, and cross media services, aimed at addressing enterprises\\ business communication needs. The company is equipped with best-in-class infrastructure and IT security systems. It is supported by professionals highly qualified in graphic design, software development and premedia technology. Vakils Premedia has all the modern encryption technologies and has complete data security as per ISO 27001:2005 standards. We have an experienced management team delivering IT and premedia services to customers in India, Australia, Europe, UK, USA and Asia. &lt;p&gt;&lt;/p&gt;', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': 'Experience with full-stack development frameworks and tools.', 'consent': False, 'jobId': '090426500106', 'showEducationAsPlaceholder': False, 'companyId': 2041992, 'brandingTags': [], 'functionalArea': 'Engineering - Software &amp; QA', 'fatFooter': {}, 'experienceText': '0-1 Yrs', 'referenceCode': '', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://www.vakilspremedia.com/career/', 'locationGids': ['134'], 'description': '&lt;p&gt;We are looking for a skilled Senior .NET Full-Stack Developer with 1 opening to join our team at Vakils Premedia Pvt. Ltd.&lt;/p&gt;&lt;br&gt;&lt;h3&gt;Roles and Responsibility&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Design, develop, and maintain high-quality software applications using .NET technologies.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Collaborate with cross-functional teams to identify and prioritize project requirements.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Develop and implement robust, scalable, and efficient codebases.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Troubleshoot and resolve technical issues efficiently.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Participate in code reviews and contribute to improving overall code quality.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Stay updated with industry trends and emerging technologies to enhance skills and knowledge.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;&lt;br&gt;&lt;h3&gt;Job Requirements&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Strong proficiency in .NET languages such as C#, VB.NET, and F#.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Experience with full-stack development frameworks and tools.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Excellent problem-solving skills and attention to detail.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Strong communication and teamwork skills.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Ability to work in an agile environment and adapt to changing priorities.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Familiarity with database management systems and querying languages.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;', 'staticCompanyName': 'vakils-premedia-jobs-careers-844541', 'industry': 'Recruitment / Staffing', 'staticUrl': 'https://www.naukri.com/job-listings-senior-net-full-stack-developer-vakils-premedia-pvt-ltd-mumbai-0-to-1-years-090426500106', 'title': 'Senior .NET Full-Stack Developer', 'walkIn': False, 'maximumExperience': 1, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 425, 'jobType': 'fulltime', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4638005.gif', 'microsite': False, 'createdDate': '2026-04-09 16:03:37', 'consultant': False, 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Mumbai', 'url': 'https://www.naukri.com/jobs-in-mumbai'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426500106&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': 'css', 'label': 'css'}, {'clickable': 'bootstrap', 'label': 'bootstrap'}, {'clickable': 'jquery', 'label': 'jquery'}, {'clickable': 'microservices', 'label': 'microservices'}, {'clickable': 'sql', 'label': 'sql'}, {'clickable': 'spring', 'label': 'spring'}, {'clickable': 'react.js', 'label': 'react.js'}, {'clickable': 'java', 'label': 'java'}, {'clickable': 'code review', 'label': 'code review'}, {'clickable': 'html', 'label': 'html'}, {'clickable': 'mysql', 'label': 'mysql'}, {'clickable': 'mongodb', 'label': 'mongodb'}, {'clickable': 'communication skills', 'label': 'communication skills'}, {'clickable': 'c#', 'label': 'c#'}, {'clickable': 'rest', 'label': 'rest'}, {'clickable': 'software development', 'label': 'software development'}, {'clickable': 'visual basic', 'label': 'vb'}, {'clickable': 'java script', 'label': 'javascript'}, {'clickable': 'sql server', 'label': 'sql server'}, {'clickable': '', 'label': 'angular'}, {'clickable': 'spring boot', 'label': 'spring boot'}, {'clickable': 'node.js', 'label': 'node.js'}, {'clickable': '', 'label': 'full stack'}, {'clickable': '.net', 'label': '.net'}, {'clickable': 'agile', 'label': 'agile'}, {'clickable': 'angularjs', 'label': 'angularjs'}, {'clickable': 'aws', 'label': 'aws'}, {'clickable': '', 'label': 'f#'}], 'preferred': []}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Senior .NET Full-Stack Developer', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4638005.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4638005.gif', 'jobId': '090426500106', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Vakils Premedia', 'isSaved': False, 'tagsAndSkills': 'css,bootstrap,jquery,microservices,sql,spring,react.js,java', 'placeholders': [{'type': 'experience', 'label': '0-1 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Mumbai'}], 'companyId': 2041992, 'jdURL': '/job-listings-senior-net-full-stack-developer-vakils-premedia-pvt-ltd-mumbai-0-to-1-years-090426500106', 'staticUrl': 'vakils-premedia-jobs-careers-844541', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/vakils-premedia-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 34, 'AggregateRating': '4.2', 'Title': 'Vakils Premedia Reviews by Employees'}, 'jobDescription': 'Experience with full-stack development frameworks and tools.', 'showMultipleApply': False, 'groupId': 4638005, 'isTopGroup': 0, 'createdDate': 1775730817000, 'mode': 'crawled', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-1 Yrs', 'minimumExperience': '0', 'maximumExperience': '1', 'applyByTime': '8:03 PM', 'companyApplyJob': True, 'walkinJob': False, 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426500106&amp;logstr=srprestapi', 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:51:59.616Z', 'url': 'https://www.nma.mobi/post/v4/job/090426500106?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;&lt;li&gt;Full-stack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles &lt;/li&gt;&lt;li&gt;Extensive experience working with most if not all the technologies listed below: Java Core with extensive hands-on experience with concurrent programming. &lt;/li&gt;&lt;li&gt;Spring Framework including Core, Integration, Batch, JDBC, Hibernate &lt;/li&gt;&lt;li&gt;Good development experience in Angular and Angular components &lt;/li&gt;&lt;li&gt;Good Knowledge in RxJS, Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent. &lt;/li&gt;&lt;li&gt;Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes) Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB &lt;/li&gt;&lt;li&gt;Familiarity with Linux environment including scripting skills SDLC/DevOps - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits.&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426909557?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['B.Tech / B.E. in Any Specialization'], 'pg': ['Any Postgraduate'], 'degreeCombination': 'ugorpgorppg', 'premiumProcessed': False, 'eduPlaceholderText': '', 'ppg': [], 'label': '', 'isSchool': None}, 'hideApplyButton': False, 'applyCount': 1988, 'groupId': 1186200, 'roleCategory': 'Software Development', 'mode': 'jp', 'tagLabels': [], 'jobRole': 'Full Stack Developer', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 1, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'wfhType': '0', 'companyDetail': {'name': 'Virtusa', 'websiteUrl': '', 'details': 'Virtusa Corporation (NASDAQ: VRTU) is a global information technology (IT) services company providing IT consulting, technology and outsourcing services. Using our enhanced global delivery model, innovative platforming approach and industry expertise, we provide cost-effective services that enable our clients to use IT to enhance business performance, accelerate time-to-market, increase productivity and improve customer service. We serve Global 2000 enterprises and the leading software vendors in communications &amp; technology; banking, financial services &amp; insurance; and media &amp; information industries. We build and sustain application platforms for our clients that create competitive advantage.&lt;br&gt;&lt;br&gt;&lt;br&gt;Founded in 1996 and headquartered in Massachusetts, we have offices and technology centers throughout the U.S., U.K. and Asia. Globally, Virtusa has been acknowledged and recognized by customers, industry associations and media among others. Some of the awards and recognitions include Dataquest-CMR €“ IT Best Employers Survey -2012 (Ranked No. 5), International Business Award €“ 2012(Stevie awards) , Britain€™s Top Employers- 2012, American Business Award€“ 2012,Boston Business Journal€™s Fastest Growing Public Companies, Global Services 100, Fintech 100, Sri Lanka National HRM and others.', 'address': 'Sy.No.115/Part,Plot No.10,Virtusa IT Park,Nanakram  guda Village,Serilingampally Mandal  , Hyderabad, Telangana, India', 'media': {'ppt': [], 'video': [], 'photos': []}, 'hiringFor': '', 'isKycSuccessful': True}, 'jobIconType': '', 'shortDescription': 'Experienced full-stack developer skilled in Java concurrent programming, Spring Framework, Angular, RxJS, micro-frontend architecture, Redis, Docker, Kubernetes, Oracle and MongoDB databases|Design and develop scalable, maintainable applications using OOP principles; work with cloud technologies, microservices, distributed caching, and DevOps tools like Git, Jenkins, and SonarQube', 'consent': False, 'jobId': '090426909557', 'showEducationAsPlaceholder': False, 'companyId': 1354, 'brandingTags': [], 'functionalArea': 'Engineering - Software &amp; QA', 'fatFooter': {}, 'experienceText': '0-2 Yrs', 'referenceCode': 'CREQ252195', 'vacancy': 0, 'template': '', 'locationGids': ['139'], 'description': '&lt;ul&gt;&lt;li&gt;Full-stack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles &lt;/li&gt;&lt;li&gt;Extensive experience working with most if not all the technologies listed below: Java Core with extensive hands-on experience with concurrent programming. &lt;/li&gt;&lt;li&gt;Spring Framework including Core, Integration, Batch, JDBC, Hibernate &lt;/li&gt;&lt;li&gt;Good development experience in Angular and Angular components &lt;/li&gt;&lt;li&gt;Good Knowledge in RxJS, Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent. &lt;/li&gt;&lt;li&gt;Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes) Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB &lt;/li&gt;&lt;li&gt;Familiarity with Linux environment including scripting skills SDLC/DevOps - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits.&lt;/li&gt;&lt;/ul&gt;', 'staticCompanyName': 'virtusa-jobs-careers-1354', 'industry': 'Banking', 'staticUrl': 'https://www.naukri.com/job-listings-java-fullstack-developer-virtusa-consulting-services-pvt-ltd-pune-0-to-2-years-090426909557', 'title': 'Java FullStack Developer', 'walkIn': False, 'maximumExperience': 2, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 2924, 'jobType': 'fulltime', 'companyPageUrl': 'virtusa-overview-1186200', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'microsite': False, 'createdDate': '2026-04-09 10:59:04', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Pune', 'url': 'https://www.naukri.com/jobs-in-pune'}], 'keySkills': {'other': [{'clickable': '', 'label': 'kubernetes'}, {'clickable': 'oracle', 'label': 'oracle'}, {'clickable': '', 'label': 'full stack developer'}, {'clickable': '', 'label': 'bitbucket'}, {'clickable': 'hibernate framework', 'label': 'hibernate'}, {'clickable': 'caching', 'label': 'caching'}, {'clickable': 'redis', 'label': 'redis'}, {'clickable': 'nosql', 'label': 'nosql'}, {'clickable': 'microservices', 'label': 'microservices'}, {'clickable': 'docker', 'label': 'docker'}, {'clickable': 'spring framework', 'label': 'spring framework'}, {'clickable': '', 'label': 'angular'}, {'clickable': 'scripting', 'label': 'scripting'}, {'clickable': 'git', 'label': 'git'}, {'clickable': 'devops', 'label': 'devops'}, {'clickable': 'linux', 'label': 'linux'}, {'clickable': '', 'label': 'full stack'}, {'clickable': 'jenkins', 'label': 'jenkins'}, {'clickable': 'cloud computing', 'label': 'cloud computing'}, {'clickable': 'sdlc', 'label': 'sdlc'}, {'clickable': 'mongodb', 'label': 'mongodb'}, {'clickable': 'programming', 'label': 'programming'}, {'clickable': 'jira', 'label': 'jira'}], 'preferred': [{'clickable': 'java', 'label': 'java'}]}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Java FullStack Developer', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'jobId': '090426909557', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Virtusa', 'isSaved': False, 'tagsAndSkills': 'java,kubernetes,oracle,full stack developer,bitbucket,hibernate,caching,redis', 'placeholders': [{'type': 'experience', 'label': '0-2 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Pune'}], 'companyId': 1354, 'jdURL': '/job-listings-java-fullstack-developer-virtusa-consulting-services-pvt-ltd-pune-0-to-2-years-090426909557', 'staticUrl': 'virtusa-jobs-careers-1354', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/virtusa-consulting-services-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 6077, 'AggregateRating': '3.7', 'Title': 'Virtusa Consulting Services Reviews by Employees'}, 'jobDescription': 'Full-stack developer with experience in designing and developing robust,scalable,and maintainable applications applying Object Oriented Design principles&lt;br&gt;&lt;br&gt;Spring Framework including Core,Integration,Batch,JDBC,Hibernate&lt;br&gt;&lt;br&gt;Good Knowledge in RxJS,Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent', 'showMultipleApply': False, 'groupId': 1186200, 'isTopGroup': 0, 'createdDate': 1775712544186, 'mode': 'jp', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-2 Yrs', 'minimumExperience': '0', 'maximumExperience': '2', 'applyByTime': '2:59 PM', 'companyApplyJob': False, 'walkinJob': False, 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:52:00.013Z', 'url': 'https://www.nma.mobi/post/v4/job/090426909557?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>Intern</t>
+  </si>
+  <si>
+    <t>&lt;div&gt; &lt;b&gt; &lt;span&gt; About Us &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; Automation Anywhere is the leader in Agentic Process Automation (APA), transforming how work gets done with AI-powered automation. Its APA system, built on the industry s first Process Reasoning Engine (PRE) and specialized AI agents, combines process discovery, RPA, end-to-end orchestration, document processing, and analytics all delivered with enterprise-grade security and governance. Guided by its vision to fuel the future of work, Automation Anywhere helps organizations worldwide boost productivity, accelerate growth, and unleash human potential. &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; We are looking for a motivated and enthusiastic  &lt;b&gt; AI/ML - Python Intern &lt;/b&gt;  to support the development of automation and intelligence solutions. This role is ideal for students or early-career individuals who are eager to learn, gain hands-on experience, and contribute to real-world AI and automation projects under the guidance of senior engineers. &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;b&gt; Key Responsibilities &lt;/b&gt; &lt;/span&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Assist in designing and developing basic AI-driven automation components under the supervision of senior team members. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Work with  &lt;b&gt; Python  &lt;/b&gt; to support scripting, data preprocessing, and simple integration tasks. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Support model development activities such as data cleaning, feature extraction, and experimenting with existing machine learning models. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Help in conducting research on AI/ML techniques, tools, and large language models (LLMs) to support ongoing projects. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Collaborate with cross-functional teams to understand requirements and contribute to solution prototypes. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Participate in testing, troubleshooting, and documenting AI solutions, including creating user guides and internal notes. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Assist in maintaining existing AI tools and workflows by monitoring performance and reporting issues. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Stay engaged with emerging trends in AI, ML, and GenAI to contribute fresh ideas to the team. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;b&gt; Required Qualifications &lt;/b&gt; &lt;/span&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Recently completed a Bachelor s or Master s degree in Computer Science, Engineering, Data Science, or a related field. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Basic proficiency in  &lt;b&gt; Python  &lt;/b&gt; and familiarity with data processing libraries (e.g., Pandas, NumPy). &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Foundational understanding of machine learning concepts and algorithms. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Interest in natural language processing and large language models. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Strong problem-solving skills and attention to detail. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Good communication skills and ability to work collaboratively in a team environment. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;b&gt; Preferred &lt;/b&gt; &lt;/span&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;span&gt; &lt;span&gt; Active GitHub repo. &lt;/span&gt; &lt;/span&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;div&gt; &lt;div&gt; &lt;div&gt; &lt;div&gt; &lt;/div&gt; &lt;/div&gt; &lt;/div&gt; &lt;/div&gt; &lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426506326?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['Any Postgraduate'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 29, 'groupId': 4581857, 'roleCategory': 'Quality Assurance and Testing', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'Blockchain Quality Assurance Engineer', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 0, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4581857.gif', 'wfhType': '0', 'companyDetail': {'name': 'Automation Anywhere', 'details': 'Automation Anywhere is the leader in intelligent automation solutions that put AI to work across every aspect of an organization. The company’s Automation Success Platform is infused with generative AI and offers process discovery, RPA, end-to-end process orchestration, document processing, and analytics, with a security and governance-first approach. Automation Anywhere empowers organizations worldwide to unleash productivity gains, drive innovation, improve customer service and accelerate business growth.', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': '. We are looking for a motivated and enthusiastic AI / ML - Python Intern to support the development of automation and intelligence solutions|Recently completed a Bachelor s or Master s degree in Computer Science,Engineering,Data Science,or a related field', 'consent': False, 'jobId': '090426506326', 'showEducationAsPlaceholder': False, 'companyId': 1804792, 'brandingTags': [], 'functionalArea': 'Engineering - Software &amp; QA', 'fatFooter': {}, 'experienceText': '0-5 Yrs', 'referenceCode': 'JR1275', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://automationanywhere.wd5.myworkdayjobs.com/en-US/AutomationAnywhereJobs/job/Bengaluru-India/Intern_JR1275', 'locationGids': ['97'], 'description': '&lt;div&gt; &lt;b&gt; &lt;span&gt; About Us &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; Automation Anywhere is the leader in Agentic Process Automation (APA), transforming how work gets done with AI-powered automation. Its APA system, built on the industry s first Process Reasoning Engine (PRE) and specialized AI agents, combines process discovery, RPA, end-to-end orchestration, document processing, and analytics all delivered with enterprise-grade security and governance. Guided by its vision to fuel the future of work, Automation Anywhere helps organizations worldwide boost productivity, accelerate growth, and unleash human potential. &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; We are looking for a motivated and enthusiastic  &lt;b&gt; AI/ML - Python Intern &lt;/b&gt;  to support the development of automation and intelligence solutions. This role is ideal for students or early-career individuals who are eager to learn, gain hands-on experience, and contribute to real-world AI and automation projects under the guidance of senior engineers. &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;b&gt; Key Responsibilities &lt;/b&gt; &lt;/span&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Assist in designing and developing basic AI-driven automation components under the supervision of senior team members. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Work with  &lt;b&gt; Python  &lt;/b&gt; to support scripting, data preprocessing, and simple integration tasks. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Support model development activities such as data cleaning, feature extraction, and experimenting with existing machine learning models. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Help in conducting research on AI/ML techniques, tools, and large language models (LLMs) to support ongoing projects. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Collaborate with cross-functional teams to understand requirements and contribute to solution prototypes. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Participate in testing, troubleshooting, and documenting AI solutions, including creating user guides and internal notes. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Assist in maintaining existing AI tools and workflows by monitoring performance and reporting issues. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Stay engaged with emerging trends in AI, ML, and GenAI to contribute fresh ideas to the team. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;b&gt; Required Qualifications &lt;/b&gt; &lt;/span&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Recently completed a Bachelor s or Master s degree in Computer Science, Engineering, Data Science, or a related field. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Basic proficiency in  &lt;b&gt; Python  &lt;/b&gt; and familiarity with data processing libraries (e.g., Pandas, NumPy). &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Foundational understanding of machine learning concepts and algorithms. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Interest in natural language processing and large language models. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Strong problem-solving skills and attention to detail. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; Good communication skills and ability to work collaboratively in a team environment. &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;span&gt; &lt;b&gt; Preferred &lt;/b&gt; &lt;/span&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;span&gt; &lt;span&gt; Active GitHub repo. &lt;/span&gt; &lt;/span&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;div&gt; &lt;div&gt; &lt;div&gt; &lt;div&gt; &lt;/div&gt; &lt;/div&gt; &lt;/div&gt; &lt;/div&gt; &lt;/div&gt;', 'staticCompanyName': 'automation-anywhere-jobs-careers-96913', 'industry': 'IT Services &amp; Consulting', 'staticUrl': 'https://www.naukri.com/job-listings-intern-automation-anywhere-software-pvt-ltd-bengaluru-0-to-5-years-090426506326', 'title': 'Intern', 'walkIn': False, 'maximumExperience': 5, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 121, 'jobType': 'internship', 'internshipInfo': {'amount': 'Unpaid', 'duration': 'No fixed duration', 'internshipExactStartDate': 'Starts in 1-3 months', 'internshipApplyByDate': None, 'perksAndBenefits': None, 'currency': 'INR'}, 'companyPageUrl': 'automation-anywhere-overview-4581857', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4581857.gif', 'microsite': False, 'internshipDuration': 'No fixed ', 'createdDate': '2026-04-09 18:37:43', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4581857.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Bengaluru', 'url': 'https://www.naukri.com/jobs-in-bangalore'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426506326&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': 'process automation', 'label': 'Process automation'}, {'clickable': 'automation', 'label': 'Automation'}, {'clickable': '', 'label': 'Intern'}, {'clickable': 'machine learning', 'label': 'Machine learning'}, {'clickable': 'data processing', 'label': 'Data processing'}, {'clickable': 'trouble shooting', 'label': 'Troubleshooting'}, {'clickable': 'analytical', 'label': 'Analytics'}, {'clickable': 'monitoring', 'label': 'Monitoring'}, {'clickable': 'python', 'label': 'Python'}], 'preferred': []}, 'salaryDetail': {'hideSalary': False, 'currency': 'INR', 'label': 'Unpaid'}, 'board': '1', 'basicInfo': {'title': 'Intern', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4581857.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4581857.gif', 'jobId': '090426506326', 'jobType': 'internship', 'currency': 'INR', 'footerPlaceholderLabel': 'Starts in 1-3 months', 'footerPlaceholderColor': 'green', 'companyName': 'Automation Anywhere', 'isSaved': False, 'placeholders': [{'type': 'duration', 'label': 'No fixed duration'}, {'type': 'salary', 'label': 'Unpaid'}, {'type': 'location', 'label': 'Bengaluru'}], 'companyId': 1804792, 'jdURL': '/job-listings-intern-automation-anywhere-software-pvt-ltd-bengaluru-0-to-5-years-090426506326', 'staticUrl': 'automation-anywhere-jobs-careers-96913', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/automation-anywhere-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 174, 'AggregateRating': '3.8', 'Title': 'Automation Anywhere Reviews by Employees'}, 'jobDescription': ' . We are looking for a motivated and enthusiastic AI / ML - Python Intern to support the development of automation and intelligence solutions&lt;br&gt;&lt;br&gt;Recently completed a Bachelor s or Master s degree in Computer Science,Engineering,Data Science,or a related field', 'showMultipleApply': False, 'groupId': 4581857, 'isTopGroup': 0, 'createdDate': 0, 'mode': 'crawled', 'board': '1', 'companyApplyJob': True, 'walkinJob': False, 'saved': False}, 'scrapedAt': '2026-04-10T09:52:00.143Z', 'url': 'https://www.nma.mobi/post/v4/job/090426506326?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>Graduate Trainee - Python, Gen AI/ML</t>
+  </si>
+  <si>
+    <t>The Calix platform enables Communication Service Providers (CSPs) of all sizes to transform and future-proof their businesses. Through real-time data, automation, and actionable insights delivered via Calix One our cloud-first, AI-powered platform CSPs can simplify operations, collapse cost, and accelerate innovation. Calix One brings together the automation of everything and the experience of one, empowering customers to deliver differentiated subscriber experiences while driving acquisition, loyalty, and revenue growth. This is the Calix mission: to enable CSPs of all sizes to simplify, innovate, and grow, strengthening both their businesses and the communities they serve. &lt;br /&gt; &lt;br /&gt;We re at the forefront of a once in a generational change in the broadband industry. Join us as we innovate, help our customers reach their potential, and connect underserved communities with unrivaled digital experiences.&lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;div&gt;At Calix, interns are treated as&lt;span&gt; &lt;/span&gt; &lt;b&gt;full contributors&lt;/b&gt;, working on meaningful, production relevant problems with real business impact, supported by strong mentorship and a collaborative engineering culture.&lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt;We are looking for a highly motivated&lt;span&gt; &lt;/span&gt; &lt;b&gt;AI / Machine Learning Intern&lt;/b&gt; to join the Calix AI/ML team. In this role, you will work on&lt;span&gt; &lt;/span&gt; &lt;b&gt;real-world AI/ML and Generative AI problems&lt;/b&gt;, contributing to models, pipelines, and intelligent systems that power next generation Calix products.&lt;/div&gt; &lt;div&gt;This is&lt;span&gt; &lt;/span&gt; &lt;b&gt;not a shadowing role&lt;/b&gt; you will design, build, experiment, and ship alongside experienced engineers and data scientists.&lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;b&gt;Key Responsibilities:&lt;/b&gt; &lt;ul&gt; &lt;li&gt;Design, implement, and experiment with&lt;span&gt; &lt;/span&gt; &lt;b&gt;machine learning and deep learning models&lt;/b&gt; for product use cases&lt;/li&gt; &lt;li&gt;Work on&lt;span&gt; &lt;/span&gt; &lt;b&gt;end to end ML workflows&lt;/b&gt;, including:&lt;ul&gt; &lt;li&gt;Data preprocessing and feature engineering&lt;/li&gt; &lt;li&gt;Model training, evaluation, and optimization&lt;/li&gt; &lt;li&gt;Experiment tracking and result analysis&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Contribute to&lt;span&gt; &lt;/span&gt; &lt;b&gt;Generative AI and agentic systems&lt;/b&gt;, including:&lt;ul&gt; &lt;li&gt;LLM based workflows&lt;/li&gt; &lt;li&gt;AI agents, orchestration, and prompt engineering&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Develop prototypes and proof of concepts that can evolve into production features&lt;/li&gt; &lt;li&gt;Write clean, maintainable, and well documented&lt;span&gt; &lt;/span&gt; &lt;b&gt;Python code&lt;/b&gt; &lt;/li&gt; &lt;li&gt;Collaborate with cross functional teams (engineering, product, platform)&lt;/li&gt; &lt;li&gt;Present findings, demos, and outcomes to the broader team&lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;b&gt;Required Qualifications:&lt;/b&gt; &lt;ul&gt; &lt;li&gt;Currently pursuing or recently completed a&lt;span&gt; &lt;/span&gt; &lt;b&gt;Bachelor s or Master s degree&lt;/b&gt; in:&lt;ul&gt; &lt;li&gt;Computer Science&lt;/li&gt; &lt;li&gt;Artificial Intelligence&lt;/li&gt; &lt;li&gt;Machine Learning&lt;/li&gt; &lt;li&gt;Data Science&lt;/li&gt; &lt;li&gt;Or a related engineering discipline&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt; &lt;b&gt;Strong Python programming skills&lt;/b&gt; &lt;/li&gt; &lt;li&gt;Solid understanding of&lt;span&gt; &lt;/span&gt; &lt;b&gt;core AI/ML concepts&lt;/b&gt;, including:&lt;ul&gt; &lt;li&gt; &lt;div&gt;Multi Agent Systems&lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt;MCP server and tool calling&lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt;Supervised and unsupervised learning&lt;/div&gt; &lt;/li&gt; &lt;li&gt;Model evaluation and validation&lt;/li&gt; &lt;li&gt;Feature engineering basics&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Familiarity with common AI/ML libraries/frameworks such as:&lt;ul&gt; &lt;li&gt;LangGraph, CrewAI, Google ADK, Microsoft AutoGen, PyTorch, TensorFlow, or scikit learn&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Comfortable working in a&lt;span&gt; &lt;/span&gt; &lt;b&gt;Linux/Unix environment&lt;/b&gt; &lt;/li&gt; &lt;li&gt;Experience using&lt;span&gt; &lt;/span&gt; &lt;b&gt;Git or other version control systems&lt;/b&gt; &lt;/li&gt; &lt;/ul&gt; &lt;b&gt;Added Advantage (Nice to Have):&lt;/b&gt; &lt;ul&gt; &lt;li&gt;Hands on project experience in:&lt;ul&gt; &lt;li&gt;Machine Learning / Deep Learning&lt;/li&gt; &lt;li&gt;Generative AI or LLM based systems&lt;/li&gt; &lt;li&gt;Agentic AI or multi agent frameworks&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Exposure to:&lt;ul&gt; &lt;li&gt;NLP, time series, recommendation systems, or anomaly detection&lt;/li&gt; &lt;li&gt;Model deployment concepts or MLOps fundamentals&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Experience with:&lt;ul&gt; &lt;li&gt;Cloud platforms (AWS, GCP, or Azure)&lt;/li&gt; &lt;li&gt;Data processing frameworks (e.g., Spark)&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Strong problem solving mindset and curiosity to explore new AI techniques&lt;/li&gt; &lt;/ul&gt; &lt;b&gt;What You ll Gain:&lt;/b&gt; &lt;ul&gt; &lt;li&gt;Hands on experience working on&lt;span&gt; &lt;/span&gt; &lt;b&gt;production grade AI systems&lt;/b&gt; &lt;/li&gt; &lt;li&gt;Exposure to&lt;span&gt; &lt;/span&gt; &lt;b&gt;modern AI stacks&lt;/b&gt;, including generative AI and agents&lt;/li&gt; &lt;li&gt;Mentorship from senior engineers and AI practitioners&lt;/li&gt; &lt;li&gt;Opportunity to make a&lt;span&gt; &lt;/span&gt; &lt;b&gt;measurable impact&lt;/b&gt; on Calix products&lt;/li&gt; &lt;li&gt;A strong foundation for a full time role in a product focused AI/ML team&lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;b&gt;Who Should Apply:&lt;/b&gt; &lt;div&gt;If you enjoy building things, experimenting with models, and turning ideas into working AI systems and you want to learn how AI is applied at scale in a real product company this internship is for you.&lt;/div&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426502178?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['Any Postgraduate'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 131, 'groupId': 4957066, 'roleCategory': 'Software Development', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'Data Platform Engineer', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 0, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4957066.gif', 'wfhType': '0', 'companyDetail': {'name': 'Calix', 'details': 'Innovative communications service providers rely on Calix platforms to help them master and monetize the complex infrastructure between their subscribers and the cloud. Calix is the leading global provider of the cloud and software platforms, systems, and services required to deliver the unified access network and smart premises of tomorrow. Our platforms and services help our customers build next generation networks by embracing a DevOps operating model, optimize the subscriber experience by leveraging big data analytics, and turn the complexity of the smart home and business into new revenue streams.', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': '. At Calix,interns are treated as. full contributors,working on meaningful,production relevant problems with real business impact,supported by strong mentorship and a collaborative engineering culture.  . We are looking for a highly motivated. AI / Machine Learning Intern to join the Calix AI / ML team|Hands on experience working on. production grade AI systems .', 'consent': False, 'jobId': '090426502178', 'showEducationAsPlaceholder': False, 'companyId': 5507094, 'brandingTags': [], 'functionalArea': 'Engineering - Software &amp; QA', 'fatFooter': {}, 'experienceText': '0-1 Yrs', 'referenceCode': 'R-11594', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://calix.wd1.myworkdayjobs.com/en-US/ExternalInternational/job/Bangalore/Graduate-Trainee---Python--Gen-AI-ML_R-11594', 'locationGids': ['97'], 'description': 'The Calix platform enables Communication Service Providers (CSPs) of all sizes to transform and future-proof their businesses. Through real-time data, automation, and actionable insights delivered via Calix One our cloud-first, AI-powered platform CSPs can simplify operations, collapse cost, and accelerate innovation. Calix One brings together the automation of everything and the experience of one, empowering customers to deliver differentiated subscriber experiences while driving acquisition, loyalty, and revenue growth. This is the Calix mission: to enable CSPs of all sizes to simplify, innovate, and grow, strengthening both their businesses and the communities they serve. &lt;br /&gt; &lt;br /&gt;We re at the forefront of a once in a generational change in the broadband industry. Join us as we innovate, help our customers reach their potential, and connect underserved communities with unrivaled digital experiences.&lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;div&gt;At Calix, interns are treated as&lt;span&gt; &lt;/span&gt; &lt;b&gt;full contributors&lt;/b&gt;, working on meaningful, production relevant problems with real business impact, supported by strong mentorship and a collaborative engineering culture.&lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt;We are looking for a highly motivated&lt;span&gt; &lt;/span&gt; &lt;b&gt;AI / Machine Learning Intern&lt;/b&gt; to join the Calix AI/ML team. In this role, you will work on&lt;span&gt; &lt;/span&gt; &lt;b&gt;real-world AI/ML and Generative AI problems&lt;/b&gt;, contributing to models, pipelines, and intelligent systems that power next generation Calix products.&lt;/div&gt; &lt;div&gt;This is&lt;span&gt; &lt;/span&gt; &lt;b&gt;not a shadowing role&lt;/b&gt; you will design, build, experiment, and ship alongside experienced engineers and data scientists.&lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;b&gt;Key Responsibilities:&lt;/b&gt; &lt;ul&gt; &lt;li&gt;Design, implement, and experiment with&lt;span&gt; &lt;/span&gt; &lt;b&gt;machine learning and deep learning models&lt;/b&gt; for product use cases&lt;/li&gt; &lt;li&gt;Work on&lt;span&gt; &lt;/span&gt; &lt;b&gt;end to end ML workflows&lt;/b&gt;, including:&lt;ul&gt; &lt;li&gt;Data preprocessing and feature engineering&lt;/li&gt; &lt;li&gt;Model training, evaluation, and optimization&lt;/li&gt; &lt;li&gt;Experiment tracking and result analysis&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Contribute to&lt;span&gt; &lt;/span&gt; &lt;b&gt;Generative AI and agentic systems&lt;/b&gt;, including:&lt;ul&gt; &lt;li&gt;LLM based workflows&lt;/li&gt; &lt;li&gt;AI agents, orchestration, and prompt engineering&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Develop prototypes and proof of concepts that can evolve into production features&lt;/li&gt; &lt;li&gt;Write clean, maintainable, and well documented&lt;span&gt; &lt;/span&gt; &lt;b&gt;Python code&lt;/b&gt; &lt;/li&gt; &lt;li&gt;Collaborate with cross functional teams (engineering, product, platform)&lt;/li&gt; &lt;li&gt;Present findings, demos, and outcomes to the broader team&lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;b&gt;Required Qualifications:&lt;/b&gt; &lt;ul&gt; &lt;li&gt;Currently pursuing or recently completed a&lt;span&gt; &lt;/span&gt; &lt;b&gt;Bachelor s or Master s degree&lt;/b&gt; in:&lt;ul&gt; &lt;li&gt;Computer Science&lt;/li&gt; &lt;li&gt;Artificial Intelligence&lt;/li&gt; &lt;li&gt;Machine Learning&lt;/li&gt; &lt;li&gt;Data Science&lt;/li&gt; &lt;li&gt;Or a related engineering discipline&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt; &lt;b&gt;Strong Python programming skills&lt;/b&gt; &lt;/li&gt; &lt;li&gt;Solid understanding of&lt;span&gt; &lt;/span&gt; &lt;b&gt;core AI/ML concepts&lt;/b&gt;, including:&lt;ul&gt; &lt;li&gt; &lt;div&gt;Multi Agent Systems&lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt;MCP server and tool calling&lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt;Supervised and unsupervised learning&lt;/div&gt; &lt;/li&gt; &lt;li&gt;Model evaluation and validation&lt;/li&gt; &lt;li&gt;Feature engineering basics&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Familiarity with common AI/ML libraries/frameworks such as:&lt;ul&gt; &lt;li&gt;LangGraph, CrewAI, Google ADK, Microsoft AutoGen, PyTorch, TensorFlow, or scikit learn&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Comfortable working in a&lt;span&gt; &lt;/span&gt; &lt;b&gt;Linux/Unix environment&lt;/b&gt; &lt;/li&gt; &lt;li&gt;Experience using&lt;span&gt; &lt;/span&gt; &lt;b&gt;Git or other version control systems&lt;/b&gt; &lt;/li&gt; &lt;/ul&gt; &lt;b&gt;Added Advantage (Nice to Have):&lt;/b&gt; &lt;ul&gt; &lt;li&gt;Hands on project experience in:&lt;ul&gt; &lt;li&gt;Machine Learning / Deep Learning&lt;/li&gt; &lt;li&gt;Generative AI or LLM based systems&lt;/li&gt; &lt;li&gt;Agentic AI or multi agent frameworks&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Exposure to:&lt;ul&gt; &lt;li&gt;NLP, time series, recommendation systems, or anomaly detection&lt;/li&gt; &lt;li&gt;Model deployment concepts or MLOps fundamentals&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Experience with:&lt;ul&gt; &lt;li&gt;Cloud platforms (AWS, GCP, or Azure)&lt;/li&gt; &lt;li&gt;Data processing frameworks (e.g., Spark)&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Strong problem solving mindset and curiosity to explore new AI techniques&lt;/li&gt; &lt;/ul&gt; &lt;b&gt;What You ll Gain:&lt;/b&gt; &lt;ul&gt; &lt;li&gt;Hands on experience working on&lt;span&gt; &lt;/span&gt; &lt;b&gt;production grade AI systems&lt;/b&gt; &lt;/li&gt; &lt;li&gt;Exposure to&lt;span&gt; &lt;/span&gt; &lt;b&gt;modern AI stacks&lt;/b&gt;, including generative AI and agents&lt;/li&gt; &lt;li&gt;Mentorship from senior engineers and AI practitioners&lt;/li&gt; &lt;li&gt;Opportunity to make a&lt;span&gt; &lt;/span&gt; &lt;b&gt;measurable impact&lt;/b&gt; on Calix products&lt;/li&gt; &lt;li&gt;A strong foundation for a full time role in a product focused AI/ML team&lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;b&gt;Who Should Apply:&lt;/b&gt; &lt;div&gt;If you enjoy building things, experimenting with models, and turning ideas into working AI systems and you want to learn how AI is applied at scale in a real product company this internship is for you.&lt;/div&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt;', 'staticCompanyName': 'calix-jobs-careers-5507094', 'industry': 'IT Services &amp; Consulting', 'staticUrl': 'https://www.naukri.com/job-listings-graduate-trainee-python-gen-ai-ml-calix-bengaluru-0-to-1-years-090426502178', 'title': 'Graduate Trainee - Python, Gen AI/ML', 'walkIn': False, 'maximumExperience': 1, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 443, 'jobType': 'internship', 'internshipInfo': {'amount': 'Unpaid', 'duration': 'No fixed duration', 'internshipExactStartDate': 'Starts in 1-3 months', 'internshipApplyByDate': None, 'perksAndBenefits': None, 'currency': 'INR'}, 'companyPageUrl': 'calix-overview-4957066', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4957066.gif', 'microsite': False, 'internshipDuration': 'No fixed ', 'createdDate': '2026-04-09 16:27:25', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4957066.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Bengaluru', 'url': 'https://www.naukri.com/jobs-in-bangalore'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426502178&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': 'unix', 'label': 'Unix'}, {'clickable': 'automation', 'label': 'Automation'}, {'clickable': 'version control', 'label': 'Version control'}, {'clickable': 'linux', 'label': 'Linux'}, {'clickable': 'gcp', 'label': 'GCP'}, {'clickable': 'artificial intelligence', 'label': 'Artificial Intelligence'}, {'clickable': 'machine learning', 'label': 'Machine learning'}, {'clickable': 'internship', 'label': 'Internship'}, {'clickable': 'python', 'label': 'Python'}], 'preferred': []}, 'salaryDetail': {'hideSalary': False, 'currency': 'INR', 'label': 'Unpaid'}, 'board': '1', 'basicInfo': {'title': 'Graduate Trainee - Python, Gen AI/ML', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4957066.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/4957066.gif', 'jobId': '090426502178', 'jobType': 'internship', 'currency': 'INR', 'footerPlaceholderLabel': 'Starts in 1-3 months', 'footerPlaceholderColor': 'green', 'companyName': 'Calix', 'isSaved': False, 'placeholders': [{'type': 'duration', 'label': 'No fixed duration'}, {'type': 'salary', 'label': 'Unpaid'}, {'type': 'location', 'label': 'Bengaluru'}], 'companyId': 5507094, 'jdURL': '/job-listings-graduate-trainee-python-gen-ai-ml-calix-bengaluru-0-to-1-years-090426502178', 'staticUrl': 'calix-jobs-careers-5507094', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/calix-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 144, 'AggregateRating': '4.0', 'Title': 'Calix Reviews by Employees'}, 'jobDescription': ' . At Calix,interns are treated as. full contributors,working on meaningful,production relevant problems with real business impact,supported by strong mentorship and a collaborative engineering culture.  . We are looking for a highly motivated. AI / Machine Learning Intern to join the Calix AI / ML team&lt;br&gt;&lt;br&gt;Hands on experience working on. production grade AI systems .', 'showMultipleApply': False, 'groupId': 4957066, 'isTopGroup': 0, 'createdDate': 0, 'mode': 'crawled', 'board': '1', 'companyApplyJob': True, 'walkinJob': False, 'saved': False}, 'scrapedAt': '2026-04-10T09:52:00.243Z', 'url': 'https://www.nma.mobi/post/v4/job/090426502178?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>Java Full Stack Developer</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt; &lt;li&gt;  Full-stack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles Extensive experience working with most if not all the technologies listed below:  &lt;/li&gt; &lt;li&gt;  Java Core with extensive hands-on experience with concurrent programming. Spring Framework including Core, Integration, Batch, JDBC, Hibernate  &lt;/li&gt; &lt;li&gt;  Good development experience in Angular and Angular components  &lt;/li&gt; &lt;li&gt;  Good Knowledge in RxJS, Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent.  &lt;/li&gt; &lt;li&gt;  Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes)  &lt;/li&gt; &lt;li&gt;  Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB  &lt;/li&gt; &lt;li&gt;  Familiarity with Linux environment including scripting skills  &lt;/li&gt; &lt;li&gt;  SDLC/Dev Ops - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits  &lt;/li&gt; &lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426915783?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['B.Tech / B.E. in Any Specialization'], 'pg': ['Any Postgraduate'], 'degreeCombination': 'ugorpgorppg', 'premiumProcessed': False, 'eduPlaceholderText': '', 'ppg': [], 'label': '', 'isSchool': None}, 'hideApplyButton': False, 'applyCount': 1343, 'groupId': 1186200, 'roleCategory': 'Software Development', 'mode': 'jp', 'tagLabels': [], 'jobRole': 'Full Stack Developer', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 1, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'wfhType': '0', 'companyDetail': {'name': 'Virtusa', 'websiteUrl': '', 'details': 'Virtusa Corporation (NASDAQ: VRTU) is a global information technology (IT) services company providing IT consulting, technology and outsourcing services. Using our enhanced global delivery model, innovative platforming approach and industry expertise, we provide cost-effective services that enable our clients to use IT to enhance business performance, accelerate time-to-market, increase productivity and improve customer service. We serve Global 2000 enterprises and the leading software vendors in communications &amp; technology; banking, financial services &amp; insurance; and media &amp; information industries. We build and sustain application platforms for our clients that create competitive advantage.&lt;br&gt;&lt;br&gt;&lt;br&gt;Founded in 1996 and headquartered in Massachusetts, we have offices and technology centers throughout the U.S., U.K. and Asia. Globally, Virtusa has been acknowledged and recognized by customers, industry associations and media among others. Some of the awards and recognitions include Dataquest-CMR €“ IT Best Employers Survey -2012 (Ranked No. 5), International Business Award €“ 2012(Stevie awards) , Britain€™s Top Employers- 2012, American Business Award€“ 2012,Boston Business Journal€™s Fastest Growing Public Companies, Global Services 100, Fintech 100, Sri Lanka National HRM and others.', 'address': 'Sy.No.115/Part,Plot No.10,Virtusa IT Park,Nanakram  guda Village,Serilingampally Mandal  , Hyderabad, Telangana, India', 'media': {'ppt': [], 'video': [], 'photos': []}, 'hiringFor': '', 'isKycSuccessful': True}, 'jobIconType': '', 'shortDescription': 'Experienced full-stack developer skilled in Java Core concurrent programming, Spring Framework, Angular, RxJS, micro-frontend architecture, Redis caching, Docker, Kubernetes, Oracle and MongoDB databases, Linux scripting, and CI/CD tools like Jenkins and Git|Design and develop scalable, maintainable applications using OOP principles; work with microservices, cloud technologies, and DevOps pipelines', 'consent': False, 'jobId': '090426915783', 'showEducationAsPlaceholder': False, 'companyId': 1354, 'brandingTags': [], 'functionalArea': 'Engineering - Software &amp; QA', 'fatFooter': {}, 'experienceText': '0-1 Yrs', 'referenceCode': 'CREQ252194', 'vacancy': 0, 'template': '', 'locationGids': ['139'], 'description': '&lt;ul&gt; &lt;li&gt;  Full-stack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles Extensive experience working with most if not all the technologies listed below:  &lt;/li&gt; &lt;li&gt;  Java Core with extensive hands-on experience with concurrent programming. Spring Framework including Core, Integration, Batch, JDBC, Hibernate  &lt;/li&gt; &lt;li&gt;  Good development experience in Angular and Angular components  &lt;/li&gt; &lt;li&gt;  Good Knowledge in RxJS, Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent.  &lt;/li&gt; &lt;li&gt;  Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes)  &lt;/li&gt; &lt;li&gt;  Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB  &lt;/li&gt; &lt;li&gt;  Familiarity with Linux environment including scripting skills  &lt;/li&gt; &lt;li&gt;  SDLC/Dev Ops - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits  &lt;/li&gt; &lt;/ul&gt;', 'staticCompanyName': 'virtusa-jobs-careers-1354', 'industry': 'Banking', 'staticUrl': 'https://www.naukri.com/job-listings-java-full-stack-developer-virtusa-consulting-services-pvt-ltd-pune-0-to-1-years-090426915783', 'title': 'Java Full Stack Developer', 'walkIn': False, 'maximumExperience': 1, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 1990, 'jobType': 'fulltime', 'companyPageUrl': 'virtusa-overview-1186200', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'microsite': False, 'createdDate': '2026-04-09 12:43:51', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Pune', 'url': 'https://www.naukri.com/jobs-in-pune'}], 'keySkills': {'other': [{'clickable': '', 'label': 'kubernetes'}, {'clickable': 'oracle', 'label': 'oracle'}, {'clickable': '', 'label': 'bitbucket'}, {'clickable': 'hibernate framework', 'label': 'hibernate'}, {'clickable': 'caching', 'label': 'caching'}, {'clickable': 'redis', 'label': 'redis'}, {'clickable': 'nosql', 'label': 'nosql'}, {'clickable': 'microservices', 'label': 'microservices'}, {'clickable': 'docker', 'label': 'docker'}, {'clickable': 'spring framework', 'label': 'spring framework'}, {'clickable': 'cloud', 'label': 'cloud'}, {'clickable': '', 'label': 'angular'}, {'clickable': 'scripting', 'label': 'scripting'}, {'clickable': 'java', 'label': 'java'}, {'clickable': 'git', 'label': 'git'}, {'clickable': 'linux', 'label': 'linux'}, {'clickable': '', 'label': 'full stack'}, {'clickable': 'jenkins', 'label': 'jenkins'}, {'clickable': 'cloud computing', 'label': 'cloud computing'}, {'clickable': 'sdlc', 'label': 'sdlc'}, {'clickable': 'mongodb', 'label': 'mongodb'}, {'clickable': 'programming', 'label': 'programming'}, {'clickable': 'jira', 'label': 'jira'}], 'preferred': [{'clickable': '', 'label': 'full stack developer'}]}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Java Full Stack Developer', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'jobId': '090426915783', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Virtusa', 'isSaved': False, 'tagsAndSkills': 'full stack developer,kubernetes,oracle,bitbucket,hibernate,caching,redis,nosql', 'placeholders': [{'type': 'experience', 'label': '0-1 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Pune'}], 'companyId': 1354, 'jdURL': '/job-listings-java-full-stack-developer-virtusa-consulting-services-pvt-ltd-pune-0-to-1-years-090426915783', 'staticUrl': 'virtusa-jobs-careers-1354', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/virtusa-consulting-services-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 6077, 'AggregateRating': '3.7', 'Title': 'Virtusa Consulting Services Reviews by Employees'}, 'jobDescription': '&lt;ul&gt; &lt;li&gt;  Full-stack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles Extensive experience working with most if not all the technologies listed below:  &lt;/li&gt; &lt;li&gt;  Java Core with extensive hands-on experience with concurrent programming. Spring Framework including Core, Integration, Batch, JDBC, Hibernate  &lt;/li&gt; &lt;li&gt;  Good development experience in Angular and Angular components  &lt;/li&gt; &lt;li&gt;  Good Knowledge in RxJS, Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent.  &lt;/li&gt; &lt;li&gt;  Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes)  &lt;/li&gt; &lt;li&gt;  Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB  &lt;/li&gt; &lt;li&gt;  Familiarity with Linux environment including scripting skills  &lt;/li&gt; &lt;li&gt;  SDLC/Dev Ops - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits  &lt;/li&gt; &lt;/ul&gt;', 'showMultipleApply': False, 'groupId': 1186200, 'isTopGroup': 0, 'createdDate': 1775718831687, 'mode': 'jp', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-1 Yrs', 'minimumExperience': '0', 'maximumExperience': '1', 'applyByTime': '4:43 PM', 'companyApplyJob': False, 'walkinJob': False, 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:52:00.333Z', 'url': 'https://www.nma.mobi/post/v4/job/090426915783?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt; &lt;li&gt;  Full-stack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles Extensive experience working with most if not all the technologies listed below:  &lt;/li&gt; &lt;li&gt;  Java Core with extensive hands-on experience with concurrent programming.  &lt;/li&gt; &lt;li&gt;  Spring Framework including Core, Integration, Batch, JDBC, Hibernate Good development experience in Angular and Angular components Good Knowledge in RxJS, Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent.  &lt;/li&gt; &lt;li&gt;  Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes)  &lt;/li&gt; &lt;li&gt;  Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB Familiarity with Linux environment including scripting skills  &lt;/li&gt; &lt;li&gt;  SDLC/Dev Ops - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits  &lt;/li&gt; &lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426915778?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['B.Tech / B.E. in Any Specialization'], 'pg': ['Any Postgraduate'], 'degreeCombination': 'ugorpgorppg', 'premiumProcessed': False, 'eduPlaceholderText': '', 'ppg': [], 'label': '', 'isSchool': None}, 'hideApplyButton': False, 'applyCount': 1088, 'groupId': 1186200, 'roleCategory': 'Software Development', 'mode': 'jp', 'tagLabels': [], 'jobRole': 'Full Stack Developer', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 1, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'wfhType': '0', 'companyDetail': {'name': 'Virtusa', 'websiteUrl': '', 'details': 'Virtusa Corporation (NASDAQ: VRTU) is a global information technology (IT) services company providing IT consulting, technology and outsourcing services. Using our enhanced global delivery model, innovative platforming approach and industry expertise, we provide cost-effective services that enable our clients to use IT to enhance business performance, accelerate time-to-market, increase productivity and improve customer service. We serve Global 2000 enterprises and the leading software vendors in communications &amp; technology; banking, financial services &amp; insurance; and media &amp; information industries. We build and sustain application platforms for our clients that create competitive advantage.&lt;br&gt;&lt;br&gt;&lt;br&gt;Founded in 1996 and headquartered in Massachusetts, we have offices and technology centers throughout the U.S., U.K. and Asia. Globally, Virtusa has been acknowledged and recognized by customers, industry associations and media among others. Some of the awards and recognitions include Dataquest-CMR €“ IT Best Employers Survey -2012 (Ranked No. 5), International Business Award €“ 2012(Stevie awards) , Britain€™s Top Employers- 2012, American Business Award€“ 2012,Boston Business Journal€™s Fastest Growing Public Companies, Global Services 100, Fintech 100, Sri Lanka National HRM and others.', 'address': 'Sy.No.115/Part,Plot No.10,Virtusa IT Park,Nanakram  guda Village,Serilingampally Mandal  , Hyderabad, Telangana, India', 'media': {'ppt': [], 'video': [], 'photos': []}, 'hiringFor': '', 'isKycSuccessful': True}, 'jobIconType': '', 'shortDescription': 'Experienced full-stack developer skilled in Java Core concurrency, Spring Framework, Angular, RxJS, micro-frontend architecture, Redis caching, Docker, Kubernetes, Oracle and MongoDB databases, Linux scripting, and CI/CD tools|Design and develop scalable, maintainable applications using OOP principles; work with microservices, cloud technologies, and DevOps pipelines', 'consent': False, 'jobId': '090426915778', 'showEducationAsPlaceholder': False, 'companyId': 1354, 'brandingTags': [], 'functionalArea': 'Engineering - Software &amp; QA', 'fatFooter': {}, 'experienceText': '0-1 Yrs', 'referenceCode': 'CREQ252193', 'vacancy': 0, 'template': '', 'locationGids': ['139'], 'description': '&lt;ul&gt; &lt;li&gt;  Full-stack developer with experience in designing and developing robust, scalable, and maintainable applications applying Object Oriented Design principles Extensive experience working with most if not all the technologies listed below:  &lt;/li&gt; &lt;li&gt;  Java Core with extensive hands-on experience with concurrent programming.  &lt;/li&gt; &lt;li&gt;  Spring Framework including Core, Integration, Batch, JDBC, Hibernate Good development experience in Angular and Angular components Good Knowledge in RxJS, Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent.  &lt;/li&gt; &lt;li&gt;  Cloud computing technologies with practical experience working with containers, microservices and large datasets (Docker, Kubernetes)  &lt;/li&gt; &lt;li&gt;  Databases - RDBMS preferably Oracle, NoSQL preferably MongoDB Familiarity with Linux environment including scripting skills  &lt;/li&gt; &lt;li&gt;  SDLC/Dev Ops - Git/BitBucket, CI/CD pipeline frameworks such as Jenkins, SonarQube, JIRA, any secure coding toolkits  &lt;/li&gt; &lt;/ul&gt;', 'staticCompanyName': 'virtusa-jobs-careers-1354', 'industry': 'Banking', 'staticUrl': 'https://www.naukri.com/job-listings-java-full-stack-developer-virtusa-consulting-services-pvt-ltd-pune-0-to-1-years-090426915778', 'title': 'Java Full Stack Developer', 'walkIn': False, 'maximumExperience': 1, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 1563, 'jobType': 'fulltime', 'companyPageUrl': 'virtusa-overview-1186200', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'microsite': False, 'createdDate': '2026-04-09 12:43:50', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Pune', 'url': 'https://www.naukri.com/jobs-in-pune'}], 'keySkills': {'other': [{'clickable': '', 'label': 'kubernetes'}, {'clickable': 'oracle', 'label': 'oracle'}, {'clickable': '', 'label': 'bitbucket'}, {'clickable': 'hibernate framework', 'label': 'hibernate'}, {'clickable': 'caching', 'label': 'caching'}, {'clickable': 'redis', 'label': 'redis'}, {'clickable': 'nosql', 'label': 'nosql'}, {'clickable': 'microservices', 'label': 'microservices'}, {'clickable': 'docker', 'label': 'docker'}, {'clickable': 'spring framework', 'label': 'spring framework'}, {'clickable': 'cloud', 'label': 'cloud'}, {'clickable': '', 'label': 'angular'}, {'clickable': 'scripting', 'label': 'scripting'}, {'clickable': 'java', 'label': 'java'}, {'clickable': 'git', 'label': 'git'}, {'clickable': 'linux', 'label': 'linux'}, {'clickable': '', 'label': 'full stack'}, {'clickable': 'jenkins', 'label': 'jenkins'}, {'clickable': 'cloud computing', 'label': 'cloud computing'}, {'clickable': 'sdlc', 'label': 'sdlc'}, {'clickable': 'mongodb', 'label': 'mongodb'}, {'clickable': 'programming', 'label': 'programming'}, {'clickable': 'jira', 'label': 'jira'}], 'preferred': [{'clickable': '', 'label': 'full stack developer'}]}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Java Full Stack Developer', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/1186200.gif', 'jobId': '090426915778', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Virtusa', 'isSaved': False, 'tagsAndSkills': 'full stack developer,kubernetes,oracle,bitbucket,hibernate,caching,redis,nosql', 'placeholders': [{'type': 'experience', 'label': '0-1 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Pune'}], 'companyId': 1354, 'jdURL': '/job-listings-java-full-stack-developer-virtusa-consulting-services-pvt-ltd-pune-0-to-1-years-090426915778', 'staticUrl': 'virtusa-jobs-careers-1354', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/virtusa-consulting-services-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 6077, 'AggregateRating': '3.7', 'Title': 'Virtusa Consulting Services Reviews by Employees'}, 'jobDescription': 'Spring Framework including Core,Integration,Batch,JDBC,Hibernate Good development experience in Angular and Angular components Good Knowledge in RxJS,Router and micro-frontend architecure Distributed Caching frameworks such as Redis or equivalent&lt;br&gt;&lt;br&gt;Java Core with extensive hands-on experience with concurrent programming', 'showMultipleApply': False, 'groupId': 1186200, 'isTopGroup': 0, 'createdDate': 1775718830177, 'mode': 'jp', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-1 Yrs', 'minimumExperience': '0', 'maximumExperience': '1', 'applyByTime': '4:43 PM', 'companyApplyJob': False, 'walkinJob': False, 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:52:01.697Z', 'url': 'https://www.nma.mobi/post/v4/job/090426915778?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt; &lt;li&gt; The Seller AI team within International Seller Services organization is focused on helping sellers with the right set of Gen-AI/LLM powered tools and agentic solutions that can enable them to accelerate business growth on Amazon.  &lt;/li&gt; &lt;li&gt; Our primary focus lies in handling annotations for training, measuring, and improving Artificial Intelligence (AI) and Large Language Models (LLMs), enabling Amazon to deliver a superior seller experience to our sellers worldwide.  &lt;/li&gt; &lt;li&gt; The AI Benchmarking Associate supports the evaluation of AI systems by designing and executing benchmarking and audit activities to assess model quality, compliance, robustness, and fairness. &lt;/li&gt; &lt;li&gt;  The role combines elements of AI auditing, quality assurance, and traditional audit-style documentation and stakeholder communication. By joining us, you will play a pivotal role in shaping the future of selling on Amazon for sellers worldwide.  &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;/ul&gt; &lt;p&gt; Key job responsibilities &lt;br /&gt; &lt;/p&gt; &lt;ul&gt; &lt;li&gt; As part of your role, you will have the opportunity to, &lt;br /&gt; Assist in planning and executing benchmarking exercises for AI models, including defining test plans, metrics, and acceptance criteria across accuracy, robustness, bias, and reliability &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Support content accuracy, relevancy, and privacy checks by reviewing datasets, model outputs, and data handling practices, escalating potential regulatory risks. &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Validate data based on specific annotation guidelines, ensuring the accuracy and quality of the collected information &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Prepare clear audit and benchmarking reports, including error ratings, root-cause analysis, and recommendations, and contribute to presentations for senior stakeholders &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Maintain organized audit documentation, evidence, and benchmarking datasets to support internal review &lt;br /&gt; &lt;/li&gt; &lt;li&gt; You will work closely with your team members and managers to drive process efficiencies and explore opportunities for automation &lt;br /&gt; &lt;/li&gt; &lt;li&gt; You will strive to enhance the productivity and effectiveness of the data generation by contributing to the development and continuous improvement of AI audit methodologies, checklists, and test frameworks as regulations and best practices evolve. &lt;br /&gt; &lt;/li&gt; &lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426503474?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['LLM in Law'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 33, 'groupId': 398058, 'roleCategory': 'Non Voice', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'Technical Support - Non Voice', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 1, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/398058.gif', 'wfhType': '0', 'companyDetail': {'name': 'Amazon', 'details': 'Amazon is guided by four principles: customer obsession rather than competitor focus, passion for invention, commitment to operational excellence, and long-term thinking. We are driven by the excitement of building technologies, inventing products, and providing services that change lives. We embrace new ways of doing things, make decisions quickly, and are not afraid to fail. We have the scope and capabilities of a large company, and the spirit and heart of a small one.', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': 'Our primary focus lies in handling annotations for training,measuring,and improving Artificial Intelligence (AI) and Large Language Models (LLMs),enabling Amazon to deliver a superior seller experience to our sellers worldwide', 'consent': False, 'jobId': '090426503474', 'showEducationAsPlaceholder': False, 'companyId': 728574, 'brandingTags': [], 'functionalArea': 'Customer Success, Service &amp; Operations', 'fatFooter': {}, 'experienceText': '0-7 Yrs', 'referenceCode': '', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://www.amazon.jobs/en/jobs/10385866/ai-benchmarking-specialist-sp-support-german-international-seller-growth', 'locationGids': ['97'], 'description': '&lt;ul&gt; &lt;li&gt; The Seller AI team within International Seller Services organization is focused on helping sellers with the right set of Gen-AI/LLM powered tools and agentic solutions that can enable them to accelerate business growth on Amazon.  &lt;/li&gt; &lt;li&gt; Our primary focus lies in handling annotations for training, measuring, and improving Artificial Intelligence (AI) and Large Language Models (LLMs), enabling Amazon to deliver a superior seller experience to our sellers worldwide.  &lt;/li&gt; &lt;li&gt; The AI Benchmarking Associate supports the evaluation of AI systems by designing and executing benchmarking and audit activities to assess model quality, compliance, robustness, and fairness. &lt;/li&gt; &lt;li&gt; \xa0The role combines elements of AI auditing, quality assurance, and traditional audit-style documentation and stakeholder communication. By joining us, you will play a pivotal role in shaping the future of selling on Amazon for sellers worldwide.  &lt;br /&gt; &lt;br /&gt; &lt;/li&gt; &lt;/ul&gt; &lt;p&gt; Key job responsibilities &lt;br /&gt; &lt;/p&gt; &lt;ul&gt; &lt;li&gt; As part of your role, you will have the opportunity to, &lt;br /&gt; Assist in planning and executing benchmarking exercises for AI models, including defining test plans, metrics, and acceptance criteria across accuracy, robustness, bias, and reliability &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Support content accuracy, relevancy, and privacy checks by reviewing datasets, model outputs, and data handling practices, escalating potential regulatory risks. &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Validate data based on specific annotation guidelines, ensuring the accuracy and quality of the collected information &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Prepare clear audit and benchmarking reports, including error ratings, root-cause analysis, and recommendations, and contribute to presentations for senior stakeholders &lt;br /&gt; &lt;/li&gt; &lt;li&gt; Maintain organized audit documentation, evidence, and benchmarking datasets to support internal review &lt;br /&gt; &lt;/li&gt; &lt;li&gt; You will work closely with your team members and managers to drive process efficiencies and explore opportunities for automation &lt;br /&gt; &lt;/li&gt; &lt;li&gt; You will strive to enhance the productivity and effectiveness of the data generation by contributing to the development and continuous improvement of AI audit methodologies, checklists, and test frameworks as regulations and best practices evolve. &lt;br /&gt; &lt;/li&gt; &lt;/ul&gt;', 'staticCompanyName': 'amazon-jobs-careers-93000', 'industry': 'Internet', 'staticUrl': 'https://www.naukri.com/job-listings-ai-benchmarking-specialist-amazon-development-centre-india-pvt-ltd-bengaluru-0-to-7-years-090426503474', 'title': 'AI Benchmarking Specialist', 'walkIn': False, 'maximumExperience': 7, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 152, 'jobType': 'fulltime', 'companyPageUrl': 'amazon-overview-398058', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/398058.gif', 'microsite': False, 'createdDate': '2026-04-09 18:06:28', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/398058.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Bengaluru', 'url': 'https://www.naukri.com/jobs-in-bangalore'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426503474&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': 'root cause analysis', 'label': 'Root cause analysis'}, {'clickable': 'automation', 'label': 'Automation'}, {'clickable': '', 'label': 'Manager Quality Assurance'}, {'clickable': 'audit documentation', 'label': 'Audit documentation'}, {'clickable': 'artificial intelligence', 'label': 'Artificial Intelligence'}, {'clickable': 'machine learning', 'label': 'Machine learning'}, {'clickable': 'german', 'label': 'German'}, {'clickable': 'continuous improvement', 'label': 'Continuous improvement'}, {'clickable': 'quality compliance', 'label': 'Quality compliance'}, {'clickable': 'recruitment', 'label': 'Recruitment'}], 'preferred': []}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'AI Benchmarking Specialist', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/398058.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/398058.gif', 'jobId': '090426503474', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Amazon', 'isSaved': False, 'tagsAndSkills': 'Root cause analysis,Automation,Manager Quality Assurance,Audit documentation,Artificial Intelligence,Machine learning,German,Continuous improvement', 'placeholders': [{'type': 'experience', 'label': '0-7 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Bengaluru'}], 'companyId': 728574, 'jdURL': '/job-listings-ai-benchmarking-specialist-amazon-development-centre-india-pvt-ltd-bengaluru-0-to-7-years-090426503474', 'staticUrl': 'amazon-jobs-careers-93000', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/amazon-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 31423, 'AggregateRating': '3.9', 'Title': 'Amazon Reviews by Employees'}, 'jobDescription': 'Our primary focus lies in handling annotations for training,measuring,and improving Artificial Intelligence (AI) and Large Language Models (LLMs),enabling Amazon to deliver a superior seller experience to our sellers worldwide', 'showMultipleApply': False, 'groupId': 398058, 'isTopGroup': 0, 'createdDate': 1775738188000, 'mode': 'crawled', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-7 Yrs', 'minimumExperience': '0', 'maximumExperience': '7', 'applyByTime': '10:06 PM', 'companyApplyJob': True, 'walkinJob': False, 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426503474&amp;logstr=srprestapi', 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:52:11.232Z', 'url': 'https://www.nma.mobi/post/v4/job/090426503474?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>Associate Software Platform Engineer II</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;We are looking for a highly skilled and experienced Associate Software Platform Engineer II to join our team. The ideal candidate will have a strong background in software development and a passion for delivering high-quality solutions.&lt;/p&gt;&lt;br&gt;&lt;h3&gt;Roles and Responsibility&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Design, develop, and test software applications using various programming languages and technologies.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Collaborate with cross-functional teams to identify and prioritize project requirements.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Develop and maintain technical documentation for software applications.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Troubleshoot and resolve technical issues related to software applications.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Participate in code reviews and contribute to improving overall code quality.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Stay up-to-date with industry trends and emerging technologies.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;&lt;br&gt;&lt;h3&gt;Job Requirements&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Strong understanding of software development principles and methodologies.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Proficiency in one or more programming languages such as Java, Python, or C++.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Experience with database management systems and querying languages.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Excellent problem-solving skills and attention to detail.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Strong communication and teamwork skills.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Ability to work in an agile environment and adapt to changing priorities.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Company name: MetLife.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Industry: IT Services &amp; Consulting.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;&lt;br&gt;&lt;br&gt;Disclaimer: This job description has been sourced from a public domain and may have been modified by Naukri.com to improve clarity for our users. We encourage job seekers to verify all details directly with the employer via their official channels before applying.</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426502551?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['Any Postgraduate'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 319, 'groupId': 115024, 'roleCategory': 'Software Development', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'Full Stack Developer', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 1, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/115024.gif', 'wfhType': '0', 'companyDetail': {'name': 'Metlife', 'details': 'We live in a time of unprecedented change. A time when economies, regulations, and social safety nets are all in flux. Customers around the globe have told us theyre overwhelmed by the pace of change and are looking for a trusted partner to help them manage lifes twists and turns. MetLife is committed to being that partner. Thats why were transforming our business: Delivering greater value for the people we serve by becoming a simpler, more focused, and future-facing company. Well be introducing new ways to meet our customersevolving needs, with flexible products; simpler, more intuitive experiences and a range of new services.', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': 'Strong understanding of software development principles and methodologies.  .  Proficiency in one or more programming languages such as Java,Python,or C++.  |  . Disclaimer: This job description has been sourced from a public domain and may have been modified by Naukri.com to improve clarity for our users|Experience with database management systems and querying languages.', 'consent': False, 'jobId': '090426502551', 'showEducationAsPlaceholder': False, 'companyId': 4681368, 'brandingTags': [], 'functionalArea': 'Engineering - Software &amp; QA', 'fatFooter': {}, 'experienceText': '0-3 Yrs', 'referenceCode': '16355', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://www.metlifecareers.com/en_US/ml/JobDetail/Associate-Software-Platform-Engineer-II/16355', 'locationGids': ['139'], 'description': '&lt;p&gt;We are looking for a highly skilled and experienced Associate Software Platform Engineer II to join our team. The ideal candidate will have a strong background in software development and a passion for delivering high-quality solutions.&lt;/p&gt;&lt;br&gt;&lt;h3&gt;Roles and Responsibility&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Design, develop, and test software applications using various programming languages and technologies.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Collaborate with cross-functional teams to identify and prioritize project requirements.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Develop and maintain technical documentation for software applications.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Troubleshoot and resolve technical issues related to software applications.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Participate in code reviews and contribute to improving overall code quality.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Stay up-to-date with industry trends and emerging technologies.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;&lt;br&gt;&lt;h3&gt;Job Requirements&lt;/h3&gt;&lt;br&gt;&lt;ul&gt;&lt;br&gt;&lt;li&gt;Strong understanding of software development principles and methodologies.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Proficiency in one or more programming languages such as Java, Python, or C++.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Experience with database management systems and querying languages.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Excellent problem-solving skills and attention to detail.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Strong communication and teamwork skills.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Ability to work in an agile environment and adapt to changing priorities.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Company name: MetLife.&lt;/li&gt;&lt;br&gt;&lt;li&gt;Industry: IT Services &amp; Consulting.&lt;/li&gt;&lt;br&gt;&lt;/ul&gt;&lt;br&gt;&lt;br&gt;Disclaimer: This job description has been sourced from a public domain and may have been modified by Naukri.com to improve clarity for our users. We encourage job seekers to verify all details directly with the employer via their official channels before applying.', 'staticCompanyName': 'metlife-jobs-careers-222139', 'industry': 'IT Services &amp; Consulting', 'staticUrl': 'https://www.naukri.com/job-listings-associate-software-platform-engineer-ii-metlife-pune-0-to-3-years-090426502551', 'title': 'Associate Software Platform Engineer II', 'walkIn': False, 'maximumExperience': 3, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 760, 'jobType': 'fulltime', 'companyPageUrl': 'metlife-overview-115024', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/115024.gif', 'microsite': False, 'createdDate': '2026-04-09 16:28:12', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/115024.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Pune', 'url': 'https://www.naukri.com/jobs-in-pune'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426502551&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': '', 'label': 'emerging technologies'}, {'clickable': 'python', 'label': 'python'}, {'clickable': 'software development', 'label': 'software development'}, {'clickable': 'c', 'label': 'c'}, {'clickable': 'it services', 'label': 'it services'}, {'clickable': 'programming', 'label': 'programming languages'}, {'clickable': '', 'label': 'code quality'}, {'clickable': 'database', 'label': 'database management'}, {'clickable': 'java', 'label': 'java'}, {'clickable': 'design', 'label': 'design'}, {'clickable': 'agile', 'label': 'agile'}, {'clickable': 'technical documentation', 'label': 'technical documentation'}, {'clickable': 'programming', 'label': 'programming'}], 'preferred': []}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Associate Software Platform Engineer II', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/115024.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/115024.gif', 'jobId': '090426502551', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Metlife', 'isSaved': False, 'tagsAndSkills': 'emerging technologies,python,software development,c,it services,programming languages,code quality,database management', 'placeholders': [{'type': 'experience', 'label': '0-3 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Pune'}], 'companyId': 4681368, 'jdURL': '/job-listings-associate-software-platform-engineer-ii-metlife-pune-0-to-3-years-090426502551', 'staticUrl': 'metlife-jobs-careers-222139', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/metlife-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 1766, 'AggregateRating': '4.0', 'Title': 'MetLife Reviews by Employees'}, 'jobDescription': '  Strong understanding of software development principles and methodologies.  .  Proficiency in one or more programming languages such as Java,Python,or C++.  &lt;br&gt;&lt;br&gt;  . Disclaimer: This job description has been sourced from a public domain and may have been modified by Naukri.com to improve clarity for our users&lt;br&gt;&lt;br&gt;Experience with database management systems and querying languages.', 'showMultipleApply': False, 'groupId': 115024, 'isTopGroup': 0, 'createdDate': 1775732292000, 'mode': 'crawled', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-3 Yrs', 'minimumExperience': '0', 'maximumExperience': '3', 'applyByTime': '8:28 PM', 'companyApplyJob': True, 'walkinJob': False, 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426502551&amp;logstr=srprestapi', 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:52:16.491Z', 'url': 'https://www.nma.mobi/post/v4/job/090426502551?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>Data Analyst - AI Projects</t>
+  </si>
+  <si>
+    <t>&lt;b&gt; Data Analyst AI Projects &lt;/b&gt; &lt;br /&gt; &lt;div&gt; &lt;strong&gt; Job Position: &lt;/strong&gt; &lt;br /&gt; Full-Time | Entry-Level &lt;/div&gt; &lt;div&gt; &lt;strong&gt; Responsibilities: &lt;/strong&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; Analyze large datasets to extract actionable insights and support AI projects. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Create dashboards and reports to visualize trends and findings. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Work closely with AI engineers and data scientists to prepare and clean datasets. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Identify patterns and anomalies in data to support model training and validation. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Assist in tracking and reporting project KPIs to stakeholders. &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;strong&gt; Skills/Knowledge Required: &lt;/strong&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; Strong skills in SQL, Excel, and data visualization tools (e.g., Tableau, Power BI). &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Knowledge of Python or R for data analysis. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Familiarity with AI and ML concepts is a plus but not mandatory. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Strong attention to detail and the ability to manage multiple tasks effectively. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Good communication skills to collaborate with cross-functional teams. &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;strong&gt; Experience: &lt;/strong&gt; &lt;br /&gt; 0-2 years in data analysis or related fields; internships count. &lt;/div&gt; &lt;div&gt; &lt;strong&gt; Location: &lt;/strong&gt; &lt;br /&gt; Mumbai, India. &lt;/div&gt; Apply Now  &lt;div&gt; First Name  &lt;/div&gt; &lt;div&gt; Last Name  &lt;/div&gt; &lt;div&gt; Your Email  &lt;/div&gt; &lt;div&gt; Phone Number  &lt;/div&gt; &lt;div&gt; More About Your Self  &lt;/div&gt; &lt;span&gt; Submit &lt;/span&gt;  Other Active Jobs  &lt;div&gt; Location: Bangalore (Asia Time Zone) Department: AI Technology Reports To: Chief Product Technology Officer (CPTO) Type: Full-Time Role &lt;/div&gt; &lt;div&gt; If you are a product enthusiast who wants to build and fund game-changing companies, this is for you. Location: Bengaluru, &lt;/div&gt; &lt;div&gt; Role and Responsibilities As an ML engineer , you will be responsible for building our machine learning team and infrastructure. &lt;/div&gt; Quick Links  &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; Contact Us  &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; We cover the entire spectrum of AI talent, ensuring that your needs are met at every stage of your AI project lifecycle. Whether you require data collection specialists, machine learning engineers, or experts in ML Ops and production, we have the expertise to source candidates with the right skills for the job. &lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426500673?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['Any Postgraduate'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 750, 'groupId': 9482649, 'roleCategory': 'Data Science &amp; Machine Learning', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'NLP / DL Engineering / Architect', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 0, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/9482649.gif', 'wfhType': '0', 'companyDetail': {'name': 'Kintellect Partners Llp', 'details': 'Kintellect Partners LLP operates in the IT services and consulting industry, focusing on technology-driven solutions and enterprise support. Its careers page highlights opportunities in software development, consulting, and IT operations, reflecting a commitment to delivering innovative and scalable digital services. By combining technical expertise with client-focused strategies, the company positions itself as a trusted partner for organizations seeking digital transformation and operational efficiency.', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': 'internships count|Skills / Knowledge Required:  . Strong skills in SQL,Excel,and data visualization tools (e.g.,Tableau,Power BI)| . Good communication skills to collaborate with cross-functional teams. |Experience:  0-2 years in data analysis or related fields', 'consent': False, 'jobId': '090426500673', 'showEducationAsPlaceholder': False, 'companyId': 125524940, 'brandingTags': [], 'functionalArea': 'Data Science &amp; Analytics', 'fatFooter': {}, 'experienceText': '0-2 Yrs', 'referenceCode': '', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://kintellect.in/data-analyst-ai-projects/', 'locationGids': ['97'], 'description': '&lt;b&gt; Data Analyst AI Projects &lt;/b&gt; &lt;br /&gt; &lt;div&gt; &lt;strong&gt; Job Position: &lt;/strong&gt; &lt;br /&gt; Full-Time | Entry-Level &lt;/div&gt; &lt;div&gt; &lt;strong&gt; Responsibilities: &lt;/strong&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; Analyze large datasets to extract actionable insights and support AI projects. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Create dashboards and reports to visualize trends and findings. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Work closely with AI engineers and data scientists to prepare and clean datasets. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Identify patterns and anomalies in data to support model training and validation. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Assist in tracking and reporting project KPIs to stakeholders. &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;strong&gt; Skills/Knowledge Required: &lt;/strong&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; Strong skills in SQL, Excel, and data visualization tools (e.g., Tableau, Power BI). &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Knowledge of Python or R for data analysis. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Familiarity with AI and ML concepts is a plus but not mandatory. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Strong attention to detail and the ability to manage multiple tasks effectively. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Good communication skills to collaborate with cross-functional teams. &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;strong&gt; Experience: &lt;/strong&gt; &lt;br /&gt; 0-2 years in data analysis or related fields; internships count. &lt;/div&gt; &lt;div&gt; &lt;strong&gt; Location: &lt;/strong&gt; &lt;br /&gt; Mumbai, India. &lt;/div&gt; Apply Now  &lt;div&gt; First Name  &lt;/div&gt; &lt;div&gt; Last Name  &lt;/div&gt; &lt;div&gt; Your Email  &lt;/div&gt; &lt;div&gt; Phone Number  &lt;/div&gt; &lt;div&gt; More About Your Self  &lt;/div&gt; &lt;span&gt; Submit &lt;/span&gt;  Other Active Jobs  &lt;div&gt; Location: Bangalore (Asia Time Zone) Department: AI Technology Reports To: Chief Product Technology Officer (CPTO) Type: Full-Time Role &lt;/div&gt; &lt;div&gt; If you are a product enthusiast who wants to build and fund game-changing companies, this is for you. Location: Bengaluru, &lt;/div&gt; &lt;div&gt; Role and Responsibilities As an ML engineer , you will be responsible for building our machine learning team and infrastructure. &lt;/div&gt; Quick Links  &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; Contact Us  &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; We cover the entire spectrum of AI talent, ensuring that your needs are met at every stage of your AI project lifecycle. Whether you require data collection specialists, machine learning engineers, or experts in ML Ops and production, we have the expertise to source candidates with the right skills for the job. &lt;/div&gt;', 'staticCompanyName': 'kintellect-partners-jobs-careers-123920687', 'industry': 'IT Services &amp; Consulting', 'staticUrl': 'https://www.naukri.com/job-listings-data-analyst-ai-projects-kintellect-partners-llp-bengaluru-0-to-2-years-090426500673', 'title': 'Data Analyst - AI Projects', 'walkIn': False, 'maximumExperience': 2, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 1531, 'jobType': 'fulltime', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/9482649.gif', 'microsite': False, 'createdDate': '2026-04-09 16:04:44', 'consultant': False, 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Bengaluru', 'url': 'https://www.naukri.com/jobs-in-bangalore'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426500673&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': 'data analysis', 'label': 'Data analysis'}, {'clickable': 'machine learning', 'label': 'Machine learning'}, {'clickable': 'data collection', 'label': 'Data collection'}, {'clickable': 'infrastructure', 'label': 'Infrastructure'}, {'clickable': '', 'label': 'Manager Technology'}, {'clickable': 'power bi', 'label': 'power bi'}, {'clickable': 'data analysis', 'label': 'Data Analyst'}, {'clickable': 'data visualization', 'label': 'data visualization'}, {'clickable': 'sql', 'label': 'SQL'}, {'clickable': 'python', 'label': 'Python'}], 'preferred': []}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Data Analyst - AI Projects', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/9482649.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/9482649.gif', 'jobId': '090426500673', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Kintellect Partners Llp', 'isSaved': False, 'tagsAndSkills': 'Data analysis,Machine learning,Data collection,Infrastructure,Manager Technology,power bi,Data Analyst,data visualization', 'placeholders': [{'type': 'experience', 'label': '0-2 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Bengaluru'}], 'companyId': 125524940, 'jdURL': '/job-listings-data-analyst-ai-projects-kintellect-partners-llp-bengaluru-0-to-2-years-090426500673', 'staticUrl': 'kintellect-partners-jobs-careers-123920687', 'jobDescription': 'internships count&lt;br&gt;&lt;br&gt;Skills / Knowledge Required:  . Strong skills in SQL,Excel,and data visualization tools (e.g.,Tableau,Power BI)&lt;br&gt;&lt;br&gt; . Good communication skills to collaborate with cross-functional teams. &lt;br&gt;&lt;br&gt;Experience:  0-2 years in data analysis or related fields', 'showMultipleApply': False, 'groupId': 9482649, 'isTopGroup': 0, 'createdDate': 1775730884000, 'mode': 'crawled', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-2 Yrs', 'minimumExperience': '0', 'maximumExperience': '2', 'applyByTime': '8:04 PM', 'companyApplyJob': True, 'walkinJob': False, 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426500673&amp;logstr=srprestapi', 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:52:16.582Z', 'url': 'https://www.nma.mobi/post/v4/job/090426500673?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>AI Engineer Intern_SaaS Intelligence &amp; Automation</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;strong&gt;Role &amp; responsibilities&lt;/strong&gt; &lt;/p&gt;&lt;br /&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;AI Agents &amp; Automation&lt;/strong&gt;  Build agents that can log into SaaS apps, traverse workflows, extract data, and take actions autonomously using tools like Claude Cowork, Playwright, and MCP servers&lt;/li&gt;&lt;li&gt;&lt;strong&gt;LLM Integration&lt;/strong&gt;  Integrate Claude / GPT APIs into existing SaaS modules to add contextual intelligence (smart search, auto-fill, summarization, recommendations)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Prompt Engineering &amp; Chain-of-Thought Pipelines&lt;/strong&gt; — Design and optimize prompts for production-grade AI features, not just demos&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Browser &amp; UI Automation&lt;/strong&gt; — Use Playwright or Puppeteer to automate SaaS UI traversal, documentation generation, and regression workflows&lt;/li&gt;&lt;li&gt;&lt;strong&gt;MCP Server Development&lt;/strong&gt; — Build Model Context Protocol servers that expose SaaS app actions as AI-consumable tools&lt;/li&gt;&lt;li&gt;&lt;strong&gt;RAG Pipelines&lt;/strong&gt; — Connect SaaS data (documents, tickets, logs) to LLMs via vector stores for intelligent retrieval&lt;/li&gt;&lt;li&gt;&lt;strong&gt;AI-Generated Documentation&lt;/strong&gt; — Build pipelines that auto-generate support docs, changelogs, and user guides from live app state&lt;/li&gt;&lt;/ul&gt;&lt;br /&gt;&lt;br /&gt;&lt;p&gt;&lt;strong&gt;Preferred candidate profile&lt;/strong&gt; &lt;/p&gt;&lt;br /&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Pursuing or recently completed a degree in CS, AI, Data Science, or a related field&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Strong Python&lt;/strong&gt; — you'll write production scripts, not just notebooks&lt;/li&gt;&lt;li&gt;Solid understanding of &lt;strong&gt;REST APIs and JSON&lt;/strong&gt; — SaaS integration is API-first&lt;/li&gt;&lt;li&gt;Familiarity with &lt;strong&gt;LLMs and prompt design&lt;/strong&gt; (OpenAI, Anthropic, or equivalent)&lt;/li&gt;&lt;li&gt;Basic understanding of &lt;strong&gt;browser automation&lt;/strong&gt; (Playwright, Selenium, or Puppeteer)&lt;/li&gt;&lt;li&gt;Comfort working in &lt;strong&gt;Git-based workflows&lt;/strong&gt; with real codebases&lt;/li&gt;&lt;/ul&gt;&lt;br /&gt;&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426020260?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'videoProfilePreferred': True, 'savedJobFlag': 0, 'education': {'ug': ['B.Tech / B.E. in Artificial Intelligence, Artificial Intelligence And Machine Learning'], 'degreeCombination': '', 'premiumProcessed': False, 'eduPlaceholderText': '', 'pg': [], 'ppg': [], 'label': '', 'isSchool': None}, 'hideApplyButton': False, 'applyCount': 177, 'groupId': 7461613, 'roleCategory': 'Software Development', 'internshipStartDate': '2026-04-14 00:00:00', 'mode': 'jp', 'tagLabels': [], 'jobRole': 'Software Development - Other', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 0, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/7461613.gif', 'wfhType': '0', 'companyDetail': {'name': 'Codengine Technologies', 'websiteUrl': '', 'details': "&lt;p&gt; &lt;/p&gt;&lt;p&gt;CodeNgine, with its roots firmly planted in the vibrant city of Pune. Within our headquarters and beyond, we've cultivated a community of exceptionally gifted individuals, all sharing a common and attainable vision.&lt;/p&gt;", 'address': '1st Floor, 112 A , Regent Plaza Baner-Pashan Link Road, Baner Gaon Pune, Maharashtra, PUNE, Maharashtra, India', 'media': {'ppt': [], 'video': [], 'photos': []}, 'hiringFor': '', 'hideClientName': False, 'clientType': '', 'isKycSuccessful': True}, 'jobIconType': '', 'shortDescription': 'Degree in CS, AI, or Data Science with strong Python, REST API, LLM and prompt design, and browser automation skills|Build autonomous AI agents, integrate LLM APIs into SaaS, design prompt pipelines, automate UI workflows, develop MCP servers, and create AI-generated documentation', 'consent': False, 'jobId': '090426020260', 'showEducationAsPlaceholder': False, 'companyId': 6122824, 'brandingTags': [], 'functionalArea': 'Engineering - Software &amp; QA', 'fatFooter': {}, 'experienceText': '0-1 Yrs', 'vacancy': 3, 'template': '', 'locationGids': ['139'], 'description': "&lt;p&gt;&lt;strong&gt;Role &amp; responsibilities&lt;/strong&gt; &lt;/p&gt;&lt;br /&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;AI Agents &amp; Automation&lt;/strong&gt;  Build agents that can log into SaaS apps, traverse workflows, extract data, and take actions autonomously using tools like Claude Cowork, Playwright, and MCP servers&lt;/li&gt;&lt;li&gt;&lt;strong&gt;LLM Integration&lt;/strong&gt;  Integrate Claude / GPT APIs into existing SaaS modules to add contextual intelligence (smart search, auto-fill, summarization, recommendations)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Prompt Engineering &amp; Chain-of-Thought Pipelines&lt;/strong&gt; — Design and optimize prompts for production-grade AI features, not just demos&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Browser &amp; UI Automation&lt;/strong&gt; — Use Playwright or Puppeteer to automate SaaS UI traversal, documentation generation, and regression workflows&lt;/li&gt;&lt;li&gt;&lt;strong&gt;MCP Server Development&lt;/strong&gt; — Build Model Context Protocol servers that expose SaaS app actions as AI-consumable tools&lt;/li&gt;&lt;li&gt;&lt;strong&gt;RAG Pipelines&lt;/strong&gt; — Connect SaaS data (documents, tickets, logs) to LLMs via vector stores for intelligent retrieval&lt;/li&gt;&lt;li&gt;&lt;strong&gt;AI-Generated Documentation&lt;/strong&gt; — Build pipelines that auto-generate support docs, changelogs, and user guides from live app state&lt;/li&gt;&lt;/ul&gt;&lt;br /&gt;&lt;br /&gt;&lt;p&gt;&lt;strong&gt;Preferred candidate profile&lt;/strong&gt; &lt;/p&gt;&lt;br /&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Pursuing or recently completed a degree in CS, AI, Data Science, or a related field&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Strong Python&lt;/strong&gt; — you'll write production scripts, not just notebooks&lt;/li&gt;&lt;li&gt;Solid understanding of &lt;strong&gt;REST APIs and JSON&lt;/strong&gt; — SaaS integration is API-first&lt;/li&gt;&lt;li&gt;Familiarity with &lt;strong&gt;LLMs and prompt design&lt;/strong&gt; (OpenAI, Anthropic, or equivalent)&lt;/li&gt;&lt;li&gt;Basic understanding of &lt;strong&gt;browser automation&lt;/strong&gt; (Playwright, Selenium, or Puppeteer)&lt;/li&gt;&lt;li&gt;Comfort working in &lt;strong&gt;Git-based workflows&lt;/strong&gt; with real codebases&lt;/li&gt;&lt;/ul&gt;&lt;br /&gt;&lt;br /&gt;", 'staticCompanyName': 'codengine-technologies-jobs-careers-6122824', 'industry': 'Software Product', 'staticUrl': 'https://www.naukri.com/job-listings-ai-engineer-intern-saas-intelligence-automation-codengine-technologies-pune-0-to-1-years-090426020260', 'title': 'AI Engineer Intern_SaaS Intelligence &amp; Automation', 'walkIn': False, 'maximumExperience': 1, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 362, 'jobType': 'internship', 'internshipInfo': {'amount': '5,000/month', 'duration': '3 months duration', 'internshipExactStartDate': "Start date : 14th Apr'26", 'internshipApplyByDate': "Apply by : 10th Apr'26", 'perksAndBenefits': [{'perksAndBenefitsId': '1', 'label': 'Certificate'}, {'perksAndBenefitsId': '3', 'label': 'Letter of recommendation'}], 'currency': 'INR'}, 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/7461613.gif', 'microsite': False, 'internshipDuration': '3 months ', 'createdDate': '2026-04-09 14:40:34', 'internshipDeadline': '2026-04-10 23:59:59', 'consultant': False, 'showRecruiterDetail': False, 'locations': [{'localities': ['Baner Pashan Link Road'], 'label': 'Pune', 'url': 'https://www.naukri.com/jobs-in-pune'}], 'keySkills': {'other': [{'clickable': 'po', 'label': 'PoS'}, {'clickable': 'saas', 'label': 'SAAS'}, {'clickable': '', 'label': 'Playwright'}, {'clickable': 'crm', 'label': 'CRM'}], 'preferred': [{'clickable': '', 'label': 'AI ML'}, {'clickable': '', 'label': 'Langchain'}, {'clickable': '', 'label': 'Ai Solutions'}, {'clickable': 'mcp', 'label': 'MCP'}, {'clickable': 'python', 'label': 'Python'}]}, 'salaryDetail': {'hideSalary': False, 'currency': 'INR', 'label': '5,000'}, 'board': '1', 'basicInfo': {'title': 'AI Engineer Intern_SaaS Intelligence &amp; Automation', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/7461613.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/7461613.gif', 'jobId': '090426020260', 'jobType': 'internship', 'currency': 'INR', 'footerPlaceholderLabel': "Starts : 14th Apr' 26", 'footerPlaceholderColor': 'green', 'companyName': 'Codengine Technologies', 'isSaved': False, 'placeholders': [{'type': 'duration', 'label': '3 months duration'}, {'type': 'salary', 'label': '5,000/month'}, {'type': 'location', 'label': 'Pune(Baner Pashan Link Road)'}], 'companyId': 6122824, 'jdURL': '/job-listings-ai-engineer-intern-saas-intelligence-automation-codengine-technologies-pune-0-to-1-years-090426020260', 'staticUrl': 'codengine-technologies-jobs-careers-6122824', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/codengine-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 16, 'AggregateRating': '3.5', 'Title': 'CodeNgine Technologies Pvt. Ltd. Reviews by Employees'}, 'jobDescription': 'Preferred candidate profile . Pursuing or recently completed a degree in CS,AI,Data Science,or a related field', 'showMultipleApply': False, 'groupId': 7461613, 'isTopGroup': 0, 'createdDate': 0, 'internshipTags': ['Closing soon'], 'mode': 'jp', 'board': '1', 'vacancy': 3, 'companyApplyJob': False, 'walkinJob': False, 'saved': False}, 'scrapedAt': '2026-04-10T09:52:16.983Z', 'url': 'https://www.nma.mobi/post/v4/job/090426020260?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426500672?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['Any Postgraduate'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 717, 'groupId': 9482649, 'roleCategory': 'Data Science &amp; Machine Learning', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'NLP / DL Engineering / Architect', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 0, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/9482649.gif', 'wfhType': '0', 'companyDetail': {'name': 'Kintellect Partners Llp', 'details': 'Kintellect Partners LLP operates in the IT services and consulting industry, focusing on technology-driven solutions and enterprise support. Its careers page highlights opportunities in software development, consulting, and IT operations, reflecting a commitment to delivering innovative and scalable digital services. By combining technical expertise with client-focused strategies, the company positions itself as a trusted partner for organizations seeking digital transformation and operational efficiency.', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': 'internships count|Skills / Knowledge Required:  . Strong skills in SQL,Excel,and data visualization tools (e.g.,Tableau,Power BI)| . Good communication skills to collaborate with cross-functional teams. |Experience:  0-2 years in data analysis or related fields', 'consent': False, 'jobId': '090426500672', 'showEducationAsPlaceholder': False, 'companyId': 125524940, 'brandingTags': [], 'functionalArea': 'Data Science &amp; Analytics', 'fatFooter': {}, 'experienceText': '0-2 Yrs', 'referenceCode': '', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://kintellect.in/data-analyst-ai-projects-2/', 'locationGids': ['97'], 'description': '&lt;b&gt; Data Analyst AI Projects &lt;/b&gt; &lt;br /&gt; &lt;div&gt; &lt;strong&gt; Job Position: &lt;/strong&gt; &lt;br /&gt; Full-Time | Entry-Level &lt;/div&gt; &lt;div&gt; &lt;strong&gt; Responsibilities: &lt;/strong&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; Analyze large datasets to extract actionable insights and support AI projects. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Create dashboards and reports to visualize trends and findings. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Work closely with AI engineers and data scientists to prepare and clean datasets. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Identify patterns and anomalies in data to support model training and validation. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Assist in tracking and reporting project KPIs to stakeholders. &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;strong&gt; Skills/Knowledge Required: &lt;/strong&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; Strong skills in SQL, Excel, and data visualization tools (e.g., Tableau, Power BI). &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Knowledge of Python or R for data analysis. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Familiarity with AI and ML concepts is a plus but not mandatory. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Strong attention to detail and the ability to manage multiple tasks effectively. &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; Good communication skills to collaborate with cross-functional teams. &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;strong&gt; Experience: &lt;/strong&gt; &lt;br /&gt; 0-2 years in data analysis or related fields; internships count. &lt;/div&gt; &lt;div&gt; &lt;strong&gt; Location: &lt;/strong&gt; &lt;br /&gt; Mumbai, India. &lt;/div&gt; Apply Now  &lt;div&gt; First Name  &lt;/div&gt; &lt;div&gt; Last Name  &lt;/div&gt; &lt;div&gt; Your Email  &lt;/div&gt; &lt;div&gt; Phone Number  &lt;/div&gt; &lt;div&gt; More About Your Self  &lt;/div&gt; &lt;span&gt; Submit &lt;/span&gt;  Other Active Jobs  &lt;div&gt; Location: Bangalore (Asia Time Zone) Department: AI Technology Reports To: Chief Product Technology Officer (CPTO) Type: Full-Time Role &lt;/div&gt; &lt;div&gt; If you are a product enthusiast who wants to build and fund game-changing companies, this is for you. Location: Bengaluru, &lt;/div&gt; &lt;div&gt; Role and Responsibilities As an ML engineer , you will be responsible for building our machine learning team and infrastructure. &lt;/div&gt; Quick Links  &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; Contact Us  &lt;ul&gt; &lt;li&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; We cover the entire spectrum of AI talent, ensuring that your needs are met at every stage of your AI project lifecycle. Whether you require data collection specialists, machine learning engineers, or experts in ML Ops and production, we have the expertise to source candidates with the right skills for the job. &lt;/div&gt;', 'staticCompanyName': 'kintellect-partners-jobs-careers-123920687', 'industry': 'IT Services &amp; Consulting', 'staticUrl': 'https://www.naukri.com/job-listings-data-analyst-ai-projects-kintellect-partners-llp-bengaluru-0-to-2-years-090426500672', 'title': 'Data Analyst - AI Projects', 'walkIn': False, 'maximumExperience': 2, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 1514, 'jobType': 'fulltime', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/9482649.gif', 'microsite': False, 'createdDate': '2026-04-09 16:04:44', 'consultant': False, 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Bengaluru', 'url': 'https://www.naukri.com/jobs-in-bangalore'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426500672&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': 'data analysis', 'label': 'Data analysis'}, {'clickable': 'machine learning', 'label': 'Machine learning'}, {'clickable': 'data collection', 'label': 'Data collection'}, {'clickable': 'infrastructure', 'label': 'Infrastructure'}, {'clickable': '', 'label': 'Manager Technology'}, {'clickable': 'power bi', 'label': 'power bi'}, {'clickable': 'data analysis', 'label': 'Data Analyst'}, {'clickable': 'data visualization', 'label': 'data visualization'}, {'clickable': 'sql', 'label': 'SQL'}, {'clickable': 'python', 'label': 'Python'}], 'preferred': []}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Data Analyst - AI Projects', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/9482649.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/9482649.gif', 'jobId': '090426500672', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Kintellect Partners Llp', 'isSaved': False, 'tagsAndSkills': 'Data analysis,Machine learning,Data collection,Infrastructure,Manager Technology,power bi,Data Analyst,data visualization', 'placeholders': [{'type': 'experience', 'label': '0-2 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Bengaluru'}], 'companyId': 125524940, 'jdURL': '/job-listings-data-analyst-ai-projects-kintellect-partners-llp-bengaluru-0-to-2-years-090426500672', 'staticUrl': 'kintellect-partners-jobs-careers-123920687', 'jobDescription': 'internships count&lt;br&gt;&lt;br&gt;Skills / Knowledge Required:  . Strong skills in SQL,Excel,and data visualization tools (e.g.,Tableau,Power BI)&lt;br&gt;&lt;br&gt; . Good communication skills to collaborate with cross-functional teams. &lt;br&gt;&lt;br&gt;Experience:  0-2 years in data analysis or related fields', 'showMultipleApply': False, 'groupId': 9482649, 'isTopGroup': 0, 'createdDate': 1775730884000, 'mode': 'crawled', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-2 Yrs', 'minimumExperience': '0', 'maximumExperience': '2', 'applyByTime': '8:04 PM', 'companyApplyJob': True, 'walkinJob': False, 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426500672&amp;logstr=srprestapi', 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:52:17.004Z', 'url': 'https://www.nma.mobi/post/v4/job/090426500672?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+  <si>
+    <t>Data Scientist 1</t>
+  </si>
+  <si>
+    <t>&lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; Job Summary &lt;/b&gt; &lt;/div&gt; Data Science team delivers the best in class actionable business insights through cutting-edge predictive models and data science techniques. The Data Scientist is responsible for generating data-driven insights using advanced analytics and machine learning techniques to support enterprise data science needs within Bread Financial. &lt;div&gt; &lt;br /&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; Essential Job Functions &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Analytics under supervision and guidance, completes the following: &lt;span&gt; &lt;/span&gt; 1) extracts and samples data, conducts data integrity checks and applicable data pre-processing such as treatment of missing values and outliers, 2) conducts exploratory data analysis for preliminary data insights to drive the selection of modeling approach that best addresses the business problem, 3) reveals hidden data patterns by data mining using unsupervised learning techniques such as clustering analysis and factor analysis, 4) conducts feature engineering to create/derive model predictors with strong predictive power, 5) trains/tunes classification/regression models by applying supervised learning techniques such as generalized linear models assuming applicable underlying distributions such as logit and gamma, tree-based models such as decision trees, random forest, boosted trees, etc, and neural net models, and 6) conducts proper model test/validation, diagnoses and fixes model issues (eg, over-fitting) when applicable. &lt;span&gt; &lt;/span&gt; Sizes the impact of using the models in production as part of the current strategy. &lt;span&gt; &lt;/span&gt; Presents results and business case to manager. Provides support for implementation and monitoring of solutions that are implemented. &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Collaboration under supervision and guidance, translates analytical results into useful recommendations for review with manager. &lt;span&gt; &lt;/span&gt; Demonstrates strong verbal and written communication skills when working with internal partners and when presenting results to various audiences. Develops foundational knowledge of credit card operations, banking, financial, loyalty rewards, retail, and credit card regulations while working with the business. &lt;span&gt; &lt;/span&gt; Collaborates with other data scientists in the company to share best practices and data science innovations. &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Data Science innovation with direction from leader, researches industry trends in data science of new tools, emerging algorithms, advanced platforms, and alternative data to enhance modeling effectiveness and efficiency. &lt;span&gt; &lt;/span&gt; Conducts use case testing for new tools/techniques/platforms/data and provides user input/feedback. &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Model Risk Management - develops foundational knowledge on common model risks and related regulatory requirements; applies proper 1st line of defense controls during model development process to minimize model risk; creates comprehensive model governance documentation and archives model data, scripts, and results; collaborates with model risk management partners to complete model validation/auditing; completes remediation as required by model governance process. &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; Reports to:  &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Manager or higher &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; Working Conditions/ Physical Requirements:  &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Normal office environment  &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; Direct Reports:  &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; None  &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; Minimum Qualifications:  &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Degree Required: bachelors Degree  &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Area of Study: Statistics, Mathematics, Engineering, Data Science, Economics, Computer Science, or another quantitative field &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Years of Work Experience Required: Fresher or less than 1 year experience. &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Type / focus of work experience required: Must have done a course in Data science and Machine learning. &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; Knowledge, Skills and Abilities &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; Must: &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Data Science &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Machine Learning &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Structured Query Language (SQL) &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Python &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Strong Communication skills &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; Good to Have: &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; Natural Language Processing (NLP) &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; Cloud Experience (AZURE/AWS) &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>https://www.nma.mobi/post/v4/job/090426501374?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true</t>
+  </si>
+  <si>
+    <t>{'savedJobFlag': 0, 'education': {'ug': ['Any Graduate'], 'pg': ['Any Postgraduate'], 'ppg': [], 'degreeCombination': '', 'bTechPremium': False, 'mbaPremium': False, 'premiumProcessed': False, 'eduPlaceholderText': '', 'label': '', 'isSchool': False}, 'hideApplyButton': False, 'applyCount': 533, 'groupId': 6254085, 'roleCategory': 'Data Science &amp; Machine Learning', 'mode': 'crawled', 'tagLabels': [], 'jobRole': 'Full Stack Data Scientist', 'companyFollowFlowMetaData': {'companyFollowFlow': False}, 'isTopGroup': 0, 'clientLogo': 'https://img.naukimg.com/logo_images/groups/v1/mobile/6254085.gif', 'wfhType': '0', 'companyDetail': {'name': 'Bread Financial', 'details': 'Bread Financial is a leading provider of simple, personalized payment, lending, and saving solutions. We create opportunities for our customers and partners through digitally enabled choices that offer ease, empowerment, and financial flexibility.', 'address': '', 'media': {'ppt': None, 'video': None, 'photos': None}}, 'jobIconType': '', 'shortDescription': 'Degree Required: bachelors Degree . Area of Study: Statistics,Mathematics,Engineering,Data Science,Economics,Computer Science,or another quantitative field . Years of Work Experience Required: Fresher or less than 1 year experience|Type / focus of work experience required: Must have done a course in Data science and Machine learning. .', 'consent': False, 'jobId': '090426501374', 'showEducationAsPlaceholder': False, 'companyId': 124028422, 'brandingTags': [], 'functionalArea': 'Data Science &amp; Analytics', 'fatFooter': {}, 'experienceText': '0-1 Yrs', 'referenceCode': 'R1012344', 'vacancy': 1, 'template': '', 'applyRedirectUrl': 'https://alliancedata.wd5.myworkdayjobs.com/en-US/breadfinancial_India/job/Bangalore-India/Data-Scientist-1_R1012344', 'locationGids': ['97'], 'description': '&lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; Job Summary &lt;/b&gt; &lt;/div&gt; Data Science team delivers the best in class actionable business insights through cutting-edge predictive models and data science techniques. The Data Scientist is responsible for generating data-driven insights using advanced analytics and machine learning techniques to support enterprise data science needs within Bread Financial. &lt;div&gt; &lt;br /&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; Essential Job Functions &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Analytics under supervision and guidance, completes the following: &lt;span&gt; &lt;/span&gt; 1) extracts and samples data, conducts data integrity checks and applicable data pre-processing such as treatment of missing values and outliers, 2) conducts exploratory data analysis for preliminary data insights to drive the selection of modeling approach that best addresses the business problem, 3) reveals hidden data patterns by data mining using unsupervised learning techniques such as clustering analysis and factor analysis, 4) conducts feature engineering to create/derive model predictors with strong predictive power, 5) trains/tunes classification/regression models by applying supervised learning techniques such as generalized linear models assuming applicable underlying distributions such as logit and gamma, tree-based models such as decision trees, random forest, boosted trees, etc, and neural net models, and 6) conducts proper model test/validation, diagnoses and fixes model issues (eg, over-fitting) when applicable. &lt;span&gt; &lt;/span&gt; Sizes the impact of using the models in production as part of the current strategy. &lt;span&gt; &lt;/span&gt; Presents results and business case to manager. Provides support for implementation and monitoring of solutions that are implemented. &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Collaboration under supervision and guidance, translates analytical results into useful recommendations for review with manager. &lt;span&gt; &lt;/span&gt; Demonstrates strong verbal and written communication skills when working with internal partners and when presenting results to various audiences. Develops foundational knowledge of credit card operations, banking, financial, loyalty rewards, retail, and credit card regulations while working with the business. &lt;span&gt; &lt;/span&gt; Collaborates with other data scientists in the company to share best practices and data science innovations. &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Data Science innovation with direction from leader, researches industry trends in data science of new tools, emerging algorithms, advanced platforms, and alternative data to enhance modeling effectiveness and efficiency. &lt;span&gt; &lt;/span&gt; Conducts use case testing for new tools/techniques/platforms/data and provides user input/feedback. &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Model Risk Management - develops foundational knowledge on common model risks and related regulatory requirements; applies proper 1st line of defense controls during model development process to minimize model risk; creates comprehensive model governance documentation and archives model data, scripts, and results; collaborates with model risk management partners to complete model validation/auditing; completes remediation as required by model governance process. &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; Reports to:  &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Manager or higher &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; Working Conditions/ Physical Requirements:  &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Normal office environment  &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; Direct Reports:  &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; None  &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;span&gt; &lt;/span&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; &lt;span&gt; Minimum Qualifications:  &lt;/span&gt; &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Degree Required: bachelors Degree  &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Area of Study: Statistics, Mathematics, Engineering, Data Science, Economics, Computer Science, or another quantitative field &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Years of Work Experience Required: Fresher or less than 1 year experience. &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Type / focus of work experience required: Must have done a course in Data science and Machine learning. &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;span&gt; &lt;/span&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; Knowledge, Skills and Abilities &lt;/b&gt; &lt;/div&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; Must: &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Data Science &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Machine Learning &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Structured Query Language (SQL) &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Python &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; &lt;span&gt; Strong Communication skills &lt;/span&gt; &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt; &lt;div&gt; &lt;/div&gt; &lt;div&gt; &lt;b&gt; Good to Have: &lt;/b&gt; &lt;/div&gt; &lt;ul&gt; &lt;li&gt; &lt;div&gt; Natural Language Processing (NLP) &lt;/div&gt; &lt;/li&gt; &lt;li&gt; &lt;div&gt; Cloud Experience (AZURE/AWS) &lt;/div&gt; &lt;/li&gt; &lt;/ul&gt;', 'staticCompanyName': 'bread-financial-jobs-careers-4665806', 'industry': 'Financial Services', 'staticUrl': 'https://www.naukri.com/job-listings-data-scientist-1-bread-financial-bengaluru-0-to-1-years-090426501374', 'title': 'Data Scientist 1', 'walkIn': False, 'maximumExperience': 1, 'logStr': '--jobsearchios-0-F-0-1---', 'viewCount': 1193, 'jobType': 'fulltime', 'companyPageUrl': 'bread-financial-overview-6254085', 'minimumExperience': 0, 'employmentType': 'Full Time, Permanent', 'banner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/6254085.gif', 'microsite': False, 'createdDate': '2026-04-09 16:10:27', 'consultant': False, 'socialBanner': 'https://img.naukimg.com/logo_images/groups/v1/mobile/6254085.gif', 'showRecruiterDetail': False, 'locations': [{'localities': [], 'label': 'Bengaluru', 'url': 'https://www.naukri.com/jobs-in-bangalore'}], 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426501374&amp;logstr=jdrestapi', 'keySkills': {'other': [{'clickable': 'remediation', 'label': 'remediation'}, {'clickable': 'data analysis', 'label': 'Data analysis'}, {'clickable': 'analytical', 'label': 'Analytical'}, {'clickable': 'risk management', 'label': 'Risk management'}, {'clickable': 'data mining', 'label': 'Data mining'}, {'clickable': 'business case', 'label': 'Business case'}, {'clickable': 'financial service', 'label': 'Financial services'}, {'clickable': 'monitoring', 'label': 'Monitoring'}, {'clickable': 'sql', 'label': 'SQL'}], 'preferred': []}, 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0, 'label': 'Not Disclosed', 'minSalaryPerMonth': 0, 'maxSalaryPerMonth': 0}, 'board': '1', 'basicInfo': {'title': 'Data Scientist 1', 'logoPath': 'https://img.naukimg.com/logo_images/groups/v1/mobile/6254085.gif', 'logoPathV3': 'https://img.naukimg.com/logo_images/groups/v1/mobile/6254085.gif', 'jobId': '090426501374', 'currency': 'INR', 'footerPlaceholderLabel': '1 Day Ago', 'footerPlaceholderColor': 'green', 'companyName': 'Bread Financial', 'isSaved': False, 'tagsAndSkills': 'remediation,Data analysis,Analytical,Risk management,Data mining,Business case,Financial services,Monitoring', 'placeholders': [{'type': 'experience', 'label': '0-1 Yrs'}, {'type': 'salary', 'label': 'Not disclosed'}, {'type': 'location', 'label': 'Bengaluru'}], 'companyId': 124028422, 'jdURL': '/job-listings-data-scientist-1-bread-financial-bengaluru-0-to-1-years-090426501374', 'staticUrl': 'bread-financial-jobs-careers-4665806', 'ambitionBoxData': {'Url': 'https://www.ambitionbox.com/reviews/bread-financial-reviews?utm_campaign=srp_ratings&amp;utm_medium=app&amp;utm_source=naukri', 'ReviewsCount': 233, 'AggregateRating': '3.8', 'Title': 'Bread Financial Reviews by Employees'}, 'jobDescription': 'Degree Required: bachelors Degree . Area of Study: Statistics,Mathematics,Engineering,Data Science,Economics,Computer Science,or another quantitative field . Years of Work Experience Required: Fresher or less than 1 year experience&lt;br&gt;&lt;br&gt;Type / focus of work experience required: Must have done a course in Data science and Machine learning. .', 'showMultipleApply': False, 'groupId': 6254085, 'isTopGroup': 0, 'createdDate': 1775731227000, 'mode': 'crawled', 'board': '1', 'salaryDetail': {'minimumSalary': 0, 'maximumSalary': 0, 'currency': 'INR', 'hideSalary': True, 'variablePercentage': 0}, 'experienceText': '0-1 Yrs', 'minimumExperience': '0', 'maximumExperience': '1', 'applyByTime': '8:10 PM', 'companyApplyJob': True, 'walkinJob': False, 'companyApplyUrl': 'https://www.naukri.com/cloudgateway-apply/apply-services/v0/apply/saveCompanyApply?id=&amp;file=090426501374&amp;logstr=srprestapi', 'segmentedTemplateId': 'Template1', 'saved': False}, 'scrapedAt': '2026-04-10T09:52:17.468Z', 'url': 'https://www.nma.mobi/post/v4/job/090426501374?src=jobsearchios&amp;brandedJd=true&amp;xp=0&amp;brandedConsultantJd=true'}</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -55,14 +897,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -85,44 +930,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -149,15 +994,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -184,7 +1028,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -196,150 +1039,861 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" t="s">
+        <v>143</v>
+      </c>
+      <c r="E28" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" t="s">
+        <v>145</v>
+      </c>
+      <c r="D29" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>148</v>
+      </c>
+      <c r="C30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" t="s">
+        <v>154</v>
+      </c>
+      <c r="E31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" t="s">
+        <v>158</v>
+      </c>
+      <c r="E32" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" t="s">
+        <v>164</v>
+      </c>
+      <c r="E34" t="s">
+        <v>106</v>
+      </c>
+      <c r="G34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>